--- a/config/companies.xlsx
+++ b/config/companies.xlsx
@@ -755,6 +755,21 @@
       <c r="E15" t="n">
         <v>10</v>
       </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>NOT FOUND</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://careers.ice.com/jobs?page=6&amp;tags2=Technology</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>browser: rendered job list with 10 rows</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="12" t="inlineStr">
@@ -808,7 +823,11 @@
           <t>T-Mobile</t>
         </is>
       </c>
-      <c r="B18" s="12" t="n"/>
+      <c r="B18" s="12" t="inlineStr">
+        <is>
+          <t>https://tmobile.wd1.myworkdayjobs.com/External/job/Henrietta-New-York/Account-Associate_REQ364623/apply</t>
+        </is>
+      </c>
       <c r="C18" s="12" t="inlineStr">
         <is>
           <t>https://careers.t-mobile.com/</t>
@@ -822,6 +841,21 @@
       <c r="E18" t="n">
         <v>500</v>
       </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>https://tmobile.wd1.myworkdayjobs.com/External/job/Henrietta-New-York/Account-Associate_REQ364623/apply</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>NOT FOUND</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>http: workday API returned 500 jobs</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
@@ -914,6 +948,21 @@
       <c r="E22" t="n">
         <v>7</v>
       </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>NOT FOUND</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>NOT FOUND</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>none: browser found only 0 row(s)</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
@@ -947,7 +996,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>none: successfactors collector failed: SuccessFactors search unavailable: HTTP 404 from https://career4.successfactors.com/search/</t>
+          <t>none: browser found only 0 row(s)</t>
         </is>
       </c>
     </row>
@@ -1017,6 +1066,21 @@
       <c r="E26" t="n">
         <v>250</v>
       </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>NOT FOUND</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>NOT FOUND</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>none: browser found only 0 row(s)</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="12" t="inlineStr">
@@ -1088,6 +1152,21 @@
       <c r="E29" t="n">
         <v>250</v>
       </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>NOT FOUND</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://careers.chewy.com/us/en/search-results?from=50&amp;s=1</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>browser: rendered job list with 10 rows</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="12" t="inlineStr">
@@ -1109,6 +1188,21 @@
       <c r="E30" t="n">
         <v>10</v>
       </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>NOT FOUND</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.pepsicojobs.com/main/jobs</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>browser: rendered job list with 10 rows</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="12" t="inlineStr">
@@ -1130,6 +1224,21 @@
       <c r="E31" t="n">
         <v>14</v>
       </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>NOT FOUND</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://careers.fedex.com/jobs?page_number=6</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>browser: rendered job list with 25 rows</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="12" t="inlineStr">
@@ -1212,6 +1321,21 @@
       <c r="E34" t="n">
         <v>20</v>
       </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>NOT FOUND</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>NOT FOUND</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>none: browser found only 0 row(s)</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="12" t="inlineStr">
@@ -1233,6 +1357,21 @@
       <c r="E35" t="n">
         <v>52</v>
       </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>NOT FOUND</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://jobs.cmc.com/go/View-All-Jobs/8239200/</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>browser: rendered job list with 26 rows</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="12" t="inlineStr">
@@ -1254,6 +1393,24 @@
       <c r="E36" t="n">
         <v>1000</v>
       </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>NOT FOUND</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>NOT FOUND</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">none: browser stage failed: Page.goto: net::ERR_NAME_NOT_RESOLVED at https://careers.prim.com/
+Call log:
+  - navigating to "https://careers.prim.com/", waiting until "domcontentloaded"
+</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="12" t="inlineStr">
@@ -1286,7 +1443,11 @@
           <t>7-Eleven</t>
         </is>
       </c>
-      <c r="B38" s="12" t="n"/>
+      <c r="B38" s="12" t="inlineStr">
+        <is>
+          <t>https://careers.7-eleven.com/</t>
+        </is>
+      </c>
       <c r="C38" s="12" t="inlineStr">
         <is>
           <t>https://careers.7-eleven.com/</t>
@@ -1299,6 +1460,21 @@
       </c>
       <c r="E38" t="n">
         <v>15</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>https://careers.7-eleven.com/</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>NOT FOUND</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>browser: radancy API returned 5141 jobs</t>
+        </is>
       </c>
     </row>
     <row r="39">

--- a/config/companies.xlsx
+++ b/config/companies.xlsx
@@ -934,7 +934,11 @@
           <t>Boingo Wireless</t>
         </is>
       </c>
-      <c r="B22" s="12" t="n"/>
+      <c r="B22" s="12" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/boingo</t>
+        </is>
+      </c>
       <c r="C22" s="12" t="inlineStr">
         <is>
           <t>https://www.boingo.com/careers/</t>

--- a/config/companies.xlsx
+++ b/config/companies.xlsx
@@ -512,7 +512,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -541,7 +541,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="7">
@@ -562,7 +562,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="8">
@@ -629,7 +629,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="11">
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="12">
@@ -671,7 +671,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>289</v>
+        <v>282</v>
       </c>
     </row>
     <row r="13">
@@ -732,7 +732,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>181</v>
+        <v>184</v>
       </c>
     </row>
     <row r="15">
@@ -749,11 +749,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>469</v>
+        <v>480</v>
       </c>
     </row>
     <row r="17">
@@ -810,7 +810,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -900,7 +900,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>10</v>
+        <v>9999</v>
       </c>
     </row>
     <row r="21">
@@ -921,7 +921,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -1026,7 +1026,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1315</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="25">
@@ -1133,7 +1133,7 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
     </row>
     <row r="29">
@@ -1154,7 +1154,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1186,11 +1186,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1222,11 +1222,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>280</v>
+        <v>140</v>
       </c>
     </row>
     <row r="34">
@@ -1319,11 +1319,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -1355,11 +1355,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -1395,7 +1395,7 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
     </row>
     <row r="38">
@@ -1463,7 +1463,7 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>15</v>
+        <v>5140</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5000</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="40">
@@ -1524,7 +1524,7 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>132</v>
+        <v>68</v>
       </c>
     </row>
     <row r="41">
@@ -1549,7 +1549,7 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
+        <v>317</v>
       </c>
     </row>
     <row r="42">
@@ -1566,11 +1566,11 @@
       <c r="C42" s="12" t="n"/>
       <c r="D42" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -1616,11 +1616,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -1645,7 +1645,7 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>492</v>
       </c>
     </row>
     <row r="46">
@@ -1691,7 +1691,7 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0</v>
+        <v>580</v>
       </c>
     </row>
     <row r="48">
@@ -1708,11 +1708,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -1737,7 +1737,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="50">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="E50" t="n">
@@ -1779,11 +1779,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -1821,11 +1821,11 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -1842,11 +1842,11 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -1867,7 +1867,7 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>483</v>
+        <v>467</v>
       </c>
     </row>
     <row r="56">
@@ -1888,7 +1888,7 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>11</v>
+        <v>100</v>
       </c>
     </row>
     <row r="57">
@@ -1909,7 +1909,7 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>65</v>
+        <v>477</v>
       </c>
     </row>
     <row r="58">
@@ -1926,11 +1926,11 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -1947,11 +1947,11 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="E60" t="n">
@@ -1993,11 +1993,11 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -2039,7 +2039,7 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>433</v>
+        <v>424</v>
       </c>
     </row>
     <row r="64">
@@ -2060,7 +2060,7 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>19</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="65">
@@ -2081,7 +2081,7 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>425</v>
+        <v>436</v>
       </c>
     </row>
     <row r="66">
@@ -2102,7 +2102,7 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>534</v>
+        <v>538</v>
       </c>
     </row>
     <row r="67">
@@ -2123,7 +2123,7 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>349</v>
+        <v>361</v>
       </c>
     </row>
     <row r="68">
@@ -2144,7 +2144,7 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>457</v>
+        <v>465</v>
       </c>
     </row>
     <row r="69">
@@ -2161,11 +2161,11 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -2211,7 +2211,7 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="72">
@@ -2232,7 +2232,7 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
     </row>
     <row r="73">
@@ -2249,11 +2249,11 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -2270,11 +2270,11 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -2295,7 +2295,7 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="76">
@@ -2316,7 +2316,7 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>476</v>
+        <v>488</v>
       </c>
     </row>
     <row r="77">
@@ -2337,7 +2337,7 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="78">
@@ -2354,11 +2354,11 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -2400,7 +2400,7 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="81">
@@ -2417,11 +2417,11 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -2505,7 +2505,7 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>15</v>
+        <v>1942</v>
       </c>
     </row>
     <row r="86">
@@ -2522,11 +2522,11 @@
       <c r="C86" s="12" t="n"/>
       <c r="D86" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
@@ -2564,11 +2564,11 @@
       <c r="C88" s="12" t="n"/>
       <c r="D88" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
@@ -2610,7 +2610,7 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="91">
@@ -2627,11 +2627,11 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
@@ -2698,7 +2698,7 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>19</v>
+        <v>2802</v>
       </c>
     </row>
     <row r="95">
@@ -2740,7 +2740,7 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>476</v>
+        <v>488</v>
       </c>
     </row>
     <row r="97">
@@ -2757,11 +2757,11 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
@@ -2799,11 +2799,11 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
@@ -2866,7 +2866,7 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="103">
@@ -2883,11 +2883,11 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104">
@@ -2904,11 +2904,11 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105">
@@ -2950,7 +2950,7 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>308</v>
+        <v>316</v>
       </c>
     </row>
     <row r="107">
@@ -2975,7 +2975,7 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>225</v>
+        <v>221</v>
       </c>
     </row>
     <row r="108">
@@ -3000,7 +3000,7 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>225</v>
+        <v>221</v>
       </c>
     </row>
     <row r="109">
@@ -3046,7 +3046,7 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>326</v>
+        <v>293</v>
       </c>
     </row>
     <row r="111">
@@ -3084,11 +3084,11 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113">
@@ -3105,11 +3105,11 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114">
@@ -3130,7 +3130,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="E114" t="n">
@@ -3151,11 +3151,11 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -3176,7 +3176,7 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>5</v>
+        <v>2101</v>
       </c>
     </row>
     <row r="117">
@@ -3193,11 +3193,11 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>3694</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118">
@@ -3214,11 +3214,11 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119">
@@ -3239,7 +3239,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="E119" t="n">
@@ -3289,7 +3289,7 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="122">
@@ -3310,7 +3310,7 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>172</v>
+        <v>187</v>
       </c>
     </row>
     <row r="123">
@@ -3352,7 +3352,7 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>466</v>
+        <v>476</v>
       </c>
     </row>
     <row r="125">
@@ -3373,7 +3373,7 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="126">
@@ -3394,7 +3394,7 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="127">
@@ -3415,7 +3415,7 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="128">
@@ -3432,11 +3432,11 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129">
@@ -3478,7 +3478,7 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="131">
@@ -3499,7 +3499,7 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>195</v>
+        <v>198</v>
       </c>
     </row>
     <row r="132">
@@ -3537,11 +3537,11 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="134">
@@ -3566,7 +3566,7 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>228</v>
+        <v>239</v>
       </c>
     </row>
     <row r="135">
@@ -3583,11 +3583,11 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="136">
@@ -3633,7 +3633,7 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>50</v>
+        <v>382</v>
       </c>
     </row>
     <row r="138">
@@ -3692,11 +3692,11 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="141">
@@ -3721,7 +3721,7 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="142">
@@ -3738,11 +3738,11 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="143">
@@ -3780,11 +3780,11 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="145">
@@ -3805,7 +3805,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="E145" t="n">
@@ -3847,11 +3847,11 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="148">
@@ -3872,7 +3872,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="E148" t="n">
@@ -3901,7 +3901,7 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>0</v>
+        <v>185</v>
       </c>
     </row>
     <row r="150">
@@ -3926,7 +3926,7 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="151">
@@ -3947,7 +3947,7 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="152">
@@ -3989,7 +3989,7 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="154">
@@ -4010,7 +4010,7 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>346</v>
+        <v>353</v>
       </c>
     </row>
     <row r="155">
@@ -4027,11 +4027,11 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="156">
@@ -4056,7 +4056,7 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="157">
@@ -4073,11 +4073,11 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="158">
@@ -4094,11 +4094,11 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="159">
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>200</v>
+        <v>196</v>
       </c>
     </row>
     <row r="160">
@@ -4136,11 +4136,11 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
     </row>
     <row r="161">
@@ -4186,7 +4186,7 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>0</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>

--- a/config/companies.xlsx
+++ b/config/companies.xlsx
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="5">
@@ -512,11 +512,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6">
@@ -629,7 +629,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="11">
@@ -749,11 +749,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>480</v>
+        <v>484</v>
       </c>
     </row>
     <row r="17">
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>578</v>
+        <v>581</v>
       </c>
     </row>
     <row r="20">
@@ -900,7 +900,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>9999</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="21">
@@ -1026,7 +1026,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1340</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="25">
@@ -1186,11 +1186,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1222,11 +1222,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1319,11 +1319,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -1355,11 +1355,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="42">
@@ -1566,11 +1566,11 @@
       <c r="C42" s="12" t="n"/>
       <c r="D42" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43">
@@ -1616,11 +1616,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="45">
@@ -1645,7 +1645,7 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>492</v>
+        <v>500</v>
       </c>
     </row>
     <row r="46">
@@ -1708,11 +1708,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="49">
@@ -1737,7 +1737,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="50">
@@ -1758,11 +1758,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="51">
@@ -1779,11 +1779,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
     </row>
     <row r="52">
@@ -1821,11 +1821,11 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
     </row>
     <row r="54">
@@ -1842,11 +1842,11 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="55">
@@ -1867,7 +1867,7 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>467</v>
+        <v>458</v>
       </c>
     </row>
     <row r="56">
@@ -1926,11 +1926,11 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
     </row>
     <row r="59">
@@ -1947,11 +1947,11 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="60">
@@ -1993,11 +1993,11 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="62">
@@ -2039,7 +2039,7 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="64">
@@ -2081,7 +2081,7 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>436</v>
+        <v>440</v>
       </c>
     </row>
     <row r="66">
@@ -2102,7 +2102,7 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>538</v>
+        <v>540</v>
       </c>
     </row>
     <row r="67">
@@ -2123,7 +2123,7 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="68">
@@ -2161,11 +2161,11 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="70">
@@ -2232,7 +2232,7 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="73">
@@ -2249,11 +2249,11 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="74">
@@ -2270,11 +2270,11 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="75">
@@ -2295,7 +2295,7 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="76">
@@ -2316,7 +2316,7 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>488</v>
+        <v>491</v>
       </c>
     </row>
     <row r="77">
@@ -2354,11 +2354,11 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
     </row>
     <row r="79">
@@ -2400,7 +2400,7 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="81">
@@ -2417,11 +2417,11 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
     </row>
     <row r="82">
@@ -2522,11 +2522,11 @@
       <c r="C86" s="12" t="n"/>
       <c r="D86" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
     </row>
     <row r="87">
@@ -2564,11 +2564,11 @@
       <c r="C88" s="12" t="n"/>
       <c r="D88" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="89">
@@ -2610,7 +2610,7 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>184</v>
+        <v>188</v>
       </c>
     </row>
     <row r="91">
@@ -2627,11 +2627,11 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="92">
@@ -2677,7 +2677,7 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>234</v>
+        <v>237</v>
       </c>
     </row>
     <row r="94">
@@ -2698,7 +2698,7 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>2802</v>
+        <v>2803</v>
       </c>
     </row>
     <row r="95">
@@ -2707,7 +2707,11 @@
           <t>Conifer Health Solutions</t>
         </is>
       </c>
-      <c r="B95" s="12" t="n"/>
+      <c r="B95" s="12" t="inlineStr">
+        <is>
+          <t>https://jobs.tenethealth.com/conifer-health-solutions</t>
+        </is>
+      </c>
       <c r="C95" s="12" t="inlineStr">
         <is>
           <t>https://jobs.tenethealth.com/conifer-health-solutions</t>
@@ -2715,11 +2719,11 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>0</v>
+        <v>3275</v>
       </c>
     </row>
     <row r="96">
@@ -2740,7 +2744,7 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>488</v>
+        <v>491</v>
       </c>
     </row>
     <row r="97">
@@ -2799,11 +2803,11 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="100">
@@ -2866,7 +2870,7 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="103">
@@ -2883,11 +2887,11 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="104">
@@ -2904,11 +2908,11 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="105">
@@ -2950,7 +2954,7 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>316</v>
+        <v>323</v>
       </c>
     </row>
     <row r="107">
@@ -3055,7 +3059,11 @@
           <t>Concentra</t>
         </is>
       </c>
-      <c r="B111" s="12" t="n"/>
+      <c r="B111" s="12" t="inlineStr">
+        <is>
+          <t>https://concentrahealthservices.jibeapply.com</t>
+        </is>
+      </c>
       <c r="C111" s="12" t="inlineStr">
         <is>
           <t>https://careers.concentra.com/</t>
@@ -3063,11 +3071,11 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>0</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="112">
@@ -3084,11 +3092,11 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="113">
@@ -3105,11 +3113,11 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="114">
@@ -3130,11 +3138,11 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>0</v>
+        <v>190</v>
       </c>
     </row>
     <row r="115">
@@ -3151,11 +3159,11 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="116">
@@ -3193,11 +3201,11 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>0</v>
+        <v>3699</v>
       </c>
     </row>
     <row r="118">
@@ -3214,11 +3222,11 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="119">
@@ -3239,11 +3247,11 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
     </row>
     <row r="120">
@@ -3268,7 +3276,7 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="121">
@@ -3310,7 +3318,7 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>187</v>
+        <v>191</v>
       </c>
     </row>
     <row r="123">
@@ -3352,7 +3360,7 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="125">
@@ -3373,7 +3381,7 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>172</v>
+        <v>176</v>
       </c>
     </row>
     <row r="126">
@@ -3415,7 +3423,7 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="128">
@@ -3432,11 +3440,11 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
     </row>
     <row r="129">
@@ -3520,7 +3528,7 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="133">
@@ -3537,11 +3545,11 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="134">
@@ -3583,11 +3591,11 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="136">
@@ -3692,11 +3700,11 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="141">
@@ -3780,11 +3788,11 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="145">
@@ -3847,11 +3855,11 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="148">
@@ -4027,11 +4035,11 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="156">
@@ -4073,11 +4081,11 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="158">
@@ -4094,11 +4102,11 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="159">
@@ -4119,7 +4127,7 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="160">
@@ -4136,11 +4144,11 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
     </row>
     <row r="161">

--- a/config/companies.xlsx
+++ b/config/companies.xlsx
@@ -449,7 +449,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5000</v>
+        <v>4998</v>
       </c>
     </row>
     <row r="3">
@@ -562,7 +562,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>499</v>
+        <v>497</v>
       </c>
     </row>
     <row r="8">
@@ -671,7 +671,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="13">
@@ -789,7 +789,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>484</v>
+        <v>487</v>
       </c>
     </row>
     <row r="17">
@@ -900,7 +900,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>10000</v>
+        <v>6200</v>
       </c>
     </row>
     <row r="21">
@@ -1026,7 +1026,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1343</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="25">
@@ -1056,7 +1056,11 @@
           <t>Collins Aerospace</t>
         </is>
       </c>
-      <c r="B26" s="12" t="n"/>
+      <c r="B26" s="12" t="inlineStr">
+        <is>
+          <t>https://careers.rtx.com/global/en/collins-aerospace</t>
+        </is>
+      </c>
       <c r="C26" s="12" t="inlineStr">
         <is>
           <t>https://careers.rtx.com/global/en/collins-aerospace</t>
@@ -1142,7 +1146,11 @@
           <t>Chewy</t>
         </is>
       </c>
-      <c r="B29" s="12" t="n"/>
+      <c r="B29" s="12" t="inlineStr">
+        <is>
+          <t>https://careers.chewy.com/us/en</t>
+        </is>
+      </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
           <t>https://careers.chewy.com/</t>
@@ -1347,7 +1355,11 @@
           <t>Commercial Metals Company (CMC)</t>
         </is>
       </c>
-      <c r="B35" s="12" t="n"/>
+      <c r="B35" s="12" t="inlineStr">
+        <is>
+          <t>https://jobs.cmc.com/</t>
+        </is>
+      </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
           <t>https://jobs.cmc.com/</t>
@@ -1383,7 +1395,11 @@
           <t>Primoris Services</t>
         </is>
       </c>
-      <c r="B36" s="12" t="n"/>
+      <c r="B36" s="12" t="inlineStr">
+        <is>
+          <t>https://prim.wd108.myworkdayjobs.com/Primoris/</t>
+        </is>
+      </c>
       <c r="C36" s="12" t="inlineStr">
         <is>
           <t>https://careers.prim.com/</t>
@@ -1512,7 +1528,11 @@
           <t>BNSF Railway</t>
         </is>
       </c>
-      <c r="B40" s="12" t="n"/>
+      <c r="B40" s="12" t="inlineStr">
+        <is>
+          <t>https://jobs.bnsf.com/us/en</t>
+        </is>
+      </c>
       <c r="C40" s="12" t="inlineStr">
         <is>
           <t>https://jobs.bnsf.com/</t>
@@ -1595,7 +1615,7 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1999</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="44">
@@ -1654,7 +1674,11 @@
           <t>Cisco</t>
         </is>
       </c>
-      <c r="B46" s="12" t="n"/>
+      <c r="B46" s="12" t="inlineStr">
+        <is>
+          <t>https://careers.cisco.com/global/en</t>
+        </is>
+      </c>
       <c r="C46" s="12" t="inlineStr">
         <is>
           <t>https://jobs.cisco.com/</t>
@@ -1737,7 +1761,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>499</v>
+        <v>459</v>
       </c>
     </row>
     <row r="50">
@@ -1758,11 +1782,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -1774,7 +1798,7 @@
       <c r="B51" s="12" t="n"/>
       <c r="C51" s="12" t="inlineStr">
         <is>
-          <t>https://careers.nttdata.com/</t>
+          <t>https://www.nttdata.com/en-us/careers</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -1867,7 +1891,7 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>458</v>
+        <v>180</v>
       </c>
     </row>
     <row r="56">
@@ -1876,7 +1900,11 @@
           <t>Deloitte</t>
         </is>
       </c>
-      <c r="B56" s="12" t="n"/>
+      <c r="B56" s="12" t="inlineStr">
+        <is>
+          <t>https://apply.deloitte.com/en_US/careers</t>
+        </is>
+      </c>
       <c r="C56" s="12" t="inlineStr">
         <is>
           <t>https://apply.deloitte.com/</t>
@@ -1888,7 +1916,7 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
     </row>
     <row r="57">
@@ -1897,7 +1925,11 @@
           <t>PwC</t>
         </is>
       </c>
-      <c r="B57" s="12" t="n"/>
+      <c r="B57" s="12" t="inlineStr">
+        <is>
+          <t>https://jobs.us.pwc.com/</t>
+        </is>
+      </c>
       <c r="C57" s="12" t="inlineStr">
         <is>
           <t>https://jobs.us.pwc.com/</t>
@@ -1926,11 +1958,11 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -2006,7 +2038,11 @@
           <t>Hewlett Packard Enterprise</t>
         </is>
       </c>
-      <c r="B62" s="12" t="n"/>
+      <c r="B62" s="12" t="inlineStr">
+        <is>
+          <t>https://careers.hpe.com/us/en</t>
+        </is>
+      </c>
       <c r="C62" s="12" t="inlineStr">
         <is>
           <t>https://careers.hpe.com/</t>
@@ -2018,7 +2054,7 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>250</v>
+        <v>40</v>
       </c>
     </row>
     <row r="63">
@@ -2027,7 +2063,11 @@
           <t>Dell Technologies</t>
         </is>
       </c>
-      <c r="B63" s="12" t="n"/>
+      <c r="B63" s="12" t="inlineStr">
+        <is>
+          <t>https://enterpriseplatform.dell.com/hcmUI/CandidateExperience/en/sites/careers</t>
+        </is>
+      </c>
       <c r="C63" s="12" t="inlineStr">
         <is>
           <t>https://jobs.dell.com/</t>
@@ -2056,11 +2096,11 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1309</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -2077,11 +2117,11 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>440</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -2102,7 +2142,7 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="67">
@@ -2123,7 +2163,7 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>362</v>
+        <v>40</v>
       </c>
     </row>
     <row r="68">
@@ -2132,7 +2172,11 @@
           <t>Thomson Reuters</t>
         </is>
       </c>
-      <c r="B68" s="12" t="n"/>
+      <c r="B68" s="12" t="inlineStr">
+        <is>
+          <t>https://thomsonreuters.wd5.myworkdayjobs.com/en-US/External_Career_Site</t>
+        </is>
+      </c>
       <c r="C68" s="12" t="inlineStr">
         <is>
           <t>https://careers.thomsonreuters.com/</t>
@@ -2144,7 +2188,7 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="69">
@@ -2174,7 +2218,11 @@
           <t>Alkami Technology</t>
         </is>
       </c>
-      <c r="B70" s="12" t="n"/>
+      <c r="B70" s="12" t="inlineStr">
+        <is>
+          <t>https://alkami.wd12.myworkdayjobs.com/Alkami</t>
+        </is>
+      </c>
       <c r="C70" s="12" t="inlineStr">
         <is>
           <t>https://www.alkami.com/careers/</t>
@@ -2220,7 +2268,11 @@
           <t>Southwest Airlines</t>
         </is>
       </c>
-      <c r="B72" s="12" t="n"/>
+      <c r="B72" s="12" t="inlineStr">
+        <is>
+          <t>https://careers.southwestair.com/us/en/</t>
+        </is>
+      </c>
       <c r="C72" s="12" t="inlineStr">
         <is>
           <t>https://careers.southwestair.com/</t>
@@ -2274,7 +2326,7 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="75">
@@ -2316,7 +2368,7 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="77">
@@ -2325,7 +2377,11 @@
           <t>Cotality</t>
         </is>
       </c>
-      <c r="B77" s="12" t="n"/>
+      <c r="B77" s="12" t="inlineStr">
+        <is>
+          <t>https://cotality.wd115.myworkdayjobs.com/Global</t>
+        </is>
+      </c>
       <c r="C77" s="12" t="inlineStr">
         <is>
           <t>https://careers.cotality.com/</t>
@@ -2367,7 +2423,11 @@
           <t>Digital Realty</t>
         </is>
       </c>
-      <c r="B79" s="12" t="n"/>
+      <c r="B79" s="12" t="inlineStr">
+        <is>
+          <t>https://hdep.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX</t>
+        </is>
+      </c>
       <c r="C79" s="12" t="inlineStr">
         <is>
           <t>https://careers.digitalrealty.com/</t>
@@ -2388,7 +2448,11 @@
           <t>CyrusOne</t>
         </is>
       </c>
-      <c r="B80" s="12" t="n"/>
+      <c r="B80" s="12" t="inlineStr">
+        <is>
+          <t>https://cyrusone.wd1.myworkdayjobs.com/CyrusOneCareerPortal</t>
+        </is>
+      </c>
       <c r="C80" s="12" t="inlineStr">
         <is>
           <t>https://www.cyrusone.com/careers</t>
@@ -2400,7 +2464,7 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="81">
@@ -2430,7 +2494,11 @@
           <t>RTX / Raytheon</t>
         </is>
       </c>
-      <c r="B82" s="12" t="n"/>
+      <c r="B82" s="12" t="inlineStr">
+        <is>
+          <t>https://careers.rtx.com/global/en</t>
+        </is>
+      </c>
       <c r="C82" s="12" t="inlineStr">
         <is>
           <t>https://careers.rtx.com/</t>
@@ -2472,7 +2540,11 @@
           <t>BAE Systems</t>
         </is>
       </c>
-      <c r="B84" s="12" t="n"/>
+      <c r="B84" s="12" t="inlineStr">
+        <is>
+          <t>https://jobs.baesystems.com/global/en</t>
+        </is>
+      </c>
       <c r="C84" s="12" t="inlineStr">
         <is>
           <t>https://jobs.baesystems.com/</t>
@@ -2493,7 +2565,11 @@
           <t>L3Harris</t>
         </is>
       </c>
-      <c r="B85" s="12" t="n"/>
+      <c r="B85" s="12" t="inlineStr">
+        <is>
+          <t>https://careers.l3harris.com/en</t>
+        </is>
+      </c>
       <c r="C85" s="12" t="inlineStr">
         <is>
           <t>https://careers.l3harris.com/</t>
@@ -2598,7 +2674,11 @@
           <t>Children’s Health</t>
         </is>
       </c>
-      <c r="B90" s="12" t="n"/>
+      <c r="B90" s="12" t="inlineStr">
+        <is>
+          <t>https://jobsearch.childrens.com/</t>
+        </is>
+      </c>
       <c r="C90" s="12" t="inlineStr">
         <is>
           <t>https://jobsearch.childrens.com/</t>
@@ -2640,7 +2720,11 @@
           <t>Methodist Health System</t>
         </is>
       </c>
-      <c r="B92" s="12" t="n"/>
+      <c r="B92" s="12" t="inlineStr">
+        <is>
+          <t>https://methodisthealthsystem.wd1.myworkdayjobs.com/MHS_Careers</t>
+        </is>
+      </c>
       <c r="C92" s="12" t="inlineStr">
         <is>
           <t>https://jobs.methodisthealthsystem.org/</t>
@@ -2686,7 +2770,11 @@
           <t>Tenet Healthcare</t>
         </is>
       </c>
-      <c r="B94" s="12" t="n"/>
+      <c r="B94" s="12" t="inlineStr">
+        <is>
+          <t>https://eodr.fa.us2.oraclecloud.com/fscmUI/redwood/internalmobility/opportunitymarketplace/search?optyType=JOB</t>
+        </is>
+      </c>
       <c r="C94" s="12" t="inlineStr">
         <is>
           <t>https://jobs.tenethealth.com/</t>
@@ -2698,7 +2786,7 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>2803</v>
+        <v>2795</v>
       </c>
     </row>
     <row r="95">
@@ -2744,7 +2832,7 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="97">
@@ -2761,11 +2849,11 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="98">
@@ -2774,7 +2862,11 @@
           <t>Cencora</t>
         </is>
       </c>
-      <c r="B98" s="12" t="n"/>
+      <c r="B98" s="12" t="inlineStr">
+        <is>
+          <t>https://careers.cencora.com/us/en</t>
+        </is>
+      </c>
       <c r="C98" s="12" t="inlineStr">
         <is>
           <t>https://careers.cencora.com/</t>
@@ -2816,7 +2908,11 @@
           <t>CVS Health / Aetna</t>
         </is>
       </c>
-      <c r="B100" s="12" t="n"/>
+      <c r="B100" s="12" t="inlineStr">
+        <is>
+          <t>https://jobs.cvshealth.com/us/en</t>
+        </is>
+      </c>
       <c r="C100" s="12" t="inlineStr">
         <is>
           <t>https://jobs.cvshealth.com/</t>
@@ -2837,7 +2933,11 @@
           <t>Signify Health</t>
         </is>
       </c>
-      <c r="B101" s="12" t="n"/>
+      <c r="B101" s="12" t="inlineStr">
+        <is>
+          <t>https://jobs.cvshealth.com/us/en/signify-health</t>
+        </is>
+      </c>
       <c r="C101" s="12" t="inlineStr">
         <is>
           <t>https://www.signifyhealth.com/careers</t>
@@ -2858,7 +2958,11 @@
           <t>Blue Cross and Blue Shield of Texas / HCSC</t>
         </is>
       </c>
-      <c r="B102" s="12" t="n"/>
+      <c r="B102" s="12" t="inlineStr">
+        <is>
+          <t>https://hcsc.wd1.myworkdayjobs.com/HCSC_External/login</t>
+        </is>
+      </c>
       <c r="C102" s="12" t="inlineStr">
         <is>
           <t>https://careers.hcsc.com/</t>
@@ -2870,7 +2974,7 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="103">
@@ -2921,7 +3025,11 @@
           <t>The Cigna Group / Evernorth</t>
         </is>
       </c>
-      <c r="B105" s="12" t="n"/>
+      <c r="B105" s="12" t="inlineStr">
+        <is>
+          <t>https://cigna.wd5.myworkdayjobs.com/cignacareers</t>
+        </is>
+      </c>
       <c r="C105" s="12" t="inlineStr">
         <is>
           <t>https://jobs.thecignagroup.com/</t>
@@ -2942,7 +3050,11 @@
           <t>Elevance Health</t>
         </is>
       </c>
-      <c r="B106" s="12" t="n"/>
+      <c r="B106" s="12" t="inlineStr">
+        <is>
+          <t>https://elevancehealth.wd1.myworkdayjobs.com/ANT/job/Florida---Port-St-Lucie/AFC-Field-Sales---Service-Rep_JR197060/apply</t>
+        </is>
+      </c>
       <c r="C106" s="12" t="inlineStr">
         <is>
           <t>https://careers.elevancehealth.com/</t>
@@ -2954,7 +3066,7 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="107">
@@ -3013,7 +3125,11 @@
           <t>Humana</t>
         </is>
       </c>
-      <c r="B109" s="12" t="n"/>
+      <c r="B109" s="12" t="inlineStr">
+        <is>
+          <t>https://careers.humana.com/us/en</t>
+        </is>
+      </c>
       <c r="C109" s="12" t="inlineStr">
         <is>
           <t>https://careers.humana.com/</t>
@@ -3050,7 +3166,7 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="111">
@@ -3142,7 +3258,7 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="115">
@@ -3154,7 +3270,7 @@
       <c r="B115" s="12" t="n"/>
       <c r="C115" s="12" t="inlineStr">
         <is>
-          <t>https://careers.addus.com/</t>
+          <t>https://addus.com/careers/</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -3172,7 +3288,11 @@
           <t>Enhabit Home Health &amp; Hospice</t>
         </is>
       </c>
-      <c r="B116" s="12" t="n"/>
+      <c r="B116" s="12" t="inlineStr">
+        <is>
+          <t>https://careers.enhabit.com/</t>
+        </is>
+      </c>
       <c r="C116" s="12" t="inlineStr">
         <is>
           <t>https://careers.ehab.com/</t>
@@ -3285,7 +3405,11 @@
           <t>Teladoc Health</t>
         </is>
       </c>
-      <c r="B121" s="12" t="n"/>
+      <c r="B121" s="12" t="inlineStr">
+        <is>
+          <t>https://teladoc.wd503.myworkdayjobs.com/en-US/teladochealth_is_hiring?q=THMG&amp;locationCountry=bc33aa3152ec42d4995f4791a106ed09</t>
+        </is>
+      </c>
       <c r="C121" s="12" t="inlineStr">
         <is>
           <t>https://www.teladochealth.com/careers/</t>
@@ -3369,7 +3493,11 @@
           <t>USAA</t>
         </is>
       </c>
-      <c r="B125" s="12" t="n"/>
+      <c r="B125" s="12" t="inlineStr">
+        <is>
+          <t>https://usaa.wd1.myworkdayjobs.com/USAAJOBSWD/login</t>
+        </is>
+      </c>
       <c r="C125" s="12" t="inlineStr">
         <is>
           <t>https://www.usaajobs.com/plano-jobs</t>
@@ -3381,7 +3509,7 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>176</v>
+        <v>179</v>
       </c>
     </row>
     <row r="126">
@@ -3402,7 +3530,7 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="127">
@@ -3411,7 +3539,11 @@
           <t>RealPage</t>
         </is>
       </c>
-      <c r="B127" s="12" t="n"/>
+      <c r="B127" s="12" t="inlineStr">
+        <is>
+          <t>https://careers-realpagepms.icims.com/jobs/search?hashed=-625856947</t>
+        </is>
+      </c>
       <c r="C127" s="12" t="inlineStr">
         <is>
           <t>https://www.realpage.com/careers/</t>
@@ -3423,7 +3555,7 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="128">
@@ -3440,11 +3572,11 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129">
@@ -3453,7 +3585,11 @@
           <t>Invitation Homes</t>
         </is>
       </c>
-      <c r="B129" s="12" t="n"/>
+      <c r="B129" s="12" t="inlineStr">
+        <is>
+          <t>https://invitationhomes.wd503.myworkdayjobs.com/en-US/INVH/introduceYourself</t>
+        </is>
+      </c>
       <c r="C129" s="12" t="inlineStr">
         <is>
           <t>https://careers.invitationhomes.com/</t>
@@ -3465,7 +3601,7 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="130">
@@ -3516,7 +3652,11 @@
           <t>State Farm</t>
         </is>
       </c>
-      <c r="B132" s="12" t="n"/>
+      <c r="B132" s="12" t="inlineStr">
+        <is>
+          <t>https://events-statefarm.icims.com/jobs/search</t>
+        </is>
+      </c>
       <c r="C132" s="12" t="inlineStr">
         <is>
           <t>https://jobs.statefarm.com/</t>
@@ -3650,7 +3790,11 @@
           <t>TPG</t>
         </is>
       </c>
-      <c r="B138" s="12" t="n"/>
+      <c r="B138" s="12" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/tpgcareers</t>
+        </is>
+      </c>
       <c r="C138" s="12" t="inlineStr">
         <is>
           <t>https://www.tpg.com/careers</t>
@@ -3704,7 +3848,7 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="141">
@@ -3826,7 +3970,11 @@
           <t>Boston Consulting Group (BCG)</t>
         </is>
       </c>
-      <c r="B146" s="12" t="n"/>
+      <c r="B146" s="12" t="inlineStr">
+        <is>
+          <t>https://careers.bcg.com/global/en/</t>
+        </is>
+      </c>
       <c r="C146" s="12" t="inlineStr">
         <is>
           <t>https://careers.bcg.com/</t>
@@ -3895,7 +4043,7 @@
       </c>
       <c r="B149" s="12" t="inlineStr">
         <is>
-          <t>https://www.jobs.jpshealthnet.org/</t>
+          <t>https://jpshealthnet.csod.com/ux/ats/careersite/4/home?c=jpshealthnet&amp;cfdd[0][id]=22&amp;cfdd[0][options][0]=18</t>
         </is>
       </c>
       <c r="C149" s="12" t="inlineStr">
@@ -3909,7 +4057,7 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="150">
@@ -3943,7 +4091,11 @@
           <t>Galderma</t>
         </is>
       </c>
-      <c r="B151" s="12" t="n"/>
+      <c r="B151" s="12" t="inlineStr">
+        <is>
+          <t>https://galderma.wd3.myworkdayjobs.com/External</t>
+        </is>
+      </c>
       <c r="C151" s="12" t="inlineStr">
         <is>
           <t>https://www.galderma.com/careers</t>
@@ -3964,7 +4116,11 @@
           <t>Abbott Laboratories</t>
         </is>
       </c>
-      <c r="B152" s="12" t="n"/>
+      <c r="B152" s="12" t="inlineStr">
+        <is>
+          <t>https://abbott.wd5.myworkdayjobs.com/abbottcareers/login?utm_source=jobs.abbott/us/en&amp;utm_medium=website&amp;utm_content=widget&amp;utm_campaign=jobs.abbott-application-status</t>
+        </is>
+      </c>
       <c r="C152" s="12" t="inlineStr">
         <is>
           <t>https://www.jobs.abbott/us/en</t>
@@ -3976,7 +4132,7 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="153">
@@ -3985,7 +4141,11 @@
           <t>Verily</t>
         </is>
       </c>
-      <c r="B153" s="12" t="n"/>
+      <c r="B153" s="12" t="inlineStr">
+        <is>
+          <t>https://verily.wd1.myworkdayjobs.com/Verily_Careers</t>
+        </is>
+      </c>
       <c r="C153" s="12" t="inlineStr">
         <is>
           <t>https://verily.com/careers</t>
@@ -4006,7 +4166,11 @@
           <t>Smith+Nephew</t>
         </is>
       </c>
-      <c r="B154" s="12" t="n"/>
+      <c r="B154" s="12" t="inlineStr">
+        <is>
+          <t>https://smithnephew.wd5.myworkdayjobs.com/External</t>
+        </is>
+      </c>
       <c r="C154" s="12" t="inlineStr">
         <is>
           <t>https://www.smith-nephew.com/en/careers</t>
@@ -4073,7 +4237,11 @@
           <t>HF Sinclair</t>
         </is>
       </c>
-      <c r="B157" s="12" t="n"/>
+      <c r="B157" s="12" t="inlineStr">
+        <is>
+          <t>https://careers.hfsinclair.com/</t>
+        </is>
+      </c>
       <c r="C157" s="12" t="inlineStr">
         <is>
           <t>https://careers.hfsinclair.com/</t>
@@ -4115,7 +4283,11 @@
           <t>Vistra</t>
         </is>
       </c>
-      <c r="B159" s="12" t="n"/>
+      <c r="B159" s="12" t="inlineStr">
+        <is>
+          <t>https://vst.wd5.myworkdayjobs.com/en-US/vistra_careers</t>
+        </is>
+      </c>
       <c r="C159" s="12" t="inlineStr">
         <is>
           <t>https://vistracorp.com/careers/</t>

--- a/config/companies.xlsx
+++ b/config/companies.xlsx
@@ -449,7 +449,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4998</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="3">
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="5">
@@ -562,7 +562,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>497</v>
+        <v>500</v>
       </c>
     </row>
     <row r="8">
@@ -741,7 +741,11 @@
           <t>Intercontinental Exchange / NYSE Texas</t>
         </is>
       </c>
-      <c r="B15" s="12" t="n"/>
+      <c r="B15" s="12" t="inlineStr">
+        <is>
+          <t>https://careers.ice.com/jobs</t>
+        </is>
+      </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
           <t>https://www.ice.com/careers</t>
@@ -789,7 +793,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="17">
@@ -830,7 +834,7 @@
       </c>
       <c r="C18" s="12" t="inlineStr">
         <is>
-          <t>https://careers.t-mobile.com/</t>
+          <t>https://careers.t-mobile.com/jobs</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -900,7 +904,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6200</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="21">
@@ -941,7 +945,7 @@
       </c>
       <c r="C22" s="12" t="inlineStr">
         <is>
-          <t>https://www.boingo.com/careers/</t>
+          <t>https://app.jobzmall.com/boingo-wireless/jobs</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1162,7 +1166,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1479,7 +1483,7 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5140</v>
+        <v>1000</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -1569,7 +1573,7 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="42">
@@ -1615,7 +1619,7 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1600</v>
+        <v>1999</v>
       </c>
     </row>
     <row r="44">
@@ -1640,7 +1644,7 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="45">
@@ -1724,7 +1728,11 @@
           <t>Ericsson</t>
         </is>
       </c>
-      <c r="B48" s="12" t="n"/>
+      <c r="B48" s="12" t="inlineStr">
+        <is>
+          <t>https://jobs.ericsson.com/careers</t>
+        </is>
+      </c>
       <c r="C48" s="12" t="inlineStr">
         <is>
           <t>https://www.ericsson.com/en/careers</t>
@@ -1736,7 +1744,7 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="49">
@@ -1761,7 +1769,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>459</v>
+        <v>500</v>
       </c>
     </row>
     <row r="50">
@@ -1782,11 +1790,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="51">
@@ -1858,7 +1866,11 @@
           <t>Capgemini</t>
         </is>
       </c>
-      <c r="B54" s="12" t="n"/>
+      <c r="B54" s="12" t="inlineStr">
+        <is>
+          <t>https://www.capgemini.com/us-en/careers/join-capgemini/job-search/</t>
+        </is>
+      </c>
       <c r="C54" s="12" t="inlineStr">
         <is>
           <t>https://www.capgemini.com/careers/</t>
@@ -1891,7 +1903,7 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>180</v>
+        <v>463</v>
       </c>
     </row>
     <row r="56">
@@ -1916,7 +1928,7 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
     </row>
     <row r="57">
@@ -1958,11 +1970,11 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
     </row>
     <row r="59">
@@ -2054,7 +2066,7 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>40</v>
+        <v>250</v>
       </c>
     </row>
     <row r="63">
@@ -2079,7 +2091,7 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>425</v>
+        <v>429</v>
       </c>
     </row>
     <row r="64">
@@ -2088,7 +2100,11 @@
           <t>Palo Alto Networks</t>
         </is>
       </c>
-      <c r="B64" s="12" t="n"/>
+      <c r="B64" s="12" t="inlineStr">
+        <is>
+          <t>https://jobs.paloaltonetworks.com/en</t>
+        </is>
+      </c>
       <c r="C64" s="12" t="inlineStr">
         <is>
           <t>https://jobs.paloaltonetworks.com/</t>
@@ -2096,11 +2112,11 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>0</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="65">
@@ -2109,7 +2125,11 @@
           <t>CrowdStrike</t>
         </is>
       </c>
-      <c r="B65" s="12" t="n"/>
+      <c r="B65" s="12" t="inlineStr">
+        <is>
+          <t>https://crowdstrike.wd5.myworkdayjobs.com/crowdstrikecareers</t>
+        </is>
+      </c>
       <c r="C65" s="12" t="inlineStr">
         <is>
           <t>https://www.crowdstrike.com/en-us/careers/</t>
@@ -2117,11 +2137,11 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>0</v>
+        <v>441</v>
       </c>
     </row>
     <row r="66">
@@ -2163,7 +2183,7 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>40</v>
+        <v>362</v>
       </c>
     </row>
     <row r="68">
@@ -2188,7 +2208,7 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="69">
@@ -2200,7 +2220,7 @@
       <c r="B69" s="12" t="n"/>
       <c r="C69" s="12" t="inlineStr">
         <is>
-          <t>https://www.tylertech.com/careers</t>
+          <t>https://www.tylertech.com/careers/job-listings</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -2326,7 +2346,7 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="75">
@@ -2347,7 +2367,7 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="76">
@@ -2439,7 +2459,7 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="80">
@@ -2602,7 +2622,7 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="87">
@@ -2761,7 +2781,7 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>237</v>
+        <v>242</v>
       </c>
     </row>
     <row r="94">
@@ -2786,7 +2806,7 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>2795</v>
+        <v>2792</v>
       </c>
     </row>
     <row r="95">
@@ -2974,7 +2994,7 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="103">
@@ -3166,7 +3186,7 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="111">
@@ -3191,7 +3211,7 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>1206</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="112">
@@ -3221,7 +3241,11 @@
           <t>Texas Oncology</t>
         </is>
       </c>
-      <c r="B113" s="12" t="n"/>
+      <c r="B113" s="12" t="inlineStr">
+        <is>
+          <t>https://careers.usoncology.com/main/jobs</t>
+        </is>
+      </c>
       <c r="C113" s="12" t="inlineStr">
         <is>
           <t>https://www.texasoncology.com/careers</t>
@@ -3233,7 +3257,7 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
     </row>
     <row r="114">
@@ -3500,7 +3524,7 @@
       </c>
       <c r="C125" s="12" t="inlineStr">
         <is>
-          <t>https://www.usaajobs.com/plano-jobs</t>
+          <t>https://www.usaajobs.com/search-jobs</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -3714,7 +3738,7 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="135">
@@ -3836,7 +3860,11 @@
           <t>Intuit</t>
         </is>
       </c>
-      <c r="B140" s="12" t="n"/>
+      <c r="B140" s="12" t="inlineStr">
+        <is>
+          <t>https://jobs.intuit.com/search-jobs</t>
+        </is>
+      </c>
       <c r="C140" s="12" t="inlineStr">
         <is>
           <t>https://www.intuit.com/careers/</t>
@@ -3848,7 +3876,7 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>21</v>
+        <v>433</v>
       </c>
     </row>
     <row r="141">
@@ -3890,11 +3918,11 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
     </row>
     <row r="143">
@@ -3924,7 +3952,11 @@
           <t>Jacobs Solutions</t>
         </is>
       </c>
-      <c r="B144" s="12" t="n"/>
+      <c r="B144" s="12" t="inlineStr">
+        <is>
+          <t>https://careers.jacobs.com/</t>
+        </is>
+      </c>
       <c r="C144" s="12" t="inlineStr">
         <is>
           <t>https://www.jacobs.com/careers-jacobs</t>
@@ -3995,7 +4027,11 @@
           <t>Ryan</t>
         </is>
       </c>
-      <c r="B147" s="12" t="n"/>
+      <c r="B147" s="12" t="inlineStr">
+        <is>
+          <t>https://ryan.wd1.myworkdayjobs.com/RyanCareers</t>
+        </is>
+      </c>
       <c r="C147" s="12" t="inlineStr">
         <is>
           <t>https://ryan.com/careers/</t>
@@ -4007,7 +4043,7 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>16</v>
+        <v>116</v>
       </c>
     </row>
     <row r="148">
@@ -4132,7 +4168,7 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="153">
@@ -4173,7 +4209,7 @@
       </c>
       <c r="C154" s="12" t="inlineStr">
         <is>
-          <t>https://www.smith-nephew.com/en/careers</t>
+          <t>https://www.smith-nephew.com/en-us/careers</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -4191,7 +4227,11 @@
           <t>Energy Transfer</t>
         </is>
       </c>
-      <c r="B155" s="12" t="n"/>
+      <c r="B155" s="12" t="inlineStr">
+        <is>
+          <t>https://energytransfer.referrals.selectminds.com/</t>
+        </is>
+      </c>
       <c r="C155" s="12" t="inlineStr">
         <is>
           <t>https://energytransfer.com/careers/</t>
@@ -4203,7 +4243,7 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
     </row>
     <row r="156">
@@ -4316,11 +4356,11 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
     </row>
     <row r="161">

--- a/config/companies.xlsx
+++ b/config/companies.xlsx
@@ -671,7 +671,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="13">
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="17">
@@ -883,7 +883,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>581</v>
+        <v>583</v>
       </c>
     </row>
     <row r="20">
@@ -1030,7 +1030,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1346</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="25">
@@ -1166,7 +1166,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1226,7 +1226,11 @@
           <t>FedEx</t>
         </is>
       </c>
-      <c r="B31" s="12" t="n"/>
+      <c r="B31" s="12" t="inlineStr">
+        <is>
+          <t>https://fedex.wd1.myworkdayjobs.com/FXE-MEISA-External/job/FXE-MEISAINDBOMHQBOMHQMumbai/Data-Analyst---Senior-II_RC781471-1/apply</t>
+        </is>
+      </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
           <t>https://careers.fedex.com/</t>
@@ -1238,7 +1242,7 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>22</v>
+        <v>67</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1744,7 +1748,7 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="49">
@@ -1903,7 +1907,7 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>463</v>
+        <v>497</v>
       </c>
     </row>
     <row r="56">
@@ -2162,7 +2166,7 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="67">
@@ -2208,7 +2212,7 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="69">
@@ -2388,7 +2392,7 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="77">
@@ -2413,7 +2417,7 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="78">
@@ -2484,7 +2488,7 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="81">
@@ -2622,7 +2626,7 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="87">
@@ -2781,7 +2785,7 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="94">
@@ -2852,7 +2856,7 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="97">
@@ -2994,7 +2998,7 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="103">
@@ -3061,7 +3065,7 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="106">
@@ -3086,7 +3090,7 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="107">
@@ -3111,7 +3115,7 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="108">
@@ -3136,7 +3140,7 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="109">
@@ -3186,7 +3190,7 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="111">
@@ -3328,7 +3332,7 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>2101</v>
+        <v>2115</v>
       </c>
     </row>
     <row r="117">
@@ -3420,7 +3424,7 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="121">
@@ -3487,7 +3491,7 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="124">
@@ -3579,7 +3583,7 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="128">
@@ -3596,11 +3600,11 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
     </row>
     <row r="129">
@@ -3713,7 +3717,7 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
     </row>
     <row r="134">
@@ -4093,7 +4097,7 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>186</v>
+        <v>189</v>
       </c>
     </row>
     <row r="150">

--- a/config/companies.xlsx
+++ b/config/companies.xlsx
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>20</v>
+        <v>220</v>
       </c>
     </row>
     <row r="6">
@@ -671,7 +671,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="13">
@@ -757,7 +757,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>10</v>
+        <v>110</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>487</v>
+        <v>483</v>
       </c>
     </row>
     <row r="17">
@@ -1030,7 +1030,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1341</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="25">
@@ -1166,7 +1166,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>10</v>
+        <v>110</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1000</v>
+        <v>5150</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -1552,7 +1552,7 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="41">
@@ -1598,7 +1598,7 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
     </row>
     <row r="43">
@@ -1648,7 +1648,7 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>30</v>
+        <v>311</v>
       </c>
     </row>
     <row r="45">
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>580</v>
+        <v>575</v>
       </c>
     </row>
     <row r="48">
@@ -1798,7 +1798,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>10</v>
+        <v>109</v>
       </c>
     </row>
     <row r="51">
@@ -1819,7 +1819,7 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>21</v>
+        <v>218</v>
       </c>
     </row>
     <row r="52">
@@ -1907,7 +1907,7 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>497</v>
+        <v>500</v>
       </c>
     </row>
     <row r="56">
@@ -1953,11 +1953,11 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>477</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -2045,7 +2045,7 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>10</v>
+        <v>102</v>
       </c>
     </row>
     <row r="62">
@@ -2095,7 +2095,7 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>429</v>
+        <v>423</v>
       </c>
     </row>
     <row r="64">
@@ -2120,7 +2120,7 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1307</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="65">
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="66">
@@ -2187,7 +2187,7 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="68">
@@ -2212,7 +2212,7 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>466</v>
+        <v>462</v>
       </c>
     </row>
     <row r="69">
@@ -2308,7 +2308,7 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="73">
@@ -2329,7 +2329,7 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>10</v>
+        <v>72</v>
       </c>
     </row>
     <row r="74">
@@ -2350,7 +2350,7 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>17</v>
+        <v>140</v>
       </c>
     </row>
     <row r="75">
@@ -2371,7 +2371,7 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="76">
@@ -2463,7 +2463,7 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="80">
@@ -2605,7 +2605,7 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1942</v>
+        <v>1930</v>
       </c>
     </row>
     <row r="86">
@@ -2626,7 +2626,7 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>32</v>
+        <v>126</v>
       </c>
     </row>
     <row r="87">
@@ -2714,7 +2714,7 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>188</v>
+        <v>184</v>
       </c>
     </row>
     <row r="91">
@@ -2835,7 +2835,7 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>3275</v>
+        <v>3274</v>
       </c>
     </row>
     <row r="96">
@@ -2877,7 +2877,7 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>10</v>
+        <v>107</v>
       </c>
     </row>
     <row r="98">
@@ -2998,7 +2998,7 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="103">
@@ -3065,7 +3065,7 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="106">
@@ -3090,7 +3090,7 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>323</v>
+        <v>309</v>
       </c>
     </row>
     <row r="107">
@@ -3115,7 +3115,7 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="108">
@@ -3140,7 +3140,7 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="109">
@@ -3190,7 +3190,7 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
     <row r="111">
@@ -3215,7 +3215,7 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>1197</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="112">
@@ -3261,7 +3261,7 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>11</v>
+        <v>106</v>
       </c>
     </row>
     <row r="114">
@@ -3332,7 +3332,7 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>2115</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="117">
@@ -3374,7 +3374,7 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="119">
@@ -3399,7 +3399,7 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>19</v>
+        <v>81</v>
       </c>
     </row>
     <row r="120">
@@ -3424,7 +3424,7 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="121">
@@ -3470,7 +3470,7 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>191</v>
+        <v>187</v>
       </c>
     </row>
     <row r="123">
@@ -3512,7 +3512,7 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>475</v>
+        <v>468</v>
       </c>
     </row>
     <row r="125">
@@ -3537,7 +3537,7 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>179</v>
+        <v>175</v>
       </c>
     </row>
     <row r="126">
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="127">
@@ -3604,7 +3604,7 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>23</v>
+        <v>160</v>
       </c>
     </row>
     <row r="129">
@@ -3629,7 +3629,7 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="130">
@@ -3788,7 +3788,7 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="137">
@@ -3880,7 +3880,7 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="141">
@@ -3905,7 +3905,7 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="142">
@@ -3972,7 +3972,7 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="145">
@@ -4097,7 +4097,7 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="150">
@@ -4147,7 +4147,7 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="152">
@@ -4222,7 +4222,7 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>353</v>
+        <v>350</v>
       </c>
     </row>
     <row r="155">

--- a/config/companies.xlsx
+++ b/config/companies.xlsx
@@ -432,7 +432,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>7336</v>
+        <v>7301</v>
       </c>
     </row>
     <row r="3" ht="27.75" customHeight="1">
@@ -453,7 +453,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1844</v>
+        <v>1841</v>
       </c>
     </row>
     <row r="4" ht="14.25" customHeight="1">
@@ -474,7 +474,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2089</v>
+        <v>2084</v>
       </c>
     </row>
     <row r="5" ht="14.25" customHeight="1">
@@ -524,7 +524,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1345</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="7" ht="27.75" customHeight="1">
@@ -545,7 +545,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1784</v>
+        <v>1704</v>
       </c>
     </row>
     <row r="8" ht="27.75" customHeight="1">
@@ -566,7 +566,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>532</v>
+        <v>547</v>
       </c>
     </row>
     <row r="9" ht="27" customHeight="1">
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>50</v>
+        <v>222</v>
       </c>
     </row>
     <row r="10" ht="27" customHeight="1">
@@ -740,7 +740,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>110</v>
+        <v>91</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>477</v>
+        <v>468</v>
       </c>
     </row>
     <row r="17" ht="14.25" customHeight="1">
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1999</v>
+        <v>2000</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -866,7 +866,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>598</v>
+        <v>597</v>
       </c>
     </row>
     <row r="20" ht="14.25" customHeight="1">
@@ -1013,7 +1013,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1343</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="25" ht="27.75" customHeight="1">
@@ -1034,7 +1034,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>663</v>
+        <v>639</v>
       </c>
     </row>
     <row r="26" ht="14.25" customHeight="1">
@@ -1059,7 +1059,7 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2000</v>
+        <v>4330</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>140</v>
+        <v>678</v>
       </c>
     </row>
     <row r="34" ht="14.25" customHeight="1">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -1445,7 +1445,7 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="38" ht="14.25" customHeight="1">
@@ -1470,7 +1470,7 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5226</v>
+        <v>5222</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="41" ht="14.25" customHeight="1">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1799</v>
+        <v>2040</v>
       </c>
     </row>
     <row r="44" ht="14.25" customHeight="1">
@@ -1631,7 +1631,7 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>303</v>
+        <v>280</v>
       </c>
     </row>
     <row r="45" ht="27" customHeight="1">
@@ -1656,7 +1656,7 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1530</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="46" ht="14.25" customHeight="1">
@@ -1681,7 +1681,7 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1195</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="47" ht="14.25" customHeight="1">
@@ -1706,7 +1706,7 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>596</v>
+        <v>595</v>
       </c>
     </row>
     <row r="48" ht="14.25" customHeight="1">
@@ -1756,7 +1756,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>671</v>
+        <v>676</v>
       </c>
     </row>
     <row r="50" ht="14.25" customHeight="1">
@@ -1777,11 +1777,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51" ht="14.25" customHeight="1">
@@ -1806,7 +1806,7 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>844</v>
+        <v>848</v>
       </c>
     </row>
     <row r="52" ht="14.25" customHeight="1">
@@ -1848,7 +1848,7 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>126</v>
+        <v>122</v>
       </c>
     </row>
     <row r="54" ht="27" customHeight="1">
@@ -1894,7 +1894,7 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1130</v>
+        <v>1760</v>
       </c>
     </row>
     <row r="56" ht="14.25" customHeight="1">
@@ -1919,7 +1919,7 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>10</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="57" ht="14.25" customHeight="1">
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>7893</v>
+        <v>7911</v>
       </c>
     </row>
     <row r="59" ht="14.25" customHeight="1">
@@ -2011,11 +2011,11 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="61" ht="14.25" customHeight="1">
@@ -2036,7 +2036,7 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="62" ht="14.25" customHeight="1">
@@ -2061,7 +2061,7 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1080</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="63" ht="27" customHeight="1">
@@ -2086,7 +2086,7 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>430</v>
+        <v>435</v>
       </c>
     </row>
     <row r="64" ht="14.25" customHeight="1">
@@ -2111,7 +2111,7 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1307</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="65" ht="27.75" customHeight="1">
@@ -2157,7 +2157,7 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="67" ht="14.25" customHeight="1">
@@ -2178,7 +2178,7 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="68" ht="27" customHeight="1">
@@ -2203,7 +2203,7 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="69" ht="14.25" customHeight="1">
@@ -2224,7 +2224,7 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70" ht="14.25" customHeight="1">
@@ -2249,7 +2249,7 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="71" ht="14.25" customHeight="1">
@@ -2320,7 +2320,7 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>84</v>
+        <v>70</v>
       </c>
     </row>
     <row r="74" ht="14.25" customHeight="1">
@@ -2341,7 +2341,7 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="75" ht="14.25" customHeight="1">
@@ -2362,7 +2362,7 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="76" ht="27" customHeight="1">
@@ -2383,7 +2383,7 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>475</v>
+        <v>472</v>
       </c>
     </row>
     <row r="77" ht="14.25" customHeight="1">
@@ -2408,7 +2408,7 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="78" ht="14.25" customHeight="1">
@@ -2504,7 +2504,7 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="82" ht="14.25" customHeight="1">
@@ -2529,7 +2529,7 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>2000</v>
+        <v>4330</v>
       </c>
     </row>
     <row r="83" ht="14.25" customHeight="1">
@@ -2575,7 +2575,7 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1858</v>
+        <v>1845</v>
       </c>
     </row>
     <row r="85" ht="14.25" customHeight="1">
@@ -2600,7 +2600,7 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1949</v>
+        <v>1943</v>
       </c>
     </row>
     <row r="86" ht="14.25" customHeight="1">
@@ -2621,7 +2621,7 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>131</v>
+        <v>35</v>
       </c>
     </row>
     <row r="87" ht="27.75" customHeight="1">
@@ -2709,7 +2709,7 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="91" ht="14.25" customHeight="1">
@@ -2755,7 +2755,7 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>692</v>
+        <v>693</v>
       </c>
     </row>
     <row r="93" ht="27" customHeight="1">
@@ -2805,7 +2805,7 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>2843</v>
+        <v>2840</v>
       </c>
     </row>
     <row r="95" ht="14.25" customHeight="1">
@@ -2830,7 +2830,7 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>3297</v>
+        <v>3333</v>
       </c>
     </row>
     <row r="96" ht="27" customHeight="1">
@@ -2851,7 +2851,7 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>475</v>
+        <v>472</v>
       </c>
     </row>
     <row r="97" ht="14.25" customHeight="1">
@@ -2897,7 +2897,7 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>961</v>
+        <v>953</v>
       </c>
     </row>
     <row r="99" ht="14.25" customHeight="1">
@@ -2914,11 +2914,11 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="100" ht="14.25" customHeight="1">
@@ -2943,7 +2943,7 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>2000</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="101" ht="14.25" customHeight="1">
@@ -2968,7 +2968,7 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>2000</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="102" ht="27" customHeight="1">
@@ -2993,7 +2993,7 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="103" ht="14.25" customHeight="1">
@@ -3060,7 +3060,7 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="106" ht="27" customHeight="1">
@@ -3085,7 +3085,7 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>305</v>
+        <v>301</v>
       </c>
     </row>
     <row r="107" ht="14.25" customHeight="1">
@@ -3110,7 +3110,7 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="108" ht="14.25" customHeight="1">
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="109" ht="14.25" customHeight="1">
@@ -3160,7 +3160,7 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>2000</v>
+        <v>2218</v>
       </c>
     </row>
     <row r="110" ht="27" customHeight="1">
@@ -3185,7 +3185,7 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="111" ht="14.25" customHeight="1">
@@ -3256,7 +3256,7 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>100</v>
+        <v>217</v>
       </c>
     </row>
     <row r="114" ht="27" customHeight="1">
@@ -3327,7 +3327,7 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>2140</v>
+        <v>2139</v>
       </c>
     </row>
     <row r="117" ht="14.25" customHeight="1">
@@ -3348,7 +3348,7 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>3706</v>
+        <v>3708</v>
       </c>
     </row>
     <row r="118" ht="14.25" customHeight="1">
@@ -3390,11 +3390,11 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120" ht="27" customHeight="1">
@@ -3465,7 +3465,7 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="123" ht="14.25" customHeight="1">
@@ -3532,7 +3532,7 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>169</v>
+        <v>164</v>
       </c>
     </row>
     <row r="126" ht="14.25" customHeight="1">
@@ -3578,7 +3578,7 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="128" ht="14.25" customHeight="1">
@@ -3599,7 +3599,7 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>398</v>
+        <v>420</v>
       </c>
     </row>
     <row r="129" ht="27" customHeight="1">
@@ -3737,7 +3737,7 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="135" ht="27.75" customHeight="1">
@@ -3854,7 +3854,7 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>1998</v>
+        <v>1993</v>
       </c>
     </row>
     <row r="140" ht="14.25" customHeight="1">
@@ -3879,7 +3879,7 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>444</v>
+        <v>449</v>
       </c>
     </row>
     <row r="141" ht="14.25" customHeight="1">
@@ -4021,7 +4021,7 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>899</v>
+        <v>892</v>
       </c>
     </row>
     <row r="147" ht="14.25" customHeight="1">
@@ -4067,11 +4067,11 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="149" ht="27" customHeight="1">
@@ -4171,7 +4171,7 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>2000</v>
+        <v>1978</v>
       </c>
     </row>
     <row r="153" ht="14.25" customHeight="1">
@@ -4246,7 +4246,7 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
     </row>
     <row r="156" ht="14.25" customHeight="1">
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="157" ht="14.25" customHeight="1">
@@ -4296,7 +4296,7 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>10</v>
+        <v>98</v>
       </c>
     </row>
     <row r="158" ht="14.25" customHeight="1">
@@ -4367,7 +4367,7 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>189</v>
+        <v>184</v>
       </c>
     </row>
     <row r="161" ht="14.25" customHeight="1">
@@ -4388,7 +4388,7 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>4950</v>
+        <v>4947</v>
       </c>
     </row>
     <row r="162" ht="14.25" customHeight="1">
@@ -4438,7 +4438,7 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>1647</v>
+        <v>1652</v>
       </c>
     </row>
     <row r="164" ht="14.25" customHeight="1">
@@ -4463,7 +4463,7 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>1320</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="165" ht="14.25" customHeight="1">
@@ -4488,7 +4488,7 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>309</v>
+        <v>294</v>
       </c>
     </row>
     <row r="166" ht="14.25" customHeight="1">
@@ -4508,7 +4508,7 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="H166" t="inlineStr">
         <is>
@@ -4558,7 +4558,7 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>161</v>
+        <v>131</v>
       </c>
     </row>
     <row r="169">
@@ -4698,7 +4698,7 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="175">
@@ -4748,7 +4748,7 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="177">
@@ -4838,7 +4838,7 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="H180" t="inlineStr">
         <is>

--- a/config/companies.xlsx
+++ b/config/companies.xlsx
@@ -432,7 +432,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>7301</v>
+        <v>7287</v>
       </c>
     </row>
     <row r="3" ht="27.75" customHeight="1">
@@ -453,7 +453,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1841</v>
+        <v>1842</v>
       </c>
     </row>
     <row r="4" ht="14.25" customHeight="1">
@@ -474,7 +474,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2084</v>
+        <v>2081</v>
       </c>
     </row>
     <row r="5" ht="14.25" customHeight="1">
@@ -499,7 +499,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220</v>
+        <v>820</v>
       </c>
     </row>
     <row r="6" ht="27" customHeight="1">
@@ -524,7 +524,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1348</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="7" ht="27.75" customHeight="1">
@@ -545,7 +545,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1704</v>
+        <v>1706</v>
       </c>
     </row>
     <row r="8" ht="27.75" customHeight="1">
@@ -566,7 +566,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>547</v>
+        <v>520</v>
       </c>
     </row>
     <row r="9" ht="27" customHeight="1">
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="10" ht="27" customHeight="1">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="12" ht="14.25" customHeight="1">
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="13" ht="27" customHeight="1">
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="15" ht="27.75" customHeight="1">
@@ -740,7 +740,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>91</v>
+        <v>40</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>468</v>
+        <v>479</v>
       </c>
     </row>
     <row r="17" ht="14.25" customHeight="1">
@@ -785,23 +785,24 @@
           <t>FM</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>https://www.careersatfm.com/search-jobs</t>
-        </is>
-      </c>
+      <c r="B17" s="2" t="n"/>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>https://jobs.fm.com/</t>
+          <t>https://careers.fm.com/</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>43</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>2026-08-26: replaced dead ATS URL (careersatfm.com does not resolve) and dead live page (jobs.fm.com refuses connections) with careers.fm.com, verified returning 44 jobs.</t>
+        </is>
       </c>
     </row>
     <row r="18" ht="27" customHeight="1">
@@ -866,7 +867,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>597</v>
+        <v>598</v>
       </c>
     </row>
     <row r="20" ht="14.25" customHeight="1">
@@ -887,7 +888,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>10000</v>
+        <v>9996</v>
       </c>
     </row>
     <row r="21" ht="14.25" customHeight="1">
@@ -1013,7 +1014,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1340</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="25" ht="27.75" customHeight="1">
@@ -1034,7 +1035,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>639</v>
+        <v>621</v>
       </c>
     </row>
     <row r="26" ht="14.25" customHeight="1">
@@ -1059,7 +1060,7 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4330</v>
+        <v>4400</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1124,7 +1125,7 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="29" ht="14.25" customHeight="1">
@@ -1225,7 +1226,7 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1301,7 +1302,7 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>678</v>
+        <v>684</v>
       </c>
     </row>
     <row r="34" ht="14.25" customHeight="1">
@@ -1322,7 +1323,7 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -1362,7 +1363,7 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -1402,7 +1403,7 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -1470,7 +1471,7 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5222</v>
+        <v>5213</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -1535,7 +1536,7 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="41" ht="14.25" customHeight="1">
@@ -1560,7 +1561,7 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>335</v>
+        <v>339</v>
       </c>
     </row>
     <row r="42" ht="27.75" customHeight="1">
@@ -1581,7 +1582,7 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
     </row>
     <row r="43" ht="41.25" customHeight="1">
@@ -1606,7 +1607,7 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2040</v>
+        <v>2032</v>
       </c>
     </row>
     <row r="44" ht="14.25" customHeight="1">
@@ -1631,7 +1632,7 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>280</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="45" ht="27" customHeight="1">
@@ -1656,7 +1657,7 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1533</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="46" ht="14.25" customHeight="1">
@@ -1681,7 +1682,7 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1189</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="47" ht="14.25" customHeight="1">
@@ -1706,7 +1707,7 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>595</v>
+        <v>603</v>
       </c>
     </row>
     <row r="48" ht="14.25" customHeight="1">
@@ -1756,7 +1757,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>676</v>
+        <v>683</v>
       </c>
     </row>
     <row r="50" ht="14.25" customHeight="1">
@@ -1806,7 +1807,7 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>848</v>
+        <v>842</v>
       </c>
     </row>
     <row r="52" ht="14.25" customHeight="1">
@@ -1848,7 +1849,7 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>122</v>
+        <v>306</v>
       </c>
     </row>
     <row r="54" ht="27" customHeight="1">
@@ -1894,7 +1895,7 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1760</v>
+        <v>1965</v>
       </c>
     </row>
     <row r="56" ht="14.25" customHeight="1">
@@ -1919,7 +1920,7 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1094</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="57" ht="14.25" customHeight="1">
@@ -1969,7 +1970,7 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>7911</v>
+        <v>7953</v>
       </c>
     </row>
     <row r="59" ht="14.25" customHeight="1">
@@ -2011,11 +2012,11 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61" ht="14.25" customHeight="1">
@@ -2036,7 +2037,7 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>110</v>
+        <v>386</v>
       </c>
     </row>
     <row r="62" ht="14.25" customHeight="1">
@@ -2061,7 +2062,7 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1090</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="63" ht="27" customHeight="1">
@@ -2086,7 +2087,7 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>435</v>
+        <v>443</v>
       </c>
     </row>
     <row r="64" ht="14.25" customHeight="1">
@@ -2111,7 +2112,7 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1308</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="65" ht="27.75" customHeight="1">
@@ -2136,7 +2137,7 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="66" ht="14.25" customHeight="1">
@@ -2157,7 +2158,7 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>548</v>
+        <v>546</v>
       </c>
     </row>
     <row r="67" ht="14.25" customHeight="1">
@@ -2178,7 +2179,7 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="68" ht="27" customHeight="1">
@@ -2203,7 +2204,7 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>469</v>
+        <v>473</v>
       </c>
     </row>
     <row r="69" ht="14.25" customHeight="1">
@@ -2224,7 +2225,7 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="70" ht="14.25" customHeight="1">
@@ -2274,7 +2275,7 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="72" ht="14.25" customHeight="1">
@@ -2299,7 +2300,7 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="73" ht="14.25" customHeight="1">
@@ -2320,7 +2321,7 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>70</v>
+        <v>37</v>
       </c>
     </row>
     <row r="74" ht="14.25" customHeight="1">
@@ -2341,7 +2342,7 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>134</v>
+        <v>4</v>
       </c>
     </row>
     <row r="75" ht="14.25" customHeight="1">
@@ -2383,7 +2384,7 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>472</v>
+        <v>470</v>
       </c>
     </row>
     <row r="77" ht="14.25" customHeight="1">
@@ -2454,7 +2455,7 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="80" ht="27.75" customHeight="1">
@@ -2529,7 +2530,7 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>4330</v>
+        <v>4400</v>
       </c>
     </row>
     <row r="83" ht="14.25" customHeight="1">
@@ -2575,7 +2576,7 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1845</v>
+        <v>1854</v>
       </c>
     </row>
     <row r="85" ht="14.25" customHeight="1">
@@ -2600,7 +2601,7 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1943</v>
+        <v>1904</v>
       </c>
     </row>
     <row r="86" ht="14.25" customHeight="1">
@@ -2621,7 +2622,7 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="87" ht="27.75" customHeight="1">
@@ -2709,7 +2710,7 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="91" ht="14.25" customHeight="1">
@@ -2805,7 +2806,7 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>2840</v>
+        <v>2841</v>
       </c>
     </row>
     <row r="95" ht="14.25" customHeight="1">
@@ -2851,7 +2852,7 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>472</v>
+        <v>470</v>
       </c>
     </row>
     <row r="97" ht="14.25" customHeight="1">
@@ -2872,7 +2873,7 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>110</v>
+        <v>180</v>
       </c>
     </row>
     <row r="98" ht="14.25" customHeight="1">
@@ -2897,7 +2898,7 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>953</v>
+        <v>959</v>
       </c>
     </row>
     <row r="99" ht="14.25" customHeight="1">
@@ -2993,7 +2994,7 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="103" ht="14.25" customHeight="1">
@@ -3060,7 +3061,7 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>570</v>
+        <v>568</v>
       </c>
     </row>
     <row r="106" ht="27" customHeight="1">
@@ -3085,7 +3086,7 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>301</v>
+        <v>306</v>
       </c>
     </row>
     <row r="107" ht="14.25" customHeight="1">
@@ -3110,7 +3111,7 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>218</v>
+        <v>215</v>
       </c>
     </row>
     <row r="108" ht="14.25" customHeight="1">
@@ -3135,7 +3136,7 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>218</v>
+        <v>215</v>
       </c>
     </row>
     <row r="109" ht="14.25" customHeight="1">
@@ -3160,7 +3161,7 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>2218</v>
+        <v>2213</v>
       </c>
     </row>
     <row r="110" ht="27" customHeight="1">
@@ -3185,7 +3186,7 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="111" ht="14.25" customHeight="1">
@@ -3256,7 +3257,7 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>217</v>
+        <v>237</v>
       </c>
     </row>
     <row r="114" ht="27" customHeight="1">
@@ -3281,7 +3282,7 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="115" ht="14.25" customHeight="1">
@@ -3327,7 +3328,7 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>2139</v>
+        <v>2141</v>
       </c>
     </row>
     <row r="117" ht="14.25" customHeight="1">
@@ -3365,11 +3366,11 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119" ht="14.25" customHeight="1">
@@ -3444,7 +3445,7 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="122" ht="14.25" customHeight="1">
@@ -3465,7 +3466,7 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>193</v>
+        <v>190</v>
       </c>
     </row>
     <row r="123" ht="14.25" customHeight="1">
@@ -3507,7 +3508,7 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>448</v>
+        <v>444</v>
       </c>
     </row>
     <row r="125" ht="14.25" customHeight="1">
@@ -3532,7 +3533,7 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>164</v>
+        <v>161</v>
       </c>
     </row>
     <row r="126" ht="14.25" customHeight="1">
@@ -3578,7 +3579,7 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="128" ht="14.25" customHeight="1">
@@ -3595,11 +3596,11 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>420</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129" ht="27" customHeight="1">
@@ -3712,7 +3713,7 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
     </row>
     <row r="134" ht="54.75" customHeight="1">
@@ -3762,7 +3763,7 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="136" ht="14.25" customHeight="1">
@@ -3808,7 +3809,7 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="138" ht="14.25" customHeight="1">
@@ -3879,7 +3880,7 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="141" ht="14.25" customHeight="1">
@@ -3904,7 +3905,7 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="142" ht="14.25" customHeight="1">
@@ -3971,7 +3972,7 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>220</v>
+        <v>720</v>
       </c>
     </row>
     <row r="145" ht="14.25" customHeight="1">
@@ -4021,7 +4022,7 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>892</v>
+        <v>891</v>
       </c>
     </row>
     <row r="147" ht="14.25" customHeight="1">
@@ -4046,7 +4047,7 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="148" ht="14.25" customHeight="1">
@@ -4096,7 +4097,7 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="150" ht="27" customHeight="1">
@@ -4146,7 +4147,7 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="152" ht="41.25" customHeight="1">
@@ -4171,7 +4172,7 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>1978</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="153" ht="14.25" customHeight="1">
@@ -4221,7 +4222,7 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>354</v>
+        <v>358</v>
       </c>
     </row>
     <row r="155" ht="14.25" customHeight="1">
@@ -4246,7 +4247,7 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
     </row>
     <row r="156" ht="14.25" customHeight="1">
@@ -4342,7 +4343,7 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="160" ht="14.25" customHeight="1">
@@ -4367,7 +4368,7 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="161" ht="14.25" customHeight="1">
@@ -4388,7 +4389,7 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>4947</v>
+        <v>4955</v>
       </c>
     </row>
     <row r="162" ht="14.25" customHeight="1">
@@ -4438,7 +4439,7 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>1652</v>
+        <v>1642</v>
       </c>
     </row>
     <row r="164" ht="14.25" customHeight="1">
@@ -4463,7 +4464,7 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>1319</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="165" ht="14.25" customHeight="1">
@@ -4488,7 +4489,7 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>294</v>
+        <v>290</v>
       </c>
     </row>
     <row r="166" ht="14.25" customHeight="1">
@@ -4508,7 +4509,7 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>101</v>
+        <v>394</v>
       </c>
       <c r="H166" t="inlineStr">
         <is>
@@ -4538,7 +4539,7 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>222</v>
+        <v>219</v>
       </c>
     </row>
     <row r="168">
@@ -4558,7 +4559,7 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>131</v>
+        <v>161</v>
       </c>
     </row>
     <row r="169">
@@ -4583,7 +4584,7 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>127</v>
+        <v>122</v>
       </c>
     </row>
     <row r="170">
@@ -4793,7 +4794,7 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>107</v>
+        <v>404</v>
       </c>
     </row>
     <row r="179">
@@ -4818,7 +4819,7 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="180">

--- a/config/companies.xlsx
+++ b/config/companies.xlsx
@@ -432,7 +432,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>7287</v>
+        <v>7303</v>
       </c>
     </row>
     <row r="3" ht="27.75" customHeight="1">
@@ -453,7 +453,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1842</v>
+        <v>1843</v>
       </c>
     </row>
     <row r="4" ht="14.25" customHeight="1">
@@ -474,7 +474,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>2103</v>
       </c>
     </row>
     <row r="5" ht="14.25" customHeight="1">
@@ -499,7 +499,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>820</v>
+        <v>800</v>
       </c>
     </row>
     <row r="6" ht="27" customHeight="1">
@@ -524,7 +524,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1337</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="7" ht="27.75" customHeight="1">
@@ -545,7 +545,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1706</v>
+        <v>1799</v>
       </c>
     </row>
     <row r="8" ht="27.75" customHeight="1">
@@ -566,7 +566,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>520</v>
+        <v>528</v>
       </c>
     </row>
     <row r="9" ht="27" customHeight="1">
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="10" ht="27" customHeight="1">
@@ -612,7 +612,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="11" ht="14.25" customHeight="1">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>345</v>
+        <v>351</v>
       </c>
     </row>
     <row r="12" ht="14.25" customHeight="1">
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="13" ht="27" customHeight="1">
@@ -671,11 +671,11 @@
       <c r="C13" s="2" t="n"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="15" ht="27.75" customHeight="1">
@@ -740,7 +740,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>40</v>
+        <v>89</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>479</v>
+        <v>494</v>
       </c>
     </row>
     <row r="17" ht="14.25" customHeight="1">
@@ -797,7 +797,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>598</v>
+        <v>596</v>
       </c>
     </row>
     <row r="20" ht="14.25" customHeight="1">
@@ -888,7 +888,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>9996</v>
+        <v>9999</v>
       </c>
     </row>
     <row r="21" ht="14.25" customHeight="1">
@@ -1014,7 +1014,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1345</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="25" ht="27.75" customHeight="1">
@@ -1035,7 +1035,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>621</v>
+        <v>671</v>
       </c>
     </row>
     <row r="26" ht="14.25" customHeight="1">
@@ -1125,7 +1125,7 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="29" ht="14.25" customHeight="1">
@@ -1150,7 +1150,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>684</v>
+        <v>671</v>
       </c>
     </row>
     <row r="34" ht="14.25" customHeight="1">
@@ -1323,7 +1323,7 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>130</v>
+        <v>393</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -1403,7 +1403,7 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -1446,7 +1446,7 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="38" ht="14.25" customHeight="1">
@@ -1471,7 +1471,7 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5213</v>
+        <v>5199</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5148</v>
+        <v>5150</v>
       </c>
     </row>
     <row r="40" ht="14.25" customHeight="1">
@@ -1561,7 +1561,7 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>339</v>
+        <v>343</v>
       </c>
     </row>
     <row r="42" ht="27.75" customHeight="1">
@@ -1607,7 +1607,7 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2032</v>
+        <v>2050</v>
       </c>
     </row>
     <row r="44" ht="14.25" customHeight="1">
@@ -1632,7 +1632,7 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1016</v>
+        <v>973</v>
       </c>
     </row>
     <row r="45" ht="27" customHeight="1">
@@ -1657,7 +1657,7 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1538</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="46" ht="14.25" customHeight="1">
@@ -1682,7 +1682,7 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1192</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="47" ht="14.25" customHeight="1">
@@ -1707,7 +1707,7 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="48" ht="14.25" customHeight="1">
@@ -1757,7 +1757,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>683</v>
+        <v>690</v>
       </c>
     </row>
     <row r="50" ht="14.25" customHeight="1">
@@ -1807,7 +1807,7 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>842</v>
+        <v>847</v>
       </c>
     </row>
     <row r="52" ht="14.25" customHeight="1">
@@ -1849,7 +1849,7 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>306</v>
+        <v>256</v>
       </c>
     </row>
     <row r="54" ht="27" customHeight="1">
@@ -1895,7 +1895,7 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1965</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="56" ht="14.25" customHeight="1">
@@ -1920,7 +1920,7 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1090</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="57" ht="14.25" customHeight="1">
@@ -1929,23 +1929,24 @@
           <t>PwC</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>https://jobs.us.pwc.com/</t>
-        </is>
-      </c>
+      <c r="B57" s="2" t="n"/>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>https://jobs.us.pwc.com/</t>
+          <t>https://www.pwc.com/us/en/careers.html</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>0</v>
+        <v>639</v>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>2026-08-26: jobs.us.pwc.com fails TLS verification and 404s when that is ignored - the host is gone. Verified 43 jobs on the main careers page.</t>
+        </is>
       </c>
     </row>
     <row r="58" ht="14.25" customHeight="1">
@@ -1970,7 +1971,7 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>7953</v>
+        <v>7965</v>
       </c>
     </row>
     <row r="59" ht="14.25" customHeight="1">
@@ -2012,11 +2013,11 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="61" ht="14.25" customHeight="1">
@@ -2037,7 +2038,7 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>386</v>
+        <v>391</v>
       </c>
     </row>
     <row r="62" ht="14.25" customHeight="1">
@@ -2062,7 +2063,7 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1095</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="63" ht="27" customHeight="1">
@@ -2087,7 +2088,7 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="64" ht="14.25" customHeight="1">
@@ -2112,7 +2113,7 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1312</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="65" ht="27.75" customHeight="1">
@@ -2137,7 +2138,7 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>453</v>
+        <v>445</v>
       </c>
     </row>
     <row r="66" ht="14.25" customHeight="1">
@@ -2158,7 +2159,7 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>546</v>
+        <v>550</v>
       </c>
     </row>
     <row r="67" ht="14.25" customHeight="1">
@@ -2179,7 +2180,7 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="68" ht="27" customHeight="1">
@@ -2204,7 +2205,7 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="69" ht="14.25" customHeight="1">
@@ -2250,7 +2251,7 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="71" ht="14.25" customHeight="1">
@@ -2275,7 +2276,7 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="72" ht="14.25" customHeight="1">
@@ -2300,7 +2301,7 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="73" ht="14.25" customHeight="1">
@@ -2321,7 +2322,7 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>37</v>
+        <v>72</v>
       </c>
     </row>
     <row r="74" ht="14.25" customHeight="1">
@@ -2342,7 +2343,7 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>4</v>
+        <v>152</v>
       </c>
     </row>
     <row r="75" ht="14.25" customHeight="1">
@@ -2363,7 +2364,7 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>113</v>
+        <v>116</v>
       </c>
     </row>
     <row r="76" ht="27" customHeight="1">
@@ -2384,7 +2385,7 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>470</v>
+        <v>468</v>
       </c>
     </row>
     <row r="77" ht="14.25" customHeight="1">
@@ -2409,7 +2410,7 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="78" ht="14.25" customHeight="1">
@@ -2455,7 +2456,7 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="80" ht="27.75" customHeight="1">
@@ -2480,7 +2481,7 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="81" ht="14.25" customHeight="1">
@@ -2505,7 +2506,7 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="82" ht="14.25" customHeight="1">
@@ -2542,16 +2543,21 @@
       <c r="B83" s="2" t="n"/>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>https://www.lockheedmartinjobs.com/</t>
+          <t>https://lockheedmartin.eightfold.ai/careers</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>0</v>
+        <v>20</v>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>2026-08-26: lockheedmartinjobs.com is a dead redirect stub (404 via lockheedmartin.com). Real board is the Eightfold tenant; its API answers 403 so the browser route is used. Verified 20 jobs.</t>
+        </is>
       </c>
     </row>
     <row r="84" ht="14.25" customHeight="1">
@@ -2576,7 +2582,7 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1854</v>
+        <v>1860</v>
       </c>
     </row>
     <row r="85" ht="14.25" customHeight="1">
@@ -2601,7 +2607,7 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1904</v>
+        <v>1920</v>
       </c>
     </row>
     <row r="86" ht="14.25" customHeight="1">
@@ -2622,7 +2628,7 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="87" ht="27.75" customHeight="1">
@@ -2636,14 +2642,23 @@
           <t>https://texashealth.taleo.net/careersection/ex3/moresearch.ftl</t>
         </is>
       </c>
-      <c r="C87" s="2" t="n"/>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.texashealth.org/</t>
+        </is>
+      </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>0</v>
+        <v>197</v>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>2026-08-26: the Taleo moresearch.ftl entry point returns 0 rows. The branded portal renders the same Taleo data and verified 391 jobs.</t>
+        </is>
       </c>
     </row>
     <row r="88" ht="14.25" customHeight="1">
@@ -2710,7 +2725,7 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>181</v>
+        <v>186</v>
       </c>
     </row>
     <row r="91" ht="14.25" customHeight="1">
@@ -2756,7 +2771,7 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>693</v>
+        <v>688</v>
       </c>
     </row>
     <row r="93" ht="27" customHeight="1">
@@ -2806,7 +2821,7 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>2841</v>
+        <v>2848</v>
       </c>
     </row>
     <row r="95" ht="14.25" customHeight="1">
@@ -2831,7 +2846,7 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>3333</v>
+        <v>3330</v>
       </c>
     </row>
     <row r="96" ht="27" customHeight="1">
@@ -2852,7 +2867,7 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>470</v>
+        <v>468</v>
       </c>
     </row>
     <row r="97" ht="14.25" customHeight="1">
@@ -2873,7 +2888,7 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>180</v>
+        <v>216</v>
       </c>
     </row>
     <row r="98" ht="14.25" customHeight="1">
@@ -2898,7 +2913,7 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>959</v>
+        <v>972</v>
       </c>
     </row>
     <row r="99" ht="14.25" customHeight="1">
@@ -2994,7 +3009,7 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>94</v>
+        <v>97</v>
       </c>
     </row>
     <row r="103" ht="14.25" customHeight="1">
@@ -3061,7 +3076,7 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>568</v>
+        <v>570</v>
       </c>
     </row>
     <row r="106" ht="27" customHeight="1">
@@ -3086,7 +3101,7 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>306</v>
+        <v>324</v>
       </c>
     </row>
     <row r="107" ht="14.25" customHeight="1">
@@ -3111,7 +3126,7 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>215</v>
+        <v>218</v>
       </c>
     </row>
     <row r="108" ht="14.25" customHeight="1">
@@ -3136,7 +3151,7 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>215</v>
+        <v>218</v>
       </c>
     </row>
     <row r="109" ht="14.25" customHeight="1">
@@ -3161,7 +3176,7 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>2213</v>
+        <v>2208</v>
       </c>
     </row>
     <row r="110" ht="27" customHeight="1">
@@ -3186,7 +3201,7 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>296</v>
+        <v>306</v>
       </c>
     </row>
     <row r="111" ht="14.25" customHeight="1">
@@ -3257,7 +3272,7 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>237</v>
+        <v>631</v>
       </c>
     </row>
     <row r="114" ht="27" customHeight="1">
@@ -3282,7 +3297,7 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>192</v>
+        <v>195</v>
       </c>
     </row>
     <row r="115" ht="14.25" customHeight="1">
@@ -3328,7 +3343,7 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>2141</v>
+        <v>2147</v>
       </c>
     </row>
     <row r="117" ht="14.25" customHeight="1">
@@ -3366,11 +3381,11 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="119" ht="14.25" customHeight="1">
@@ -3445,7 +3460,7 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="122" ht="14.25" customHeight="1">
@@ -3466,7 +3481,7 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>190</v>
+        <v>193</v>
       </c>
     </row>
     <row r="123" ht="14.25" customHeight="1">
@@ -3508,7 +3523,7 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>444</v>
+        <v>442</v>
       </c>
     </row>
     <row r="125" ht="14.25" customHeight="1">
@@ -3533,7 +3548,7 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>161</v>
+        <v>177</v>
       </c>
     </row>
     <row r="126" ht="14.25" customHeight="1">
@@ -3554,7 +3569,7 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="127" ht="27" customHeight="1">
@@ -3596,11 +3611,11 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>0</v>
+        <v>662</v>
       </c>
     </row>
     <row r="129" ht="27" customHeight="1">
@@ -3646,7 +3661,7 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="131" ht="14.25" customHeight="1">
@@ -3667,7 +3682,7 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>191</v>
+        <v>181</v>
       </c>
     </row>
     <row r="132" ht="14.25" customHeight="1">
@@ -3713,7 +3728,7 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>37</v>
+        <v>23</v>
       </c>
     </row>
     <row r="134" ht="54.75" customHeight="1">
@@ -3738,7 +3753,7 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="135" ht="27.75" customHeight="1">
@@ -3763,7 +3778,7 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="136" ht="14.25" customHeight="1">
@@ -3809,7 +3824,7 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>379</v>
+        <v>373</v>
       </c>
     </row>
     <row r="138" ht="14.25" customHeight="1">
@@ -3855,7 +3870,7 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>1993</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="140" ht="14.25" customHeight="1">
@@ -3880,7 +3895,7 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="141" ht="14.25" customHeight="1">
@@ -3922,11 +3937,11 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
     </row>
     <row r="143" ht="14.25" customHeight="1">
@@ -3972,7 +3987,7 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>720</v>
+        <v>716</v>
       </c>
     </row>
     <row r="145" ht="14.25" customHeight="1">
@@ -4022,7 +4037,7 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>891</v>
+        <v>895</v>
       </c>
     </row>
     <row r="147" ht="14.25" customHeight="1">
@@ -4172,7 +4187,7 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>2000</v>
+        <v>1984</v>
       </c>
     </row>
     <row r="153" ht="14.25" customHeight="1">
@@ -4197,7 +4212,7 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="154" ht="14.25" customHeight="1">
@@ -4222,7 +4237,7 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>358</v>
+        <v>356</v>
       </c>
     </row>
     <row r="155" ht="14.25" customHeight="1">
@@ -4247,7 +4262,7 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>30</v>
+        <v>123</v>
       </c>
     </row>
     <row r="156" ht="14.25" customHeight="1">
@@ -4297,7 +4312,7 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>98</v>
+        <v>102</v>
       </c>
     </row>
     <row r="158" ht="14.25" customHeight="1">
@@ -4343,7 +4358,7 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="160" ht="14.25" customHeight="1">
@@ -4368,7 +4383,7 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="161" ht="14.25" customHeight="1">
@@ -4389,7 +4404,7 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>4955</v>
+        <v>4980</v>
       </c>
     </row>
     <row r="162" ht="14.25" customHeight="1">
@@ -4414,7 +4429,7 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="163" ht="14.25" customHeight="1">
@@ -4439,7 +4454,7 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>1642</v>
+        <v>1652</v>
       </c>
     </row>
     <row r="164" ht="14.25" customHeight="1">
@@ -4464,7 +4479,7 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>1303</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="165" ht="14.25" customHeight="1">
@@ -4489,7 +4504,7 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>290</v>
+        <v>320</v>
       </c>
     </row>
     <row r="166" ht="14.25" customHeight="1">
@@ -4509,7 +4524,7 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>394</v>
+        <v>129</v>
       </c>
       <c r="H166" t="inlineStr">
         <is>
@@ -4539,7 +4554,7 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>219</v>
+        <v>216</v>
       </c>
     </row>
     <row r="168">
@@ -4584,7 +4599,7 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>122</v>
+        <v>127</v>
       </c>
     </row>
     <row r="170">
@@ -4699,7 +4714,7 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="175">
@@ -4819,7 +4834,7 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="180">
@@ -4839,7 +4854,7 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>10</v>
+        <v>346</v>
       </c>
       <c r="H180" t="inlineStr">
         <is>

--- a/config/companies.xlsx
+++ b/config/companies.xlsx
@@ -432,7 +432,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>7303</v>
+        <v>7310</v>
       </c>
     </row>
     <row r="3" ht="27.75" customHeight="1">
@@ -453,7 +453,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1843</v>
+        <v>1848</v>
       </c>
     </row>
     <row r="4" ht="14.25" customHeight="1">
@@ -474,7 +474,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2103</v>
+        <v>2097</v>
       </c>
     </row>
     <row r="5" ht="14.25" customHeight="1">
@@ -499,7 +499,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>800</v>
+        <v>820</v>
       </c>
     </row>
     <row r="6" ht="27" customHeight="1">
@@ -524,7 +524,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1334</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="7" ht="27.75" customHeight="1">
@@ -545,7 +545,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1799</v>
+        <v>1849</v>
       </c>
     </row>
     <row r="8" ht="27.75" customHeight="1">
@@ -566,7 +566,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>528</v>
+        <v>530</v>
       </c>
     </row>
     <row r="9" ht="27" customHeight="1">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>351</v>
+        <v>348</v>
       </c>
     </row>
     <row r="12" ht="14.25" customHeight="1">
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="13" ht="27" customHeight="1">
@@ -776,7 +776,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="17" ht="14.25" customHeight="1">
@@ -797,7 +797,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>596</v>
+        <v>601</v>
       </c>
     </row>
     <row r="20" ht="14.25" customHeight="1">
@@ -888,7 +888,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>9999</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="21" ht="14.25" customHeight="1">
@@ -1014,7 +1014,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1339</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="25" ht="27.75" customHeight="1">
@@ -1035,7 +1035,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>671</v>
+        <v>685</v>
       </c>
     </row>
     <row r="26" ht="14.25" customHeight="1">
@@ -1150,7 +1150,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>671</v>
+        <v>669</v>
       </c>
     </row>
     <row r="34" ht="14.25" customHeight="1">
@@ -1323,7 +1323,7 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>393</v>
+        <v>410</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -1403,7 +1403,7 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>710</v>
+        <v>713</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5199</v>
+        <v>5213</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5150</v>
+        <v>5152</v>
       </c>
     </row>
     <row r="40" ht="14.25" customHeight="1">
@@ -1536,7 +1536,7 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="41" ht="14.25" customHeight="1">
@@ -1582,7 +1582,7 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="43" ht="41.25" customHeight="1">
@@ -1607,7 +1607,7 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2050</v>
+        <v>2162</v>
       </c>
     </row>
     <row r="44" ht="14.25" customHeight="1">
@@ -1632,7 +1632,7 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>973</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="45" ht="27" customHeight="1">
@@ -1657,7 +1657,7 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1533</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="46" ht="14.25" customHeight="1">
@@ -1682,7 +1682,7 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="47" ht="14.25" customHeight="1">
@@ -1707,7 +1707,7 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="48" ht="14.25" customHeight="1">
@@ -1757,7 +1757,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>690</v>
+        <v>686</v>
       </c>
     </row>
     <row r="50" ht="14.25" customHeight="1">
@@ -1807,7 +1807,7 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>847</v>
+        <v>846</v>
       </c>
     </row>
     <row r="52" ht="14.25" customHeight="1">
@@ -1849,7 +1849,7 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>256</v>
+        <v>339</v>
       </c>
     </row>
     <row r="54" ht="27" customHeight="1">
@@ -1895,7 +1895,7 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1980</v>
+        <v>1966</v>
       </c>
     </row>
     <row r="56" ht="14.25" customHeight="1">
@@ -1920,7 +1920,7 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1116</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="57" ht="14.25" customHeight="1">
@@ -1941,7 +1941,7 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>639</v>
+        <v>619</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>7965</v>
+        <v>7972</v>
       </c>
     </row>
     <row r="59" ht="14.25" customHeight="1">
@@ -1992,7 +1992,7 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="60" ht="27" customHeight="1">
@@ -2038,7 +2038,7 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>391</v>
+        <v>386</v>
       </c>
     </row>
     <row r="62" ht="14.25" customHeight="1">
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1088</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="63" ht="27" customHeight="1">
@@ -2088,7 +2088,7 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="64" ht="14.25" customHeight="1">
@@ -2113,7 +2113,7 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1310</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="65" ht="27.75" customHeight="1">
@@ -2138,7 +2138,7 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>445</v>
+        <v>440</v>
       </c>
     </row>
     <row r="66" ht="14.25" customHeight="1">
@@ -2159,7 +2159,7 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>550</v>
+        <v>548</v>
       </c>
     </row>
     <row r="67" ht="14.25" customHeight="1">
@@ -2180,7 +2180,7 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>367</v>
+        <v>374</v>
       </c>
     </row>
     <row r="68" ht="27" customHeight="1">
@@ -2205,7 +2205,7 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>472</v>
+        <v>475</v>
       </c>
     </row>
     <row r="69" ht="14.25" customHeight="1">
@@ -2301,7 +2301,7 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>21</v>
+        <v>36</v>
       </c>
     </row>
     <row r="73" ht="14.25" customHeight="1">
@@ -2322,7 +2322,7 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>72</v>
+        <v>79</v>
       </c>
     </row>
     <row r="74" ht="14.25" customHeight="1">
@@ -2331,7 +2331,11 @@
           <t>Caterpillar</t>
         </is>
       </c>
-      <c r="B74" s="2" t="n"/>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>https://cat.wd5.myworkdayjobs.com/en-US/CaterpillarCareers/job/Wujiang-Jiangsu/Digital-Information-Systems-Engineer_R0000375017/apply</t>
+        </is>
+      </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
           <t>https://careers.caterpillar.com/</t>
@@ -2343,7 +2347,7 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>152</v>
+        <v>929</v>
       </c>
     </row>
     <row r="75" ht="14.25" customHeight="1">
@@ -2385,7 +2389,7 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>468</v>
+        <v>472</v>
       </c>
     </row>
     <row r="77" ht="14.25" customHeight="1">
@@ -2456,7 +2460,7 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>209</v>
+        <v>206</v>
       </c>
     </row>
     <row r="80" ht="27.75" customHeight="1">
@@ -2481,7 +2485,7 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="81" ht="14.25" customHeight="1">
@@ -2506,7 +2510,7 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="82" ht="14.25" customHeight="1">
@@ -2552,7 +2556,7 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
@@ -2582,7 +2586,7 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1860</v>
+        <v>1868</v>
       </c>
     </row>
     <row r="85" ht="14.25" customHeight="1">
@@ -2607,7 +2611,7 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1920</v>
+        <v>1954</v>
       </c>
     </row>
     <row r="86" ht="14.25" customHeight="1">
@@ -2653,7 +2657,7 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>197</v>
+        <v>399</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
@@ -2725,7 +2729,7 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="91" ht="14.25" customHeight="1">
@@ -2771,7 +2775,7 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>688</v>
+        <v>684</v>
       </c>
     </row>
     <row r="93" ht="27" customHeight="1">
@@ -2796,7 +2800,7 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>249</v>
+        <v>252</v>
       </c>
     </row>
     <row r="94" ht="27" customHeight="1">
@@ -2821,7 +2825,7 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>2848</v>
+        <v>2849</v>
       </c>
     </row>
     <row r="95" ht="14.25" customHeight="1">
@@ -2867,7 +2871,7 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>468</v>
+        <v>472</v>
       </c>
     </row>
     <row r="97" ht="14.25" customHeight="1">
@@ -2888,7 +2892,7 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="98" ht="14.25" customHeight="1">
@@ -2913,7 +2917,7 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>972</v>
+        <v>970</v>
       </c>
     </row>
     <row r="99" ht="14.25" customHeight="1">
@@ -2945,21 +2949,26 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
+          <t>https://cvshealth.wd1.myworkdayjobs.com/en-US/CVS_Health_Careers</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
           <t>https://jobs.cvshealth.com/us/en</t>
         </is>
       </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>https://jobs.cvshealth.com/</t>
-        </is>
-      </c>
       <c r="D100" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>8000</v>
+        <v>6800</v>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>2026-08-26: moved off the Phenom board (jobs.cvshealth.com) to the Workday tenant its own applyUrl links to. Phenom served this tenant in relevance order - measured, offset 0 held a 12 Jun posting and offset 7,990 one from 24 Aug - so its 8,000-row ceiling hid jobs of every age including current ones. Workday CXS is posting-date descending (offset 0 'Posted Today', 6,000 '9 Days Ago', 12,000 '23 Days Ago'), so the walk stops at the freshness window instead: 6,777 jobs in 220s, oldest 12 days, vs 8,000 in 432s.</t>
+        </is>
       </c>
     </row>
     <row r="101" ht="14.25" customHeight="1">
@@ -2986,6 +2995,11 @@
       <c r="E101" t="n">
         <v>8000</v>
       </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>2026-08-26: DUPLICATE OF CVS. signifyhealth.com/careers redirects to jobs.cvshealth.com/us/en/signify-health, and that sub-path has no board of its own - the search endpoint ignores it and returns CVS's full 19,126, so this row scrapes CVS's board a second time (~430s) and files the result under the wrong employer. There is no Signify site on the CVS Workday tenant either (Signify_Health / SignifyHealth / Signify_Health_Careers all 404). Consider removing this row.</t>
+        </is>
+      </c>
     </row>
     <row r="102" ht="27" customHeight="1">
       <c r="A102" s="2" t="inlineStr">
@@ -3009,7 +3023,7 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>97</v>
+        <v>101</v>
       </c>
     </row>
     <row r="103" ht="14.25" customHeight="1">
@@ -3076,7 +3090,7 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>570</v>
+        <v>574</v>
       </c>
     </row>
     <row r="106" ht="27" customHeight="1">
@@ -3101,7 +3115,7 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>324</v>
+        <v>333</v>
       </c>
     </row>
     <row r="107" ht="14.25" customHeight="1">
@@ -3126,7 +3140,7 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>218</v>
+        <v>225</v>
       </c>
     </row>
     <row r="108" ht="14.25" customHeight="1">
@@ -3151,7 +3165,7 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>218</v>
+        <v>225</v>
       </c>
     </row>
     <row r="109" ht="14.25" customHeight="1">
@@ -3176,7 +3190,7 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>2208</v>
+        <v>2205</v>
       </c>
     </row>
     <row r="110" ht="27" customHeight="1">
@@ -3201,7 +3215,7 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="111" ht="14.25" customHeight="1">
@@ -3226,7 +3240,7 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>1192</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="112" ht="14.25" customHeight="1">
@@ -3272,7 +3286,7 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>631</v>
+        <v>691</v>
       </c>
     </row>
     <row r="114" ht="27" customHeight="1">
@@ -3297,7 +3311,7 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="115" ht="14.25" customHeight="1">
@@ -3343,7 +3357,7 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>2147</v>
+        <v>2140</v>
       </c>
     </row>
     <row r="117" ht="14.25" customHeight="1">
@@ -3435,7 +3449,7 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="121" ht="41.25" customHeight="1">
@@ -3481,7 +3495,7 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="123" ht="14.25" customHeight="1">
@@ -3523,7 +3537,7 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>442</v>
+        <v>440</v>
       </c>
     </row>
     <row r="125" ht="14.25" customHeight="1">
@@ -3548,7 +3562,7 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="126" ht="14.25" customHeight="1">
@@ -3569,7 +3583,7 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="127" ht="27" customHeight="1">
@@ -3594,7 +3608,7 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="128" ht="14.25" customHeight="1">
@@ -3615,7 +3629,7 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>662</v>
+        <v>824</v>
       </c>
     </row>
     <row r="129" ht="27" customHeight="1">
@@ -3661,7 +3675,7 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="131" ht="14.25" customHeight="1">
@@ -3753,7 +3767,7 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="135" ht="27.75" customHeight="1">
@@ -3778,7 +3792,7 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>204</v>
+        <v>199</v>
       </c>
     </row>
     <row r="136" ht="14.25" customHeight="1">
@@ -3824,7 +3838,7 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>373</v>
+        <v>371</v>
       </c>
     </row>
     <row r="138" ht="14.25" customHeight="1">
@@ -3870,7 +3884,7 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>2000</v>
+        <v>1991</v>
       </c>
     </row>
     <row r="140" ht="14.25" customHeight="1">
@@ -3895,7 +3909,7 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>453</v>
+        <v>446</v>
       </c>
     </row>
     <row r="141" ht="14.25" customHeight="1">
@@ -3920,7 +3934,7 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="142" ht="14.25" customHeight="1">
@@ -3937,11 +3951,11 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
     </row>
     <row r="143" ht="14.25" customHeight="1">
@@ -3987,7 +4001,7 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>716</v>
+        <v>760</v>
       </c>
     </row>
     <row r="145" ht="14.25" customHeight="1">
@@ -4037,7 +4051,7 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>895</v>
+        <v>894</v>
       </c>
     </row>
     <row r="147" ht="14.25" customHeight="1">
@@ -4112,7 +4126,7 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>176</v>
+        <v>172</v>
       </c>
     </row>
     <row r="150" ht="27" customHeight="1">
@@ -4162,7 +4176,7 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="152" ht="41.25" customHeight="1">
@@ -4187,7 +4201,7 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>1984</v>
+        <v>1994</v>
       </c>
     </row>
     <row r="153" ht="14.25" customHeight="1">
@@ -4237,7 +4251,7 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>356</v>
+        <v>354</v>
       </c>
     </row>
     <row r="155" ht="14.25" customHeight="1">
@@ -4262,7 +4276,7 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>123</v>
+        <v>55</v>
       </c>
     </row>
     <row r="156" ht="14.25" customHeight="1">
@@ -4312,7 +4326,7 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="158" ht="14.25" customHeight="1">
@@ -4358,7 +4372,7 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="160" ht="14.25" customHeight="1">
@@ -4383,7 +4397,7 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="161" ht="14.25" customHeight="1">
@@ -4404,7 +4418,7 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>4980</v>
+        <v>4991</v>
       </c>
     </row>
     <row r="162" ht="14.25" customHeight="1">
@@ -4454,7 +4468,7 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>1652</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="164" ht="14.25" customHeight="1">
@@ -4479,7 +4493,7 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>1311</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="165" ht="14.25" customHeight="1">
@@ -4504,7 +4518,7 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>320</v>
+        <v>315</v>
       </c>
     </row>
     <row r="166" ht="14.25" customHeight="1">
@@ -4524,7 +4538,7 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>129</v>
+        <v>399</v>
       </c>
       <c r="H166" t="inlineStr">
         <is>
@@ -4554,7 +4568,7 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="168">
@@ -4599,7 +4613,7 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="170">
@@ -4644,7 +4658,7 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="H171" t="inlineStr">
         <is>
@@ -4669,7 +4683,7 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="173">
@@ -4764,7 +4778,7 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="177">
@@ -4834,7 +4848,7 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="180">
@@ -4854,7 +4868,7 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>346</v>
+        <v>277</v>
       </c>
       <c r="H180" t="inlineStr">
         <is>

--- a/config/companies.xlsx
+++ b/config/companies.xlsx
@@ -361,7 +361,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H181"/>
+  <dimension ref="A1:H184"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.68359375" defaultRowHeight="14.4"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -432,7 +432,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>7310</v>
+        <v>7288</v>
       </c>
     </row>
     <row r="3" ht="27.75" customHeight="1">
@@ -453,7 +453,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1848</v>
+        <v>1851</v>
       </c>
     </row>
     <row r="4" ht="14.25" customHeight="1">
@@ -474,7 +474,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2097</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="5" ht="14.25" customHeight="1">
@@ -524,7 +524,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1331</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="7" ht="27.75" customHeight="1">
@@ -545,7 +545,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1849</v>
+        <v>1802</v>
       </c>
     </row>
     <row r="8" ht="27.75" customHeight="1">
@@ -566,7 +566,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>530</v>
+        <v>534</v>
       </c>
     </row>
     <row r="9" ht="27" customHeight="1">
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="15" ht="27.75" customHeight="1">
@@ -776,7 +776,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>495</v>
+        <v>493</v>
       </c>
     </row>
     <row r="17" ht="14.25" customHeight="1">
@@ -1014,7 +1014,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1343</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="25" ht="27.75" customHeight="1">
@@ -1035,7 +1035,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>685</v>
+        <v>643</v>
       </c>
     </row>
     <row r="26" ht="14.25" customHeight="1">
@@ -1060,7 +1060,7 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4400</v>
+        <v>4466</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="29" ht="14.25" customHeight="1">
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>669</v>
+        <v>672</v>
       </c>
     </row>
     <row r="34" ht="14.25" customHeight="1">
@@ -1363,7 +1363,7 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -1446,7 +1446,7 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
     </row>
     <row r="38" ht="14.25" customHeight="1">
@@ -1471,7 +1471,7 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5213</v>
+        <v>5212</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -1536,7 +1536,7 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="41" ht="14.25" customHeight="1">
@@ -1561,7 +1561,7 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="42" ht="27.75" customHeight="1">
@@ -1607,7 +1607,7 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2162</v>
+        <v>2156</v>
       </c>
     </row>
     <row r="44" ht="14.25" customHeight="1">
@@ -1632,7 +1632,7 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1024</v>
+        <v>996</v>
       </c>
     </row>
     <row r="45" ht="27" customHeight="1">
@@ -1657,7 +1657,7 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1534</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="46" ht="14.25" customHeight="1">
@@ -1682,7 +1682,7 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1212</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="47" ht="14.25" customHeight="1">
@@ -1707,7 +1707,7 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>600</v>
+        <v>598</v>
       </c>
     </row>
     <row r="48" ht="14.25" customHeight="1">
@@ -1732,7 +1732,7 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="49" ht="14.25" customHeight="1">
@@ -1757,7 +1757,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>686</v>
+        <v>682</v>
       </c>
     </row>
     <row r="50" ht="14.25" customHeight="1">
@@ -1807,7 +1807,7 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>846</v>
+        <v>848</v>
       </c>
     </row>
     <row r="52" ht="14.25" customHeight="1">
@@ -1849,7 +1849,7 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>339</v>
+        <v>200</v>
       </c>
     </row>
     <row r="54" ht="27" customHeight="1">
@@ -1895,7 +1895,7 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1966</v>
+        <v>1880</v>
       </c>
     </row>
     <row r="56" ht="14.25" customHeight="1">
@@ -1920,7 +1920,7 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1128</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="57" ht="14.25" customHeight="1">
@@ -1941,7 +1941,7 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>619</v>
+        <v>639</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>7972</v>
+        <v>7986</v>
       </c>
     </row>
     <row r="59" ht="14.25" customHeight="1">
@@ -2013,11 +2013,11 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61" ht="14.25" customHeight="1">
@@ -2038,7 +2038,7 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>386</v>
+        <v>397</v>
       </c>
     </row>
     <row r="62" ht="14.25" customHeight="1">
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1092</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="63" ht="27" customHeight="1">
@@ -2088,7 +2088,7 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>446</v>
+        <v>452</v>
       </c>
     </row>
     <row r="64" ht="14.25" customHeight="1">
@@ -2113,7 +2113,7 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1313</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="65" ht="27.75" customHeight="1">
@@ -2180,7 +2180,7 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>374</v>
+        <v>369</v>
       </c>
     </row>
     <row r="68" ht="27" customHeight="1">
@@ -2205,7 +2205,7 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>475</v>
+        <v>469</v>
       </c>
     </row>
     <row r="69" ht="14.25" customHeight="1">
@@ -2276,7 +2276,7 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="72" ht="14.25" customHeight="1">
@@ -2301,7 +2301,7 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="73" ht="14.25" customHeight="1">
@@ -2322,7 +2322,7 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="74" ht="14.25" customHeight="1">
@@ -2347,7 +2347,7 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>929</v>
+        <v>912</v>
       </c>
     </row>
     <row r="75" ht="14.25" customHeight="1">
@@ -2368,7 +2368,7 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>116</v>
+        <v>111</v>
       </c>
     </row>
     <row r="76" ht="27" customHeight="1">
@@ -2389,7 +2389,7 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>472</v>
+        <v>470</v>
       </c>
     </row>
     <row r="77" ht="14.25" customHeight="1">
@@ -2414,7 +2414,7 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="78" ht="14.25" customHeight="1">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>206</v>
+        <v>203</v>
       </c>
     </row>
     <row r="80" ht="27.75" customHeight="1">
@@ -2510,7 +2510,7 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="82" ht="14.25" customHeight="1">
@@ -2535,7 +2535,7 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>4400</v>
+        <v>4466</v>
       </c>
     </row>
     <row r="83" ht="14.25" customHeight="1">
@@ -2556,7 +2556,7 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
@@ -2586,7 +2586,7 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1868</v>
+        <v>1856</v>
       </c>
     </row>
     <row r="85" ht="14.25" customHeight="1">
@@ -2611,7 +2611,7 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1954</v>
+        <v>1941</v>
       </c>
     </row>
     <row r="86" ht="14.25" customHeight="1">
@@ -2632,7 +2632,7 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>35</v>
+        <v>181</v>
       </c>
     </row>
     <row r="87" ht="27.75" customHeight="1">
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
@@ -2825,7 +2825,7 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>2849</v>
+        <v>2846</v>
       </c>
     </row>
     <row r="95" ht="14.25" customHeight="1">
@@ -2850,7 +2850,7 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>3330</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="96" ht="27" customHeight="1">
@@ -2871,7 +2871,7 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>472</v>
+        <v>470</v>
       </c>
     </row>
     <row r="97" ht="14.25" customHeight="1">
@@ -2892,7 +2892,7 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="98" ht="14.25" customHeight="1">
@@ -2917,7 +2917,7 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>970</v>
+        <v>967</v>
       </c>
     </row>
     <row r="99" ht="14.25" customHeight="1">
@@ -2963,7 +2963,7 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6800</v>
+        <v>5700</v>
       </c>
       <c r="H100" t="inlineStr">
         <is>
@@ -3023,7 +3023,7 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="103" ht="14.25" customHeight="1">
@@ -3090,7 +3090,7 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="106" ht="27" customHeight="1">
@@ -3115,7 +3115,7 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>333</v>
+        <v>323</v>
       </c>
     </row>
     <row r="107" ht="14.25" customHeight="1">
@@ -3140,7 +3140,7 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>225</v>
+        <v>219</v>
       </c>
     </row>
     <row r="108" ht="14.25" customHeight="1">
@@ -3165,7 +3165,7 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>225</v>
+        <v>219</v>
       </c>
     </row>
     <row r="109" ht="14.25" customHeight="1">
@@ -3190,7 +3190,7 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>2205</v>
+        <v>2192</v>
       </c>
     </row>
     <row r="110" ht="27" customHeight="1">
@@ -3357,7 +3357,7 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>2140</v>
+        <v>2152</v>
       </c>
     </row>
     <row r="117" ht="14.25" customHeight="1">
@@ -3474,7 +3474,7 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="122" ht="14.25" customHeight="1">
@@ -3495,7 +3495,7 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>192</v>
+        <v>206</v>
       </c>
     </row>
     <row r="123" ht="14.25" customHeight="1">
@@ -3537,7 +3537,7 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>440</v>
+        <v>449</v>
       </c>
     </row>
     <row r="125" ht="14.25" customHeight="1">
@@ -3562,7 +3562,7 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>179</v>
+        <v>169</v>
       </c>
     </row>
     <row r="126" ht="14.25" customHeight="1">
@@ -3608,7 +3608,7 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="128" ht="14.25" customHeight="1">
@@ -3629,7 +3629,7 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>824</v>
+        <v>820</v>
       </c>
     </row>
     <row r="129" ht="27" customHeight="1">
@@ -3792,7 +3792,7 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="136" ht="14.25" customHeight="1">
@@ -3884,7 +3884,7 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>1991</v>
+        <v>1994</v>
       </c>
     </row>
     <row r="140" ht="14.25" customHeight="1">
@@ -3909,7 +3909,7 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="141" ht="14.25" customHeight="1">
@@ -3934,7 +3934,7 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="142" ht="14.25" customHeight="1">
@@ -4001,7 +4001,7 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>760</v>
+        <v>720</v>
       </c>
     </row>
     <row r="145" ht="14.25" customHeight="1">
@@ -4051,7 +4051,7 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>894</v>
+        <v>893</v>
       </c>
     </row>
     <row r="147" ht="14.25" customHeight="1">
@@ -4076,7 +4076,7 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="148" ht="14.25" customHeight="1">
@@ -4176,7 +4176,7 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="152" ht="41.25" customHeight="1">
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>1994</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="153" ht="14.25" customHeight="1">
@@ -4251,7 +4251,7 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="155" ht="14.25" customHeight="1">
@@ -4276,7 +4276,7 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>55</v>
+        <v>49</v>
       </c>
     </row>
     <row r="156" ht="14.25" customHeight="1">
@@ -4372,7 +4372,7 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="160" ht="14.25" customHeight="1">
@@ -4397,7 +4397,7 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="161" ht="14.25" customHeight="1">
@@ -4418,7 +4418,7 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>4991</v>
+        <v>5007</v>
       </c>
     </row>
     <row r="162" ht="14.25" customHeight="1">
@@ -4468,7 +4468,7 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>1656</v>
+        <v>1654</v>
       </c>
     </row>
     <row r="164" ht="14.25" customHeight="1">
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>1317</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="165" ht="14.25" customHeight="1">
@@ -4518,7 +4518,7 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="166" ht="14.25" customHeight="1">
@@ -4538,7 +4538,7 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="H166" t="inlineStr">
         <is>
@@ -4568,7 +4568,7 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="168">
@@ -4613,7 +4613,7 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>129</v>
+        <v>126</v>
       </c>
     </row>
     <row r="170">
@@ -4658,7 +4658,7 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H171" t="inlineStr">
         <is>
@@ -4868,7 +4868,7 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>277</v>
+        <v>3</v>
       </c>
       <c r="H180" t="inlineStr">
         <is>
@@ -4894,6 +4894,66 @@
       </c>
       <c r="E181" t="n">
         <v>46</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Dexian</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>https://dexian.com/jobs/</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="E182" t="n">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Built In</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>https://builtin.com/jobs</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="E183" t="n">
+        <v>1296</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>MSCI</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>https://globalcareers-msci.icims.com/jobs/</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="E184" t="n">
+        <v>108</v>
       </c>
     </row>
   </sheetData>

--- a/config/companies.xlsx
+++ b/config/companies.xlsx
@@ -432,7 +432,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>7288</v>
+        <v>7218</v>
       </c>
     </row>
     <row r="3" ht="27.75" customHeight="1">
@@ -453,7 +453,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1851</v>
+        <v>1844</v>
       </c>
     </row>
     <row r="4" ht="14.25" customHeight="1">
@@ -474,7 +474,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2087</v>
+        <v>2080</v>
       </c>
     </row>
     <row r="5" ht="14.25" customHeight="1">
@@ -524,7 +524,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1322</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="7" ht="27.75" customHeight="1">
@@ -545,7 +545,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1802</v>
+        <v>1805</v>
       </c>
     </row>
     <row r="8" ht="27.75" customHeight="1">
@@ -566,7 +566,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>534</v>
+        <v>529</v>
       </c>
     </row>
     <row r="9" ht="27" customHeight="1">
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="10" ht="27" customHeight="1">
@@ -612,7 +612,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="11" ht="14.25" customHeight="1">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>348</v>
+        <v>353</v>
       </c>
     </row>
     <row r="12" ht="14.25" customHeight="1">
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>281</v>
+        <v>267</v>
       </c>
     </row>
     <row r="13" ht="27" customHeight="1">
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="15" ht="27.75" customHeight="1">
@@ -740,7 +740,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>493</v>
+        <v>462</v>
       </c>
     </row>
     <row r="17" ht="14.25" customHeight="1">
@@ -797,7 +797,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>601</v>
+        <v>600</v>
       </c>
     </row>
     <row r="20" ht="14.25" customHeight="1">
@@ -888,7 +888,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>10000</v>
+        <v>9999</v>
       </c>
     </row>
     <row r="21" ht="14.25" customHeight="1">
@@ -974,7 +974,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1338</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="25" ht="27.75" customHeight="1">
@@ -1035,7 +1035,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>643</v>
+        <v>653</v>
       </c>
     </row>
     <row r="26" ht="14.25" customHeight="1">
@@ -1060,7 +1060,7 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4466</v>
+        <v>4497</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="29" ht="14.25" customHeight="1">
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>672</v>
+        <v>675</v>
       </c>
     </row>
     <row r="34" ht="14.25" customHeight="1">
@@ -1363,7 +1363,7 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -1403,7 +1403,7 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>713</v>
+        <v>698</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -1446,7 +1446,7 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="38" ht="14.25" customHeight="1">
@@ -1471,7 +1471,7 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5212</v>
+        <v>5218</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5152</v>
+        <v>5179</v>
       </c>
     </row>
     <row r="40" ht="14.25" customHeight="1">
@@ -1536,7 +1536,7 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="41" ht="14.25" customHeight="1">
@@ -1561,7 +1561,7 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="42" ht="27.75" customHeight="1">
@@ -1582,7 +1582,7 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="43" ht="41.25" customHeight="1">
@@ -1607,7 +1607,7 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2156</v>
+        <v>2158</v>
       </c>
     </row>
     <row r="44" ht="14.25" customHeight="1">
@@ -1632,7 +1632,7 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>996</v>
+        <v>969</v>
       </c>
     </row>
     <row r="45" ht="27" customHeight="1">
@@ -1657,7 +1657,7 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1543</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="46" ht="14.25" customHeight="1">
@@ -1682,7 +1682,7 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1206</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="47" ht="14.25" customHeight="1">
@@ -1707,7 +1707,7 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>598</v>
+        <v>605</v>
       </c>
     </row>
     <row r="48" ht="14.25" customHeight="1">
@@ -1732,7 +1732,7 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="49" ht="14.25" customHeight="1">
@@ -1757,7 +1757,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>682</v>
+        <v>695</v>
       </c>
     </row>
     <row r="50" ht="14.25" customHeight="1">
@@ -1807,7 +1807,7 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>848</v>
+        <v>843</v>
       </c>
     </row>
     <row r="52" ht="14.25" customHeight="1">
@@ -1849,7 +1849,7 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
     </row>
     <row r="54" ht="27" customHeight="1">
@@ -1895,7 +1895,7 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1880</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="56" ht="14.25" customHeight="1">
@@ -1920,7 +1920,7 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1124</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="57" ht="14.25" customHeight="1">
@@ -1971,7 +1971,7 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>7986</v>
+        <v>8104</v>
       </c>
     </row>
     <row r="59" ht="14.25" customHeight="1">
@@ -1992,7 +1992,7 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="60" ht="27" customHeight="1">
@@ -2038,7 +2038,7 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>397</v>
+        <v>371</v>
       </c>
     </row>
     <row r="62" ht="14.25" customHeight="1">
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1093</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="63" ht="27" customHeight="1">
@@ -2088,7 +2088,7 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>452</v>
+        <v>457</v>
       </c>
     </row>
     <row r="64" ht="14.25" customHeight="1">
@@ -2113,7 +2113,7 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1439</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="65" ht="27.75" customHeight="1">
@@ -2138,7 +2138,7 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>440</v>
+        <v>425</v>
       </c>
     </row>
     <row r="66" ht="14.25" customHeight="1">
@@ -2159,7 +2159,7 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>548</v>
+        <v>557</v>
       </c>
     </row>
     <row r="67" ht="14.25" customHeight="1">
@@ -2180,7 +2180,7 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>369</v>
+        <v>367</v>
       </c>
     </row>
     <row r="68" ht="27" customHeight="1">
@@ -2205,7 +2205,7 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>469</v>
+        <v>453</v>
       </c>
     </row>
     <row r="69" ht="14.25" customHeight="1">
@@ -2276,7 +2276,7 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="72" ht="14.25" customHeight="1">
@@ -2301,7 +2301,7 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="73" ht="14.25" customHeight="1">
@@ -2322,7 +2322,7 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="74" ht="14.25" customHeight="1">
@@ -2347,7 +2347,7 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>912</v>
+        <v>950</v>
       </c>
     </row>
     <row r="75" ht="14.25" customHeight="1">
@@ -2368,7 +2368,7 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="76" ht="27" customHeight="1">
@@ -2389,7 +2389,7 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>470</v>
+        <v>489</v>
       </c>
     </row>
     <row r="77" ht="14.25" customHeight="1">
@@ -2414,7 +2414,7 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
     </row>
     <row r="78" ht="14.25" customHeight="1">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>203</v>
+        <v>195</v>
       </c>
     </row>
     <row r="80" ht="27.75" customHeight="1">
@@ -2485,7 +2485,7 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
     </row>
     <row r="81" ht="14.25" customHeight="1">
@@ -2510,7 +2510,7 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="82" ht="14.25" customHeight="1">
@@ -2535,7 +2535,7 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>4466</v>
+        <v>4497</v>
       </c>
     </row>
     <row r="83" ht="14.25" customHeight="1">
@@ -2586,7 +2586,7 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1856</v>
+        <v>1867</v>
       </c>
     </row>
     <row r="85" ht="14.25" customHeight="1">
@@ -2611,7 +2611,7 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1941</v>
+        <v>1968</v>
       </c>
     </row>
     <row r="86" ht="14.25" customHeight="1">
@@ -2632,7 +2632,7 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>181</v>
+        <v>36</v>
       </c>
     </row>
     <row r="87" ht="27.75" customHeight="1">
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>404</v>
+        <v>389</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
@@ -2729,7 +2729,7 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>185</v>
+        <v>190</v>
       </c>
     </row>
     <row r="91" ht="14.25" customHeight="1">
@@ -2800,7 +2800,7 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="94" ht="27" customHeight="1">
@@ -2825,7 +2825,7 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>2846</v>
+        <v>2858</v>
       </c>
     </row>
     <row r="95" ht="14.25" customHeight="1">
@@ -2850,7 +2850,7 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>3335</v>
+        <v>3355</v>
       </c>
     </row>
     <row r="96" ht="27" customHeight="1">
@@ -2871,7 +2871,7 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>470</v>
+        <v>489</v>
       </c>
     </row>
     <row r="97" ht="14.25" customHeight="1">
@@ -2917,7 +2917,7 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>967</v>
+        <v>977</v>
       </c>
     </row>
     <row r="99" ht="14.25" customHeight="1">
@@ -2938,7 +2938,7 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="100" ht="14.25" customHeight="1">
@@ -2963,7 +2963,7 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>5700</v>
+        <v>5893</v>
       </c>
       <c r="H100" t="inlineStr">
         <is>
@@ -3023,7 +3023,7 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="103" ht="14.25" customHeight="1">
@@ -3090,7 +3090,7 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>573</v>
+        <v>576</v>
       </c>
     </row>
     <row r="106" ht="27" customHeight="1">
@@ -3115,7 +3115,7 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="107" ht="14.25" customHeight="1">
@@ -3190,7 +3190,7 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>2192</v>
+        <v>2152</v>
       </c>
     </row>
     <row r="110" ht="27" customHeight="1">
@@ -3215,7 +3215,7 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>308</v>
+        <v>327</v>
       </c>
     </row>
     <row r="111" ht="14.25" customHeight="1">
@@ -3240,7 +3240,7 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>1182</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="112" ht="14.25" customHeight="1">
@@ -3311,7 +3311,7 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="115" ht="14.25" customHeight="1">
@@ -3357,7 +3357,7 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>2152</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="117" ht="14.25" customHeight="1">
@@ -3378,7 +3378,7 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>3708</v>
+        <v>3718</v>
       </c>
     </row>
     <row r="118" ht="14.25" customHeight="1">
@@ -3449,7 +3449,7 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="121" ht="41.25" customHeight="1">
@@ -3474,7 +3474,7 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="122" ht="14.25" customHeight="1">
@@ -3495,7 +3495,7 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="123" ht="14.25" customHeight="1">
@@ -3537,7 +3537,7 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>449</v>
+        <v>447</v>
       </c>
     </row>
     <row r="125" ht="14.25" customHeight="1">
@@ -3562,7 +3562,7 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>169</v>
+        <v>175</v>
       </c>
     </row>
     <row r="126" ht="14.25" customHeight="1">
@@ -3583,7 +3583,7 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="127" ht="27" customHeight="1">
@@ -3629,7 +3629,7 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>820</v>
+        <v>822</v>
       </c>
     </row>
     <row r="129" ht="27" customHeight="1">
@@ -3654,7 +3654,7 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="130" ht="27" customHeight="1">
@@ -3675,7 +3675,7 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="131" ht="14.25" customHeight="1">
@@ -3696,7 +3696,7 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="132" ht="14.25" customHeight="1">
@@ -3742,7 +3742,7 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="134" ht="54.75" customHeight="1">
@@ -3767,7 +3767,7 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="135" ht="27.75" customHeight="1">
@@ -3792,7 +3792,7 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="136" ht="14.25" customHeight="1">
@@ -3817,7 +3817,7 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="137" ht="14.25" customHeight="1">
@@ -3838,7 +3838,7 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>371</v>
+        <v>363</v>
       </c>
     </row>
     <row r="138" ht="14.25" customHeight="1">
@@ -3884,7 +3884,7 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>1994</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="140" ht="14.25" customHeight="1">
@@ -3934,7 +3934,7 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="142" ht="14.25" customHeight="1">
@@ -3951,11 +3951,11 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
     </row>
     <row r="143" ht="14.25" customHeight="1">
@@ -4051,7 +4051,7 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>893</v>
+        <v>892</v>
       </c>
     </row>
     <row r="147" ht="14.25" customHeight="1">
@@ -4076,7 +4076,7 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="148" ht="14.25" customHeight="1">
@@ -4126,7 +4126,7 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>172</v>
+        <v>168</v>
       </c>
     </row>
     <row r="150" ht="27" customHeight="1">
@@ -4151,7 +4151,7 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="151" ht="14.25" customHeight="1">
@@ -4176,7 +4176,7 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="152" ht="41.25" customHeight="1">
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>2000</v>
+        <v>1996</v>
       </c>
     </row>
     <row r="153" ht="14.25" customHeight="1">
@@ -4226,7 +4226,7 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="154" ht="14.25" customHeight="1">
@@ -4251,7 +4251,7 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>353</v>
+        <v>343</v>
       </c>
     </row>
     <row r="155" ht="14.25" customHeight="1">
@@ -4276,7 +4276,7 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="156" ht="14.25" customHeight="1">
@@ -4301,7 +4301,7 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="157" ht="14.25" customHeight="1">
@@ -4326,7 +4326,7 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="158" ht="14.25" customHeight="1">
@@ -4372,7 +4372,7 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>187</v>
+        <v>183</v>
       </c>
     </row>
     <row r="160" ht="14.25" customHeight="1">
@@ -4397,7 +4397,7 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="161" ht="14.25" customHeight="1">
@@ -4418,7 +4418,7 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>5007</v>
+        <v>4992</v>
       </c>
     </row>
     <row r="162" ht="14.25" customHeight="1">
@@ -4443,7 +4443,7 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="163" ht="14.25" customHeight="1">
@@ -4468,7 +4468,7 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>1654</v>
+        <v>1619</v>
       </c>
     </row>
     <row r="164" ht="14.25" customHeight="1">
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>1289</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="165" ht="14.25" customHeight="1">
@@ -4518,7 +4518,7 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>314</v>
+        <v>331</v>
       </c>
     </row>
     <row r="166" ht="14.25" customHeight="1">
@@ -4538,7 +4538,7 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>409</v>
+        <v>385</v>
       </c>
       <c r="H166" t="inlineStr">
         <is>
@@ -4568,7 +4568,7 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>216</v>
+        <v>222</v>
       </c>
     </row>
     <row r="168">
@@ -4588,7 +4588,7 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="169">
@@ -4613,7 +4613,7 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>126</v>
+        <v>120</v>
       </c>
     </row>
     <row r="170">
@@ -4683,7 +4683,7 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="173">
@@ -4728,7 +4728,7 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="175">
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>231</v>
+        <v>234</v>
       </c>
     </row>
     <row r="177">
@@ -4823,7 +4823,7 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>404</v>
+        <v>363</v>
       </c>
     </row>
     <row r="179">
@@ -4848,7 +4848,7 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>219</v>
+        <v>225</v>
       </c>
     </row>
     <row r="180">
@@ -4868,7 +4868,7 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>3</v>
+        <v>338</v>
       </c>
       <c r="H180" t="inlineStr">
         <is>
@@ -4913,7 +4913,7 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>583</v>
+        <v>589</v>
       </c>
     </row>
     <row r="183">
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>1296</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="184">
@@ -4953,7 +4953,7 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
   </sheetData>

--- a/config/companies.xlsx
+++ b/config/companies.xlsx
@@ -361,7 +361,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H184"/>
+  <dimension ref="A1:H185"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.68359375" defaultRowHeight="14.4"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -432,7 +432,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>7218</v>
+        <v>6987</v>
       </c>
     </row>
     <row r="3" ht="27.75" customHeight="1">
@@ -453,7 +453,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1844</v>
+        <v>1848</v>
       </c>
     </row>
     <row r="4" ht="14.25" customHeight="1">
@@ -474,7 +474,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2080</v>
+        <v>2095</v>
       </c>
     </row>
     <row r="5" ht="14.25" customHeight="1">
@@ -524,7 +524,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1312</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="7" ht="27.75" customHeight="1">
@@ -545,7 +545,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1805</v>
+        <v>1593</v>
       </c>
     </row>
     <row r="8" ht="27.75" customHeight="1">
@@ -566,7 +566,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>529</v>
+        <v>547</v>
       </c>
     </row>
     <row r="9" ht="27" customHeight="1">
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221</v>
+        <v>206</v>
       </c>
     </row>
     <row r="10" ht="27" customHeight="1">
@@ -612,7 +612,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="11" ht="14.25" customHeight="1">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>353</v>
+        <v>350</v>
       </c>
     </row>
     <row r="12" ht="14.25" customHeight="1">
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>267</v>
+        <v>270</v>
       </c>
     </row>
     <row r="13" ht="27" customHeight="1">
@@ -740,7 +740,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>462</v>
+        <v>355</v>
       </c>
     </row>
     <row r="17" ht="14.25" customHeight="1">
@@ -797,7 +797,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -827,7 +827,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2000</v>
+        <v>1995</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>600</v>
+        <v>590</v>
       </c>
     </row>
     <row r="20" ht="14.25" customHeight="1">
@@ -888,7 +888,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>9999</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="21" ht="14.25" customHeight="1">
@@ -938,7 +938,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1358</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="25" ht="27.75" customHeight="1">
@@ -1035,7 +1035,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>653</v>
+        <v>612</v>
       </c>
     </row>
     <row r="26" ht="14.25" customHeight="1">
@@ -1060,7 +1060,7 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4497</v>
+        <v>4431</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="29" ht="14.25" customHeight="1">
@@ -1150,7 +1150,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>675</v>
+        <v>640</v>
       </c>
     </row>
     <row r="34" ht="14.25" customHeight="1">
@@ -1363,7 +1363,7 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>343</v>
+        <v>333</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -1403,7 +1403,7 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>698</v>
+        <v>706</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -1446,7 +1446,7 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="38" ht="14.25" customHeight="1">
@@ -1471,7 +1471,7 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5218</v>
+        <v>5263</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5179</v>
+        <v>5181</v>
       </c>
     </row>
     <row r="40" ht="14.25" customHeight="1">
@@ -1536,7 +1536,7 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>72</v>
+        <v>60</v>
       </c>
     </row>
     <row r="41" ht="14.25" customHeight="1">
@@ -1561,7 +1561,7 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>343</v>
+        <v>352</v>
       </c>
     </row>
     <row r="42" ht="27.75" customHeight="1">
@@ -1607,7 +1607,7 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2158</v>
+        <v>2155</v>
       </c>
     </row>
     <row r="44" ht="14.25" customHeight="1">
@@ -1632,7 +1632,7 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>969</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="45" ht="27" customHeight="1">
@@ -1657,7 +1657,7 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1534</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="46" ht="14.25" customHeight="1">
@@ -1682,7 +1682,7 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1194</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="47" ht="14.25" customHeight="1">
@@ -1707,7 +1707,7 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>605</v>
+        <v>566</v>
       </c>
     </row>
     <row r="48" ht="14.25" customHeight="1">
@@ -1728,11 +1728,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49" ht="14.25" customHeight="1">
@@ -1757,7 +1757,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>695</v>
+        <v>615</v>
       </c>
     </row>
     <row r="50" ht="14.25" customHeight="1">
@@ -1807,7 +1807,7 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>843</v>
+        <v>822</v>
       </c>
     </row>
     <row r="52" ht="14.25" customHeight="1">
@@ -1849,7 +1849,7 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>250</v>
+        <v>360</v>
       </c>
     </row>
     <row r="54" ht="27" customHeight="1">
@@ -1895,7 +1895,7 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2000</v>
+        <v>1967</v>
       </c>
     </row>
     <row r="56" ht="14.25" customHeight="1">
@@ -1920,7 +1920,7 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1161</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="57" ht="14.25" customHeight="1">
@@ -1941,7 +1941,7 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>639</v>
+        <v>657</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>8104</v>
+        <v>7605</v>
       </c>
     </row>
     <row r="59" ht="14.25" customHeight="1">
@@ -1992,7 +1992,7 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="60" ht="27" customHeight="1">
@@ -2038,7 +2038,7 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>371</v>
+        <v>385</v>
       </c>
     </row>
     <row r="62" ht="14.25" customHeight="1">
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1111</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="63" ht="27" customHeight="1">
@@ -2088,7 +2088,7 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>457</v>
+        <v>387</v>
       </c>
     </row>
     <row r="64" ht="14.25" customHeight="1">
@@ -2113,7 +2113,7 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1320</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="65" ht="27.75" customHeight="1">
@@ -2138,7 +2138,7 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>425</v>
+        <v>429</v>
       </c>
     </row>
     <row r="66" ht="14.25" customHeight="1">
@@ -2180,7 +2180,7 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>367</v>
+        <v>358</v>
       </c>
     </row>
     <row r="68" ht="27" customHeight="1">
@@ -2205,7 +2205,7 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>453</v>
+        <v>391</v>
       </c>
     </row>
     <row r="69" ht="14.25" customHeight="1">
@@ -2251,7 +2251,7 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="71" ht="14.25" customHeight="1">
@@ -2276,7 +2276,7 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>126</v>
+        <v>121</v>
       </c>
     </row>
     <row r="72" ht="14.25" customHeight="1">
@@ -2301,7 +2301,7 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>33</v>
+        <v>21</v>
       </c>
     </row>
     <row r="73" ht="14.25" customHeight="1">
@@ -2322,7 +2322,7 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>74</v>
+        <v>68</v>
       </c>
     </row>
     <row r="74" ht="14.25" customHeight="1">
@@ -2347,7 +2347,7 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>950</v>
+        <v>863</v>
       </c>
     </row>
     <row r="75" ht="14.25" customHeight="1">
@@ -2368,7 +2368,7 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="76" ht="27" customHeight="1">
@@ -2414,7 +2414,7 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
     <row r="78" ht="14.25" customHeight="1">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>195</v>
+        <v>192</v>
       </c>
     </row>
     <row r="80" ht="27.75" customHeight="1">
@@ -2485,7 +2485,7 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="81" ht="14.25" customHeight="1">
@@ -2510,7 +2510,7 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>125</v>
+        <v>237</v>
       </c>
     </row>
     <row r="82" ht="14.25" customHeight="1">
@@ -2535,7 +2535,7 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>4497</v>
+        <v>4431</v>
       </c>
     </row>
     <row r="83" ht="14.25" customHeight="1">
@@ -2586,7 +2586,7 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1867</v>
+        <v>1868</v>
       </c>
     </row>
     <row r="85" ht="14.25" customHeight="1">
@@ -2611,7 +2611,7 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1968</v>
+        <v>1914</v>
       </c>
     </row>
     <row r="86" ht="14.25" customHeight="1">
@@ -2632,7 +2632,7 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>36</v>
+        <v>320</v>
       </c>
     </row>
     <row r="87" ht="27.75" customHeight="1">
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>389</v>
+        <v>400</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
@@ -2729,7 +2729,7 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="91" ht="14.25" customHeight="1">
@@ -2775,7 +2775,7 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>684</v>
+        <v>712</v>
       </c>
     </row>
     <row r="93" ht="27" customHeight="1">
@@ -2800,7 +2800,7 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="94" ht="27" customHeight="1">
@@ -2825,7 +2825,7 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>2858</v>
+        <v>2849</v>
       </c>
     </row>
     <row r="95" ht="14.25" customHeight="1">
@@ -2850,7 +2850,7 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>3355</v>
+        <v>3344</v>
       </c>
     </row>
     <row r="96" ht="27" customHeight="1">
@@ -2888,11 +2888,11 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>217</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98" ht="14.25" customHeight="1">
@@ -2917,7 +2917,7 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>977</v>
+        <v>960</v>
       </c>
     </row>
     <row r="99" ht="14.25" customHeight="1">
@@ -2963,7 +2963,7 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>5893</v>
+        <v>5864</v>
       </c>
       <c r="H100" t="inlineStr">
         <is>
@@ -3023,7 +3023,7 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="103" ht="14.25" customHeight="1">
@@ -3090,7 +3090,7 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>576</v>
+        <v>558</v>
       </c>
     </row>
     <row r="106" ht="27" customHeight="1">
@@ -3115,7 +3115,7 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>325</v>
+        <v>301</v>
       </c>
     </row>
     <row r="107" ht="14.25" customHeight="1">
@@ -3140,7 +3140,7 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>219</v>
+        <v>216</v>
       </c>
     </row>
     <row r="108" ht="14.25" customHeight="1">
@@ -3165,7 +3165,7 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>219</v>
+        <v>216</v>
       </c>
     </row>
     <row r="109" ht="14.25" customHeight="1">
@@ -3190,7 +3190,7 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>2152</v>
+        <v>2151</v>
       </c>
     </row>
     <row r="110" ht="27" customHeight="1">
@@ -3215,7 +3215,7 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>327</v>
+        <v>331</v>
       </c>
     </row>
     <row r="111" ht="14.25" customHeight="1">
@@ -3240,7 +3240,7 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>1183</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="112" ht="14.25" customHeight="1">
@@ -3311,7 +3311,7 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>192</v>
+        <v>195</v>
       </c>
     </row>
     <row r="115" ht="14.25" customHeight="1">
@@ -3357,7 +3357,7 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>2131</v>
+        <v>2140</v>
       </c>
     </row>
     <row r="117" ht="14.25" customHeight="1">
@@ -3378,7 +3378,7 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>3718</v>
+        <v>3722</v>
       </c>
     </row>
     <row r="118" ht="14.25" customHeight="1">
@@ -3449,7 +3449,7 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="121" ht="41.25" customHeight="1">
@@ -3495,7 +3495,7 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>205</v>
+        <v>199</v>
       </c>
     </row>
     <row r="123" ht="14.25" customHeight="1">
@@ -3516,7 +3516,7 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="124" ht="27" customHeight="1">
@@ -3537,7 +3537,7 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>447</v>
+        <v>423</v>
       </c>
     </row>
     <row r="125" ht="14.25" customHeight="1">
@@ -3562,7 +3562,7 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>175</v>
+        <v>171</v>
       </c>
     </row>
     <row r="126" ht="14.25" customHeight="1">
@@ -3583,7 +3583,7 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="127" ht="27" customHeight="1">
@@ -3608,7 +3608,7 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>72</v>
+        <v>64</v>
       </c>
     </row>
     <row r="128" ht="14.25" customHeight="1">
@@ -3629,7 +3629,7 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>822</v>
+        <v>752</v>
       </c>
     </row>
     <row r="129" ht="27" customHeight="1">
@@ -3654,7 +3654,7 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="130" ht="27" customHeight="1">
@@ -3696,7 +3696,7 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>178</v>
+        <v>183</v>
       </c>
     </row>
     <row r="132" ht="14.25" customHeight="1">
@@ -3721,7 +3721,7 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="133" ht="14.25" customHeight="1">
@@ -3742,7 +3742,7 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="134" ht="54.75" customHeight="1">
@@ -3767,7 +3767,7 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>248</v>
+        <v>254</v>
       </c>
     </row>
     <row r="135" ht="27.75" customHeight="1">
@@ -3792,7 +3792,7 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="136" ht="14.25" customHeight="1">
@@ -3817,7 +3817,7 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="137" ht="14.25" customHeight="1">
@@ -3838,7 +3838,7 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="138" ht="14.25" customHeight="1">
@@ -3909,7 +3909,7 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>447</v>
+        <v>454</v>
       </c>
     </row>
     <row r="141" ht="14.25" customHeight="1">
@@ -3934,7 +3934,7 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>72</v>
+        <v>66</v>
       </c>
     </row>
     <row r="142" ht="14.25" customHeight="1">
@@ -4001,7 +4001,7 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>720</v>
+        <v>738</v>
       </c>
     </row>
     <row r="145" ht="14.25" customHeight="1">
@@ -4051,7 +4051,7 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>892</v>
+        <v>890</v>
       </c>
     </row>
     <row r="147" ht="14.25" customHeight="1">
@@ -4076,7 +4076,7 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="148" ht="14.25" customHeight="1">
@@ -4176,7 +4176,7 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>368</v>
+        <v>361</v>
       </c>
     </row>
     <row r="152" ht="41.25" customHeight="1">
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>1996</v>
+        <v>1998</v>
       </c>
     </row>
     <row r="153" ht="14.25" customHeight="1">
@@ -4226,7 +4226,7 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="154" ht="14.25" customHeight="1">
@@ -4251,7 +4251,7 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>343</v>
+        <v>339</v>
       </c>
     </row>
     <row r="155" ht="14.25" customHeight="1">
@@ -4276,7 +4276,7 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>48</v>
+        <v>10</v>
       </c>
     </row>
     <row r="156" ht="14.25" customHeight="1">
@@ -4301,7 +4301,7 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="157" ht="14.25" customHeight="1">
@@ -4326,7 +4326,7 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="158" ht="14.25" customHeight="1">
@@ -4372,7 +4372,7 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="160" ht="14.25" customHeight="1">
@@ -4397,7 +4397,7 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="161" ht="14.25" customHeight="1">
@@ -4418,7 +4418,7 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>4992</v>
+        <v>5010</v>
       </c>
     </row>
     <row r="162" ht="14.25" customHeight="1">
@@ -4443,7 +4443,7 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
     </row>
     <row r="163" ht="14.25" customHeight="1">
@@ -4468,7 +4468,7 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>1619</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="164" ht="14.25" customHeight="1">
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>1300</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="165" ht="14.25" customHeight="1">
@@ -4518,7 +4518,7 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>331</v>
+        <v>313</v>
       </c>
     </row>
     <row r="166" ht="14.25" customHeight="1">
@@ -4538,7 +4538,7 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>385</v>
+        <v>346</v>
       </c>
       <c r="H166" t="inlineStr">
         <is>
@@ -4568,7 +4568,7 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="168">
@@ -4613,7 +4613,7 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="170">
@@ -4658,7 +4658,7 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="H171" t="inlineStr">
         <is>
@@ -4728,7 +4728,7 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="175">
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="177">
@@ -4848,7 +4848,7 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="180">
@@ -4868,7 +4868,7 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>338</v>
+        <v>3</v>
       </c>
       <c r="H180" t="inlineStr">
         <is>
@@ -4893,7 +4893,7 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="182">
@@ -4913,7 +4913,7 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>589</v>
+        <v>39</v>
       </c>
     </row>
     <row r="183">
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>1225</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="184">
@@ -4953,7 +4953,27 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>109</v>
+        <v>105</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>ISNetworld</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>https://www.isnetworld.com/en/careers#jobs</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="E185" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/config/companies.xlsx
+++ b/config/companies.xlsx
@@ -2,53 +2,36 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13992" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Company Job Sources" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
-      <charset val="1"/>
+      <family val="2"/>
+      <color theme="1"/>
       <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <charset val="1"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <charset val="1"/>
-      <color theme="10"/>
-      <sz val="11"/>
-      <u val="single"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F4E78"/>
-        <bgColor rgb="FF003366"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -60,105 +43,74 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <font>
-        <color rgb="FF7F6000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFF2CC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF375623"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFE2F0D9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
-      <rgbColor rgb="FF000000"/>
-      <rgbColor rgb="FFFFFFFF"/>
-      <rgbColor rgb="FFFF0000"/>
-      <rgbColor rgb="FF00FF00"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008000"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FF7F6000"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FFC0C0C0"/>
-      <rgbColor rgb="FF808080"/>
-      <rgbColor rgb="FF9999FF"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFFF2CC"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FF660066"/>
-      <rgbColor rgb="FFFF8080"/>
-      <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFCCCCFF"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFE2F0D9"/>
-      <rgbColor rgb="FFFFFF99"/>
-      <rgbColor rgb="FF99CCFF"/>
-      <rgbColor rgb="FFFF99CC"/>
-      <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFFCC99"/>
-      <rgbColor rgb="FF3366FF"/>
-      <rgbColor rgb="FF33CCCC"/>
-      <rgbColor rgb="FF99CC00"/>
-      <rgbColor rgb="FFFFCC00"/>
-      <rgbColor rgb="FFFF9900"/>
-      <rgbColor rgb="FFFF6600"/>
-      <rgbColor rgb="FF666699"/>
-      <rgbColor rgb="FF969696"/>
-      <rgbColor rgb="FF003366"/>
-      <rgbColor rgb="FF339966"/>
-      <rgbColor rgb="FF003300"/>
-      <rgbColor rgb="FF333300"/>
-      <rgbColor rgb="FF993300"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FF1F4E78"/>
-      <rgbColor rgb="FF375623"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
       <rgbColor rgb="00003366"/>
       <rgbColor rgb="00339966"/>
       <rgbColor rgb="00003300"/>
@@ -172,180 +124,280 @@
 </styleSheet>
 </file>
 
-<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="CompanyJobSourcesTable" displayName="CompanyJobSourcesTable" ref="A1:C181" headerRowCount="1" totalsRowShown="0">
-  <autoFilter ref="A1:C181"/>
-  <tableColumns count="3">
-    <tableColumn id="1" name="Company"/>
-    <tableColumn id="2" name="ATS URL"/>
-    <tableColumn id="3" name="Live Jobs Page (if ATS URL unavailable)"/>
-  </tableColumns>
-  <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="ChatGPT">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="ChatGPT">
+    <a:clrScheme name="Office">
       <a:dk1>
-        <a:srgbClr val="000000"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="FFFFFF"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="0E2841"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E8E8E8"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="156082"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="E97132"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="196B24"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="0F9ED5"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="A02B93"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="4EA72E"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="467886"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="96607D"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light"/>
-        <a:ea typeface="Calibri Light"/>
-        <a:cs typeface="Calibri Light"/>
+        <a:latin typeface="Cambria"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
-        <a:ea typeface="Calibri"/>
-        <a:cs typeface="Calibri"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme>
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="67000"/>
-                <a:lumMod val="110000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="35000">
               <a:schemeClr val="phClr">
-                <a:tint val="73000"/>
-                <a:lumMod val="105000"/>
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="81000"/>
-                <a:lumMod val="105000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="94000"/>
-                <a:lumMod val="102000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="80000">
               <a:schemeClr val="phClr">
-                <a:shade val="100000"/>
-                <a:lumMod val="100000"/>
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="78000"/>
-                <a:lumMod val="99000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="12700">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="19050">
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="25400">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="40000">
               <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
@@ -362,24 +414,20 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:H185"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.68359375" defaultRowHeight="14.4"/>
-  <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="52" customWidth="1" min="2" max="3"/>
-  </cols>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" ht="13.5" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Company</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>ATS URL</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Live Jobs Page (if ATS URL unavailable)</t>
         </is>
@@ -410,269 +458,278 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="27" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="2">
+      <c r="A2" t="inlineStr">
         <is>
           <t>JPMorgan Chase</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>https://jpmc.fa.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1001/requisitions</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>https://careers.jpmorgan.com/</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="D2" t="b">
+        <v>1</v>
       </c>
       <c r="E2" t="n">
         <v>6987</v>
       </c>
-    </row>
-    <row r="3" ht="27.75" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
         <is>
           <t>Capital One</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>https://capitalone.wd12.myworkdayjobs.com/en-US/Capital_One/</t>
         </is>
       </c>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="b">
+        <v>1</v>
       </c>
       <c r="E3" t="n">
         <v>1848</v>
       </c>
-    </row>
-    <row r="4" ht="14.25" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Bank of America</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>https://ghr.wd1.myworkdayjobs.com/en-US/Lateral-US/</t>
         </is>
       </c>
-      <c r="C4" s="2" t="n"/>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="b">
+        <v>1</v>
       </c>
       <c r="E4" t="n">
         <v>2095</v>
       </c>
-    </row>
-    <row r="5" ht="14.25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Goldman Sachs</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>https://higher.gs.com/results</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>https://www.goldmansachs.com/careers/</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="D5" t="b">
+        <v>1</v>
       </c>
       <c r="E5" t="n">
         <v>820</v>
       </c>
-    </row>
-    <row r="6" ht="27" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Morgan Stanley</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>https://ms.wd5.myworkdayjobs.com/External</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>https://www.morganstanley.com/careers/career-opportunities-search</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="D6" t="b">
+        <v>1</v>
       </c>
       <c r="E6" t="n">
         <v>1315</v>
       </c>
-    </row>
-    <row r="7" ht="27.75" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Wells Fargo</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>https://wf.wd1.myworkdayjobs.com/en-US/WellsFargoJobs/</t>
         </is>
       </c>
-      <c r="C7" s="2" t="n"/>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="b">
+        <v>1</v>
       </c>
       <c r="E7" t="n">
         <v>1593</v>
       </c>
-    </row>
-    <row r="8" ht="27.75" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Fidelity Investments</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>https://fmr.wd1.myworkdayjobs.com/en-US/FidelityCareers/</t>
         </is>
       </c>
-      <c r="C8" s="2" t="n"/>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="b">
+        <v>1</v>
       </c>
       <c r="E8" t="n">
         <v>547</v>
       </c>
-    </row>
-    <row r="9" ht="27" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>Liberty Mutual</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>https://libertymutual.eightfold.ai/careers?query=Data%20Engineer&amp;domain=libertymutual.com</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>https://jobs.libertymutualgroup.com/locations/plano-tx/</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="D9" t="b">
+        <v>1</v>
       </c>
       <c r="E9" t="n">
         <v>206</v>
       </c>
-    </row>
-    <row r="10" ht="27" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>Texas Capital Bank</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>https://texascapitalbank.wd12.myworkdayjobs.com/en-US/Careers/</t>
         </is>
       </c>
-      <c r="C10" s="2" t="n"/>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="b">
+        <v>1</v>
       </c>
       <c r="E10" t="n">
         <v>84</v>
       </c>
-    </row>
-    <row r="11" ht="14.25" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>Travelers</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>https://travelers.wd5.myworkdayjobs.com/en-US/External/</t>
         </is>
       </c>
-      <c r="C11" s="2" t="n"/>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="b">
+        <v>1</v>
       </c>
       <c r="E11" t="n">
         <v>350</v>
       </c>
-    </row>
-    <row r="12" ht="14.25" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>GEICO</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>https://geico.wd1.myworkdayjobs.com/en-US/External/</t>
         </is>
       </c>
-      <c r="C12" s="2" t="n"/>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="b">
+        <v>1</v>
       </c>
       <c r="E12" t="n">
         <v>270</v>
       </c>
-    </row>
-    <row r="13" ht="27" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>Texans Credit Union</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>https://recruiting.paylocity.com/recruiting/jobs/All/1934ff17-218d-4324-bec6-ecc4c5ddcfc4/Texans-Credit-Union</t>
         </is>
       </c>
-      <c r="C13" s="2" t="n"/>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="b">
+        <v>1</v>
       </c>
       <c r="E13" t="n">
         <v>18</v>
@@ -693,51 +750,50 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="27.75" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>Nasdaq</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>https://nasdaq.wd1.myworkdayjobs.com/Global_External_Site</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>https://www.nasdaq.com/about/careers</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="D14" t="b">
+        <v>1</v>
       </c>
       <c r="E14" t="n">
         <v>182</v>
       </c>
-    </row>
-    <row r="15" ht="27.75" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>Intercontinental Exchange / NYSE Texas</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>https://careers.ice.com/jobs</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>https://www.ice.com/careers</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="D15" t="b">
+        <v>1</v>
       </c>
       <c r="E15" t="n">
         <v>85</v>
@@ -758,73 +814,72 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="14.25" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Fiserv</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>https://careers.fiserv.com/us/en/search-results</t>
         </is>
       </c>
-      <c r="C16" s="2" t="n"/>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="b">
+        <v>1</v>
       </c>
       <c r="E16" t="n">
         <v>355</v>
       </c>
-    </row>
-    <row r="17" ht="14.25" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>FM</t>
         </is>
       </c>
-      <c r="B17" s="2" t="n"/>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr">
         <is>
           <t>https://careers.fm.com/</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="D17" t="b">
+        <v>1</v>
       </c>
       <c r="E17" t="n">
         <v>44</v>
       </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
           <t>2026-08-26: replaced dead ATS URL (careersatfm.com does not resolve) and dead live page (jobs.fm.com refuses connections) with careers.fm.com, verified returning 44 jobs.</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="27" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>T-Mobile</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>https://tmobile.wd1.myworkdayjobs.com/External/job/Henrietta-New-York/Account-Associate_REQ364623/apply</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>https://careers.t-mobile.com/jobs</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="D18" t="b">
+        <v>1</v>
       </c>
       <c r="E18" t="n">
         <v>1995</v>
@@ -845,97 +900,98 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="41.25" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Texas Instruments</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>https://edbz.fa.us2.oraclecloud.com/hcmRestApi/CandidateExperience/en/sites/CX/page/1001?statusCode=ORA_ACTIVE&amp;onlyData=true</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>https://careers.ti.com/</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="D19" t="b">
+        <v>1</v>
       </c>
       <c r="E19" t="n">
         <v>590</v>
       </c>
-    </row>
-    <row r="20" ht="14.25" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>https://www.amazon.jobs/en/</t>
         </is>
       </c>
-      <c r="C20" s="2" t="n"/>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="b">
+        <v>1</v>
       </c>
       <c r="E20" t="n">
         <v>10000</v>
       </c>
-    </row>
-    <row r="21" ht="14.25" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
         <is>
           <t>HCLTech</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>https://careers.hcltech.com/</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>https://www.hcltech.com/careers</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
+      <c r="D21" t="b">
+        <v>0</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" ht="14.25" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
           <t>Boingo Wireless</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>https://boards.greenhouse.io/boingo</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>https://app.jobzmall.com/boingo-wireless/jobs</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="D22" t="b">
+        <v>1</v>
       </c>
       <c r="E22" t="n">
         <v>4</v>
@@ -956,22 +1012,20 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="14.25" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
+    <row r="23">
+      <c r="A23" t="inlineStr">
         <is>
           <t>CommScope</t>
         </is>
       </c>
-      <c r="B23" s="2" t="n"/>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr">
         <is>
           <t>https://jobs.commscope.com/</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="D23" t="b">
+        <v>1</v>
       </c>
       <c r="E23" t="n">
         <v>38</v>
@@ -992,72 +1046,72 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="69" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t>Honeywell</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>https://ibqbjb.fa.ocs.oraclecloud.com/hcmRestApi/resources/latest/recruitingCEEvents?onlyData=true&amp;finder=findEvents;siteNumber=CX_1,limit=25,facetsList=START_DATES%3BLOCATIONS%3BEVENT_CATEGORIES%3BEVENT_FORMATS,keyword=%22Data%20Engineer%22,sortBy=RELEVANCY</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>https://careers.honeywell.com/</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="D24" t="b">
+        <v>1</v>
       </c>
       <c r="E24" t="n">
         <v>1338</v>
       </c>
-    </row>
-    <row r="25" ht="27.75" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>Boeing Global Services</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>https://boeing.wd1.myworkdayjobs.com/external_subsidiary/</t>
         </is>
       </c>
-      <c r="C25" s="2" t="n"/>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="b">
+        <v>1</v>
       </c>
       <c r="E25" t="n">
         <v>612</v>
       </c>
-    </row>
-    <row r="26" ht="14.25" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
         <is>
           <t>Collins Aerospace</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>https://careers.rtx.com/global/en/collins-aerospace</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>https://careers.rtx.com/global/en/collins-aerospace</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="D26" t="b">
+        <v>1</v>
       </c>
       <c r="E26" t="n">
         <v>4431</v>
@@ -1078,76 +1132,76 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="27.75" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
+    <row r="27">
+      <c r="A27" t="inlineStr">
         <is>
           <t>Genpact</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>https://genpact.wd108.myworkdayjobs.com/External_Careers</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>https://www.genpact.com/careers</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="D27" t="b">
+        <v>1</v>
       </c>
       <c r="E27" t="n">
         <v>2000</v>
       </c>
-    </row>
-    <row r="28" ht="14.25" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
         <is>
           <t>Yahoo</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>https://ouryahoo.wd5.myworkdayjobs.com/en-US/careers</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>https://www.yahooinc.com/careers/</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="D28" t="b">
+        <v>1</v>
       </c>
       <c r="E28" t="n">
         <v>88</v>
       </c>
-    </row>
-    <row r="29" ht="14.25" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
         <is>
           <t>Chewy</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>https://careers.chewy.com/us/en</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>https://careers.chewy.com/</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="D29" t="b">
+        <v>1</v>
       </c>
       <c r="E29" t="n">
         <v>240</v>
@@ -1168,22 +1222,20 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="14.25" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
+    <row r="30">
+      <c r="A30" t="inlineStr">
         <is>
           <t>PepsiCo / Frito-Lay North America</t>
         </is>
       </c>
-      <c r="B30" s="2" t="n"/>
-      <c r="C30" s="2" t="inlineStr">
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr">
         <is>
           <t>https://www.pepsicojobs.com/</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="D30" t="b">
+        <v>1</v>
       </c>
       <c r="E30" t="n">
         <v>10</v>
@@ -1204,26 +1256,24 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="41.25" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
+    <row r="31">
+      <c r="A31" t="inlineStr">
         <is>
           <t>FedEx</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>https://fedex.wd1.myworkdayjobs.com/FXE-MEISA-External/job/FXE-MEISAINDBOMHQBOMHQMumbai/Data-Analyst---Senior-II_RC781471-1/apply</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>https://careers.fedex.com/</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="D31" t="b">
+        <v>1</v>
       </c>
       <c r="E31" t="n">
         <v>46</v>
@@ -1244,22 +1294,20 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="27.75" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
+    <row r="32">
+      <c r="A32" t="inlineStr">
         <is>
           <t>Walmart</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>https://walmart.wd5.myworkdayjobs.com/WalmartExternal/</t>
         </is>
       </c>
-      <c r="C32" s="2" t="n"/>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="b">
+        <v>0</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
@@ -1280,47 +1328,46 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="27" customHeight="1">
-      <c r="A33" s="2" t="inlineStr">
+    <row r="33">
+      <c r="A33" t="inlineStr">
         <is>
           <t>Fluor</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>https://app.eightfold.ai/api/suggest?term=Data%20Engineer&amp;dictionary=job_search&amp;domain=fluor.com</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>https://www.fluor.com/careers/</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="D33" t="b">
+        <v>1</v>
       </c>
       <c r="E33" t="n">
         <v>640</v>
       </c>
-    </row>
-    <row r="34" ht="14.25" customHeight="1">
-      <c r="A34" s="2" t="inlineStr">
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
         <is>
           <t>Builders FirstSource</t>
         </is>
       </c>
-      <c r="B34" s="2" t="n"/>
-      <c r="C34" s="2" t="inlineStr">
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" t="inlineStr">
         <is>
           <t>https://careers.bldr.com/jobs</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="D34" t="b">
+        <v>1</v>
       </c>
       <c r="E34" t="n">
         <v>410</v>
@@ -1341,26 +1388,24 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="14.25" customHeight="1">
-      <c r="A35" s="2" t="inlineStr">
+    <row r="35">
+      <c r="A35" t="inlineStr">
         <is>
           <t>Commercial Metals Company (CMC)</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>https://jobs.cmc.com/</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>https://jobs.cmc.com/</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="D35" t="b">
+        <v>1</v>
       </c>
       <c r="E35" t="n">
         <v>333</v>
@@ -1381,26 +1426,24 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="54.75" customHeight="1">
-      <c r="A36" s="2" t="inlineStr">
+    <row r="36">
+      <c r="A36" t="inlineStr">
         <is>
           <t>Primoris Services</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>https://prim.wd108.myworkdayjobs.com/Primoris/</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>https://careers.prim.com/</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="D36" t="b">
+        <v>1</v>
       </c>
       <c r="E36" t="n">
         <v>706</v>
@@ -1415,7 +1458,7 @@
           <t>NOT FOUND</t>
         </is>
       </c>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="H36" t="inlineStr">
         <is>
           <t xml:space="preserve">none: browser stage failed: Page.goto: net::ERR_NAME_NOT_RESOLVED at https://careers.prim.com/
 Call log:
@@ -1424,51 +1467,50 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="27" customHeight="1">
-      <c r="A37" s="2" t="inlineStr">
+    <row r="37">
+      <c r="A37" t="inlineStr">
         <is>
           <t>Atmos Energy</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>https://atmosenergy.wd108.myworkdayjobs.com/External_Career_Site</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>https://www.atmosenergy.com/careers/</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="D37" t="b">
+        <v>1</v>
       </c>
       <c r="E37" t="n">
         <v>34</v>
       </c>
-    </row>
-    <row r="38" ht="14.25" customHeight="1">
-      <c r="A38" s="2" t="inlineStr">
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
         <is>
           <t>7-Eleven</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>https://careers.7-eleven.com/</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>https://careers.7-eleven.com/</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="D38" t="b">
+        <v>1</v>
       </c>
       <c r="E38" t="n">
         <v>5263</v>
@@ -1489,2964 +1531,3083 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="27" customHeight="1">
-      <c r="A39" s="2" t="inlineStr">
+    <row r="39">
+      <c r="A39" t="inlineStr">
         <is>
           <t>GameStop</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>https://gamestop.rec.pro.ukg.net/GAM1502GMSP/JobBoard/4a726edc-cff3-44d0-a230-bfeb9bb65328</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>https://careers.gamestop.com/us/en</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="D39" t="b">
+        <v>1</v>
       </c>
       <c r="E39" t="n">
         <v>5181</v>
       </c>
-    </row>
-    <row r="40" ht="14.25" customHeight="1">
-      <c r="A40" s="2" t="inlineStr">
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
         <is>
           <t>BNSF Railway</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>https://jobs.bnsf.com/us/en</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>https://jobs.bnsf.com/</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="D40" t="b">
+        <v>1</v>
       </c>
       <c r="E40" t="n">
         <v>60</v>
       </c>
-    </row>
-    <row r="41" ht="14.25" customHeight="1">
-      <c r="A41" s="2" t="inlineStr">
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
         <is>
           <t>Copart</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>https://copart.wd12.myworkdayjobs.com/Copart</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>https://www.copart.com/content/us/en/careers</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="D41" t="b">
+        <v>1</v>
       </c>
       <c r="E41" t="n">
         <v>352</v>
       </c>
-    </row>
-    <row r="42" ht="27.75" customHeight="1">
-      <c r="A42" s="2" t="inlineStr">
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
         <is>
           <t>Google</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>https://www.google.com/about/careers/applications/jobs/results/</t>
         </is>
       </c>
-      <c r="C42" s="2" t="n"/>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="b">
+        <v>1</v>
       </c>
       <c r="E42" t="n">
         <v>35</v>
       </c>
-    </row>
-    <row r="43" ht="41.25" customHeight="1">
-      <c r="A43" s="2" t="inlineStr">
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
         <is>
           <t>Oracle</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>https://eeho.fa.us2.oraclecloud.com/hcmRestApi/CandidateExperience/en/sites/CX_45001/page/125001?statusCode=ORA_ACTIVE&amp;onlyData=true</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>https://careers.oracle.com/</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="D43" t="b">
+        <v>1</v>
       </c>
       <c r="E43" t="n">
         <v>2155</v>
       </c>
-    </row>
-    <row r="44" ht="14.25" customHeight="1">
-      <c r="A44" s="2" t="inlineStr">
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
         <is>
           <t>IBM</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>https://www.ibm.com/careers/search</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>https://www.ibm.com/careers</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="D44" t="b">
+        <v>1</v>
       </c>
       <c r="E44" t="n">
         <v>1046</v>
       </c>
-    </row>
-    <row r="45" ht="27" customHeight="1">
-      <c r="A45" s="2" t="inlineStr">
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
         <is>
           <t>Salesforce</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>https://salesforce.wd12.myworkdayjobs.com/External_Career_Site</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
+      <c r="C45" t="inlineStr">
         <is>
           <t>https://careers.salesforce.com/</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="D45" t="b">
+        <v>1</v>
       </c>
       <c r="E45" t="n">
         <v>1479</v>
       </c>
-    </row>
-    <row r="46" ht="14.25" customHeight="1">
-      <c r="A46" s="2" t="inlineStr">
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
         <is>
           <t>Cisco</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>https://careers.cisco.com/global/en</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>https://jobs.cisco.com/</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="D46" t="b">
+        <v>1</v>
       </c>
       <c r="E46" t="n">
         <v>1235</v>
       </c>
-    </row>
-    <row r="47" ht="14.25" customHeight="1">
-      <c r="A47" s="2" t="inlineStr">
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
         <is>
           <t>Nokia</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t>https://jobs.nokia.com/en/sites/CX_1/jobs</t>
         </is>
       </c>
-      <c r="C47" s="2" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>https://www.nokia.com/about-us/careers/</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="D47" t="b">
+        <v>1</v>
       </c>
       <c r="E47" t="n">
         <v>566</v>
       </c>
-    </row>
-    <row r="48" ht="14.25" customHeight="1">
-      <c r="A48" s="2" t="inlineStr">
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
         <is>
           <t>Ericsson</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>https://jobs.ericsson.com/careers</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>https://www.ericsson.com/en/careers</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
+      <c r="D48" t="b">
+        <v>0</v>
       </c>
       <c r="E48" t="n">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" ht="14.25" customHeight="1">
-      <c r="A49" s="2" t="inlineStr">
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
         <is>
           <t>Samsung</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
+      <c r="B49" t="inlineStr">
         <is>
           <t>https://sec.wd3.myworkdayjobs.com/Samsung_Careers</t>
         </is>
       </c>
-      <c r="C49" s="2" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>https://www.samsungcareers.com/</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="D49" t="b">
+        <v>1</v>
       </c>
       <c r="E49" t="n">
         <v>615</v>
       </c>
-    </row>
-    <row r="50" ht="14.25" customHeight="1">
-      <c r="A50" s="2" t="inlineStr">
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
         <is>
           <t>Fujitsu</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="B50" t="inlineStr">
         <is>
           <t>https://www.jobs.global.fujitsu.com/</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
+      <c r="C50" t="inlineStr">
         <is>
           <t>https://www.fujitsu.com/global/about/careers/</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
+      <c r="D50" t="b">
+        <v>0</v>
       </c>
       <c r="E50" t="n">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" ht="14.25" customHeight="1">
-      <c r="A51" s="2" t="inlineStr">
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
         <is>
           <t>NTT DATA</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
+      <c r="B51" t="inlineStr">
         <is>
           <t>https://nttlimited.wd3.myworkdayjobs.com/NTT_Careers/job/Bangalore-India/Data-Engineer_R-136594/apply</t>
         </is>
       </c>
-      <c r="C51" s="2" t="inlineStr">
+      <c r="C51" t="inlineStr">
         <is>
           <t>https://www.nttdata.com/en-us/careers</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="D51" t="b">
+        <v>1</v>
       </c>
       <c r="E51" t="n">
         <v>822</v>
       </c>
-    </row>
-    <row r="52" ht="14.25" customHeight="1">
-      <c r="A52" s="2" t="inlineStr">
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
         <is>
           <t>Infosys</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="B52" t="inlineStr">
         <is>
           <t>https://www.infosys.com/careers/</t>
         </is>
       </c>
-      <c r="C52" s="2" t="n"/>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
+      <c r="C52" t="inlineStr"/>
+      <c r="D52" t="b">
+        <v>0</v>
       </c>
       <c r="E52" t="n">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" ht="14.25" customHeight="1">
-      <c r="A53" s="2" t="inlineStr">
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
         <is>
           <t>Cognizant</t>
         </is>
       </c>
-      <c r="B53" s="2" t="n"/>
-      <c r="C53" s="2" t="inlineStr">
+      <c r="B53" t="inlineStr"/>
+      <c r="C53" t="inlineStr">
         <is>
           <t>https://careers.cognizant.com/</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="D53" t="b">
+        <v>1</v>
       </c>
       <c r="E53" t="n">
         <v>360</v>
       </c>
-    </row>
-    <row r="54" ht="27" customHeight="1">
-      <c r="A54" s="2" t="inlineStr">
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
         <is>
           <t>Capgemini</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
+      <c r="B54" t="inlineStr">
         <is>
           <t>https://www.capgemini.com/us-en/careers/join-capgemini/job-search/</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr">
+      <c r="C54" t="inlineStr">
         <is>
           <t>https://www.capgemini.com/careers/</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="D54" t="b">
+        <v>1</v>
       </c>
       <c r="E54" t="n">
         <v>11</v>
       </c>
-    </row>
-    <row r="55" ht="27" customHeight="1">
-      <c r="A55" s="2" t="inlineStr">
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
         <is>
           <t>Accenture</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
+      <c r="B55" t="inlineStr">
         <is>
           <t>https://accenture.wd103.myworkdayjobs.com/en-US/AccentureCareers/</t>
         </is>
       </c>
-      <c r="C55" s="2" t="n"/>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="C55" t="inlineStr"/>
+      <c r="D55" t="b">
+        <v>1</v>
       </c>
       <c r="E55" t="n">
         <v>1967</v>
       </c>
-    </row>
-    <row r="56" ht="14.25" customHeight="1">
-      <c r="A56" s="2" t="inlineStr">
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
         <is>
           <t>Deloitte</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
+      <c r="B56" t="inlineStr">
         <is>
           <t>https://apply.deloitte.com/en_US/careers</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr">
+      <c r="C56" t="inlineStr">
         <is>
           <t>https://apply.deloitte.com/</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="D56" t="b">
+        <v>1</v>
       </c>
       <c r="E56" t="n">
         <v>1149</v>
       </c>
-    </row>
-    <row r="57" ht="14.25" customHeight="1">
-      <c r="A57" s="2" t="inlineStr">
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
         <is>
           <t>PwC</t>
         </is>
       </c>
-      <c r="B57" s="2" t="n"/>
-      <c r="C57" s="2" t="inlineStr">
+      <c r="B57" t="inlineStr"/>
+      <c r="C57" t="inlineStr">
         <is>
           <t>https://www.pwc.com/us/en/careers.html</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="D57" t="b">
+        <v>1</v>
       </c>
       <c r="E57" t="n">
         <v>657</v>
       </c>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr">
         <is>
           <t>2026-08-26: jobs.us.pwc.com fails TLS verification and 404s when that is ignored - the host is gone. Verified 43 jobs on the main careers page.</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="14.25" customHeight="1">
-      <c r="A58" s="2" t="inlineStr">
+    <row r="58">
+      <c r="A58" t="inlineStr">
         <is>
           <t>EY</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
+      <c r="B58" t="inlineStr">
         <is>
           <t>https://careers.ey.com/</t>
         </is>
       </c>
-      <c r="C58" s="2" t="inlineStr">
+      <c r="C58" t="inlineStr">
         <is>
           <t>https://careers.ey.com/</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="D58" t="b">
+        <v>1</v>
       </c>
       <c r="E58" t="n">
         <v>7605</v>
       </c>
-    </row>
-    <row r="59" ht="14.25" customHeight="1">
-      <c r="A59" s="2" t="inlineStr">
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
         <is>
           <t>KPMG</t>
         </is>
       </c>
-      <c r="B59" s="2" t="n"/>
-      <c r="C59" s="2" t="inlineStr">
+      <c r="B59" t="inlineStr"/>
+      <c r="C59" t="inlineStr">
         <is>
           <t>https://www.kpmguscareers.com/</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="D59" t="b">
+        <v>1</v>
       </c>
       <c r="E59" t="n">
         <v>6</v>
       </c>
-    </row>
-    <row r="60" ht="27" customHeight="1">
-      <c r="A60" s="2" t="inlineStr">
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
         <is>
           <t>CGI</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
+      <c r="B60" t="inlineStr">
         <is>
           <t>https://cgi.njoyn.com/corp/xweb/xweb.asp?NTKN=c&amp;clid=21001&amp;Page=joblisting</t>
         </is>
       </c>
-      <c r="C60" s="2" t="inlineStr">
+      <c r="C60" t="inlineStr">
         <is>
           <t>https://www.cgi.com/en/careers</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
+      <c r="D60" t="b">
+        <v>0</v>
       </c>
       <c r="E60" t="n">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" ht="14.25" customHeight="1">
-      <c r="A61" s="2" t="inlineStr">
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
         <is>
           <t>DXC Technology</t>
         </is>
       </c>
-      <c r="B61" s="2" t="n"/>
-      <c r="C61" s="2" t="inlineStr">
+      <c r="B61" t="inlineStr"/>
+      <c r="C61" t="inlineStr">
         <is>
           <t>https://careers.dxc.com/</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="D61" t="b">
+        <v>1</v>
       </c>
       <c r="E61" t="n">
         <v>385</v>
       </c>
-    </row>
-    <row r="62" ht="14.25" customHeight="1">
-      <c r="A62" s="2" t="inlineStr">
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
         <is>
           <t>Hewlett Packard Enterprise</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
+      <c r="B62" t="inlineStr">
         <is>
           <t>https://careers.hpe.com/us/en</t>
         </is>
       </c>
-      <c r="C62" s="2" t="inlineStr">
+      <c r="C62" t="inlineStr">
         <is>
           <t>https://careers.hpe.com/</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="D62" t="b">
+        <v>1</v>
       </c>
       <c r="E62" t="n">
         <v>1112</v>
       </c>
-    </row>
-    <row r="63" ht="27" customHeight="1">
-      <c r="A63" s="2" t="inlineStr">
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
         <is>
           <t>Dell Technologies</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
+      <c r="B63" t="inlineStr">
         <is>
           <t>https://enterpriseplatform.dell.com/hcmUI/CandidateExperience/en/sites/careers</t>
         </is>
       </c>
-      <c r="C63" s="2" t="inlineStr">
+      <c r="C63" t="inlineStr">
         <is>
           <t>https://jobs.dell.com/</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="D63" t="b">
+        <v>1</v>
       </c>
       <c r="E63" t="n">
         <v>387</v>
       </c>
-    </row>
-    <row r="64" ht="14.25" customHeight="1">
-      <c r="A64" s="2" t="inlineStr">
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
         <is>
           <t>Palo Alto Networks</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
+      <c r="B64" t="inlineStr">
         <is>
           <t>https://jobs.paloaltonetworks.com/en</t>
         </is>
       </c>
-      <c r="C64" s="2" t="inlineStr">
+      <c r="C64" t="inlineStr">
         <is>
           <t>https://jobs.paloaltonetworks.com/</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="D64" t="b">
+        <v>1</v>
       </c>
       <c r="E64" t="n">
         <v>1310</v>
       </c>
-    </row>
-    <row r="65" ht="27.75" customHeight="1">
-      <c r="A65" s="2" t="inlineStr">
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
         <is>
           <t>CrowdStrike</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
+      <c r="B65" t="inlineStr">
         <is>
           <t>https://crowdstrike.wd5.myworkdayjobs.com/crowdstrikecareers</t>
         </is>
       </c>
-      <c r="C65" s="2" t="inlineStr">
+      <c r="C65" t="inlineStr">
         <is>
           <t>https://www.crowdstrike.com/en-us/careers/</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="D65" t="b">
+        <v>1</v>
       </c>
       <c r="E65" t="n">
         <v>429</v>
       </c>
-    </row>
-    <row r="66" ht="14.25" customHeight="1">
-      <c r="A66" s="2" t="inlineStr">
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
         <is>
           <t>ServiceNow</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
+      <c r="B66" t="inlineStr">
         <is>
           <t>https://careers.smartrecruiters.com/ServiceNow</t>
         </is>
       </c>
-      <c r="C66" s="2" t="n"/>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="C66" t="inlineStr"/>
+      <c r="D66" t="b">
+        <v>1</v>
       </c>
       <c r="E66" t="n">
         <v>557</v>
       </c>
-    </row>
-    <row r="67" ht="14.25" customHeight="1">
-      <c r="A67" s="2" t="inlineStr">
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
         <is>
           <t>Workday</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
+      <c r="B67" t="inlineStr">
         <is>
           <t>https://workday.wd5.myworkdayjobs.com/Workday</t>
         </is>
       </c>
-      <c r="C67" s="2" t="n"/>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="C67" t="inlineStr"/>
+      <c r="D67" t="b">
+        <v>1</v>
       </c>
       <c r="E67" t="n">
         <v>358</v>
       </c>
-    </row>
-    <row r="68" ht="27" customHeight="1">
-      <c r="A68" s="2" t="inlineStr">
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
         <is>
           <t>Thomson Reuters</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
+      <c r="B68" t="inlineStr">
         <is>
           <t>https://thomsonreuters.wd5.myworkdayjobs.com/en-US/External_Career_Site</t>
         </is>
       </c>
-      <c r="C68" s="2" t="inlineStr">
+      <c r="C68" t="inlineStr">
         <is>
           <t>https://careers.thomsonreuters.com/</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="D68" t="b">
+        <v>1</v>
       </c>
       <c r="E68" t="n">
         <v>391</v>
       </c>
-    </row>
-    <row r="69" ht="14.25" customHeight="1">
-      <c r="A69" s="2" t="inlineStr">
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
         <is>
           <t>Tyler Technologies</t>
         </is>
       </c>
-      <c r="B69" s="2" t="n"/>
-      <c r="C69" s="2" t="inlineStr">
+      <c r="B69" t="inlineStr"/>
+      <c r="C69" t="inlineStr">
         <is>
           <t>https://www.tylertech.com/careers/job-listings</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="D69" t="b">
+        <v>1</v>
       </c>
       <c r="E69" t="n">
         <v>10</v>
       </c>
-    </row>
-    <row r="70" ht="14.25" customHeight="1">
-      <c r="A70" s="2" t="inlineStr">
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
         <is>
           <t>Alkami Technology</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
+      <c r="B70" t="inlineStr">
         <is>
           <t>https://alkami.wd12.myworkdayjobs.com/Alkami</t>
         </is>
       </c>
-      <c r="C70" s="2" t="inlineStr">
+      <c r="C70" t="inlineStr">
         <is>
           <t>https://www.alkami.com/careers/</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="D70" t="b">
+        <v>1</v>
       </c>
       <c r="E70" t="n">
         <v>70</v>
       </c>
-    </row>
-    <row r="71" ht="14.25" customHeight="1">
-      <c r="A71" s="2" t="inlineStr">
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
         <is>
           <t>Sabre</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
+      <c r="B71" t="inlineStr">
         <is>
           <t>https://sabre.wd1.myworkdayjobs.com/SabreJobs</t>
         </is>
       </c>
-      <c r="C71" s="2" t="inlineStr">
+      <c r="C71" t="inlineStr">
         <is>
           <t>https://careers.sabre.com/</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="D71" t="b">
+        <v>1</v>
       </c>
       <c r="E71" t="n">
         <v>121</v>
       </c>
-    </row>
-    <row r="72" ht="14.25" customHeight="1">
-      <c r="A72" s="2" t="inlineStr">
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
         <is>
           <t>Southwest Airlines</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
+      <c r="B72" t="inlineStr">
         <is>
           <t>https://careers.southwestair.com/us/en/</t>
         </is>
       </c>
-      <c r="C72" s="2" t="inlineStr">
+      <c r="C72" t="inlineStr">
         <is>
           <t>https://careers.southwestair.com/</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="D72" t="b">
+        <v>1</v>
       </c>
       <c r="E72" t="n">
         <v>21</v>
       </c>
-    </row>
-    <row r="73" ht="14.25" customHeight="1">
-      <c r="A73" s="2" t="inlineStr">
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
         <is>
           <t>American Airlines</t>
         </is>
       </c>
-      <c r="B73" s="2" t="n"/>
-      <c r="C73" s="2" t="inlineStr">
+      <c r="B73" t="inlineStr"/>
+      <c r="C73" t="inlineStr">
         <is>
           <t>https://jobs.aa.com/</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="D73" t="b">
+        <v>1</v>
       </c>
       <c r="E73" t="n">
         <v>68</v>
       </c>
-    </row>
-    <row r="74" ht="14.25" customHeight="1">
-      <c r="A74" s="2" t="inlineStr">
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
         <is>
           <t>Caterpillar</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
+      <c r="B74" t="inlineStr">
         <is>
           <t>https://cat.wd5.myworkdayjobs.com/en-US/CaterpillarCareers/job/Wujiang-Jiangsu/Digital-Information-Systems-Engineer_R0000375017/apply</t>
         </is>
       </c>
-      <c r="C74" s="2" t="inlineStr">
+      <c r="C74" t="inlineStr">
         <is>
           <t>https://careers.caterpillar.com/</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="D74" t="b">
+        <v>1</v>
       </c>
       <c r="E74" t="n">
         <v>863</v>
       </c>
-    </row>
-    <row r="75" ht="14.25" customHeight="1">
-      <c r="A75" s="2" t="inlineStr">
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
         <is>
           <t>Toyota North America</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
+      <c r="B75" t="inlineStr">
         <is>
           <t>https://toyota.wd503.myworkdayjobs.com/en-US/TMNA/</t>
         </is>
       </c>
-      <c r="C75" s="2" t="n"/>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="C75" t="inlineStr"/>
+      <c r="D75" t="b">
+        <v>1</v>
       </c>
       <c r="E75" t="n">
         <v>107</v>
       </c>
-    </row>
-    <row r="76" ht="27" customHeight="1">
-      <c r="A76" s="2" t="inlineStr">
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
         <is>
           <t>McKesson Technology</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
+      <c r="B76" t="inlineStr">
         <is>
           <t>https://mckesson.wd3.myworkdayjobs.com/en-US/External_Careers/</t>
         </is>
       </c>
-      <c r="C76" s="2" t="n"/>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="C76" t="inlineStr"/>
+      <c r="D76" t="b">
+        <v>1</v>
       </c>
       <c r="E76" t="n">
         <v>489</v>
       </c>
-    </row>
-    <row r="77" ht="14.25" customHeight="1">
-      <c r="A77" s="2" t="inlineStr">
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
         <is>
           <t>Cotality</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
+      <c r="B77" t="inlineStr">
         <is>
           <t>https://cotality.wd115.myworkdayjobs.com/Global</t>
         </is>
       </c>
-      <c r="C77" s="2" t="inlineStr">
+      <c r="C77" t="inlineStr">
         <is>
           <t>https://careers.cotality.com/</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="D77" t="b">
+        <v>1</v>
       </c>
       <c r="E77" t="n">
         <v>44</v>
       </c>
-    </row>
-    <row r="78" ht="14.25" customHeight="1">
-      <c r="A78" s="2" t="inlineStr">
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
         <is>
           <t>Equinix</t>
         </is>
       </c>
-      <c r="B78" s="2" t="n"/>
-      <c r="C78" s="2" t="inlineStr">
+      <c r="B78" t="inlineStr"/>
+      <c r="C78" t="inlineStr">
         <is>
           <t>https://careers.equinix.com/</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="D78" t="b">
+        <v>1</v>
       </c>
       <c r="E78" t="n">
         <v>39</v>
       </c>
-    </row>
-    <row r="79" ht="27" customHeight="1">
-      <c r="A79" s="2" t="inlineStr">
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
         <is>
           <t>Digital Realty</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
+      <c r="B79" t="inlineStr">
         <is>
           <t>https://hdep.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX</t>
         </is>
       </c>
-      <c r="C79" s="2" t="inlineStr">
+      <c r="C79" t="inlineStr">
         <is>
           <t>https://careers.digitalrealty.com/</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="D79" t="b">
+        <v>1</v>
       </c>
       <c r="E79" t="n">
         <v>192</v>
       </c>
-    </row>
-    <row r="80" ht="27.75" customHeight="1">
-      <c r="A80" s="2" t="inlineStr">
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
         <is>
           <t>CyrusOne</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
+      <c r="B80" t="inlineStr">
         <is>
           <t>https://cyrusone.wd1.myworkdayjobs.com/CyrusOneCareerPortal</t>
         </is>
       </c>
-      <c r="C80" s="2" t="inlineStr">
+      <c r="C80" t="inlineStr">
         <is>
           <t>https://www.cyrusone.com/careers</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="D80" t="b">
+        <v>1</v>
       </c>
       <c r="E80" t="n">
         <v>99</v>
       </c>
-    </row>
-    <row r="81" ht="14.25" customHeight="1">
-      <c r="A81" s="2" t="inlineStr">
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
         <is>
           <t>Qorvo</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
+      <c r="B81" t="inlineStr">
         <is>
           <t>https://careers.qorvo.com/</t>
         </is>
       </c>
-      <c r="C81" s="2" t="inlineStr">
+      <c r="C81" t="inlineStr">
         <is>
           <t>https://careers.qorvo.com/</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="D81" t="b">
+        <v>1</v>
       </c>
       <c r="E81" t="n">
         <v>237</v>
       </c>
-    </row>
-    <row r="82" ht="14.25" customHeight="1">
-      <c r="A82" s="2" t="inlineStr">
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
         <is>
           <t>RTX / Raytheon</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
+      <c r="B82" t="inlineStr">
         <is>
           <t>https://careers.rtx.com/global/en</t>
         </is>
       </c>
-      <c r="C82" s="2" t="inlineStr">
+      <c r="C82" t="inlineStr">
         <is>
           <t>https://careers.rtx.com/</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="D82" t="b">
+        <v>1</v>
       </c>
       <c r="E82" t="n">
         <v>4431</v>
       </c>
-    </row>
-    <row r="83" ht="14.25" customHeight="1">
-      <c r="A83" s="2" t="inlineStr">
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
         <is>
           <t>Lockheed Martin</t>
         </is>
       </c>
-      <c r="B83" s="2" t="n"/>
-      <c r="C83" s="2" t="inlineStr">
+      <c r="B83" t="inlineStr"/>
+      <c r="C83" t="inlineStr">
         <is>
           <t>https://lockheedmartin.eightfold.ai/careers</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="D83" t="b">
+        <v>1</v>
       </c>
       <c r="E83" t="n">
         <v>20</v>
       </c>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr"/>
       <c r="H83" t="inlineStr">
         <is>
           <t>2026-08-26: lockheedmartinjobs.com is a dead redirect stub (404 via lockheedmartin.com). Real board is the Eightfold tenant; its API answers 403 so the browser route is used. Verified 20 jobs.</t>
         </is>
       </c>
     </row>
-    <row r="84" ht="14.25" customHeight="1">
-      <c r="A84" s="2" t="inlineStr">
+    <row r="84">
+      <c r="A84" t="inlineStr">
         <is>
           <t>BAE Systems</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
+      <c r="B84" t="inlineStr">
         <is>
           <t>https://jobs.baesystems.com/global/en</t>
         </is>
       </c>
-      <c r="C84" s="2" t="inlineStr">
+      <c r="C84" t="inlineStr">
         <is>
           <t>https://jobs.baesystems.com/</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="D84" t="b">
+        <v>1</v>
       </c>
       <c r="E84" t="n">
         <v>1868</v>
       </c>
-    </row>
-    <row r="85" ht="14.25" customHeight="1">
-      <c r="A85" s="2" t="inlineStr">
+      <c r="F84" t="inlineStr"/>
+      <c r="G84" t="inlineStr"/>
+      <c r="H84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
         <is>
           <t>L3Harris</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
+      <c r="B85" t="inlineStr">
         <is>
           <t>https://careers.l3harris.com/en</t>
         </is>
       </c>
-      <c r="C85" s="2" t="inlineStr">
+      <c r="C85" t="inlineStr">
         <is>
           <t>https://careers.l3harris.com/</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="D85" t="b">
+        <v>1</v>
       </c>
       <c r="E85" t="n">
         <v>1914</v>
       </c>
-    </row>
-    <row r="86" ht="14.25" customHeight="1">
-      <c r="A86" s="2" t="inlineStr">
+      <c r="F85" t="inlineStr"/>
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
         <is>
           <t>Baylor Scott &amp; White Health</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
+      <c r="B86" t="inlineStr">
         <is>
           <t>https://bswhealth.taleo.net/careersection/ex/jobsearch.ftl</t>
         </is>
       </c>
-      <c r="C86" s="2" t="n"/>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="C86" t="inlineStr"/>
+      <c r="D86" t="b">
+        <v>1</v>
       </c>
       <c r="E86" t="n">
         <v>320</v>
       </c>
-    </row>
-    <row r="87" ht="27.75" customHeight="1">
-      <c r="A87" s="2" t="inlineStr">
+      <c r="F86" t="inlineStr"/>
+      <c r="G86" t="inlineStr"/>
+      <c r="H86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
         <is>
           <t>Texas Health Resources</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
+      <c r="B87" t="inlineStr">
         <is>
           <t>https://texashealth.taleo.net/careersection/ex3/moresearch.ftl</t>
         </is>
       </c>
-      <c r="C87" s="2" t="inlineStr">
+      <c r="C87" t="inlineStr">
         <is>
           <t>https://jobs.texashealth.org/</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="D87" t="b">
+        <v>1</v>
       </c>
       <c r="E87" t="n">
         <v>400</v>
       </c>
+      <c r="F87" t="inlineStr"/>
+      <c r="G87" t="inlineStr"/>
       <c r="H87" t="inlineStr">
         <is>
           <t>2026-08-26: the Taleo moresearch.ftl entry point returns 0 rows. The branded portal renders the same Taleo data and verified 391 jobs.</t>
         </is>
       </c>
     </row>
-    <row r="88" ht="14.25" customHeight="1">
-      <c r="A88" s="2" t="inlineStr">
+    <row r="88">
+      <c r="A88" t="inlineStr">
         <is>
           <t>UT Southwestern Medical Center</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
+      <c r="B88" t="inlineStr">
         <is>
           <t>https://utsw.referrals.selectminds.com/?lang=en</t>
         </is>
       </c>
-      <c r="C88" s="2" t="n"/>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="C88" t="inlineStr"/>
+      <c r="D88" t="b">
+        <v>1</v>
       </c>
       <c r="E88" t="n">
         <v>10</v>
       </c>
-    </row>
-    <row r="89" ht="14.25" customHeight="1">
-      <c r="A89" s="2" t="inlineStr">
+      <c r="F88" t="inlineStr"/>
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
         <is>
           <t>Medical City Healthcare / HCA</t>
         </is>
       </c>
-      <c r="B89" s="2" t="n"/>
-      <c r="C89" s="2" t="inlineStr">
+      <c r="B89" t="inlineStr"/>
+      <c r="C89" t="inlineStr">
         <is>
           <t>https://careers.hcahealthcare.com/</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
+      <c r="D89" t="b">
+        <v>0</v>
       </c>
       <c r="E89" t="n">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" ht="14.25" customHeight="1">
-      <c r="A90" s="2" t="inlineStr">
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
         <is>
           <t>Children’s Health</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
+      <c r="B90" t="inlineStr">
         <is>
           <t>https://jobsearch.childrens.com/</t>
         </is>
       </c>
-      <c r="C90" s="2" t="inlineStr">
+      <c r="C90" t="inlineStr">
         <is>
           <t>https://jobsearch.childrens.com/</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="D90" t="b">
+        <v>1</v>
       </c>
       <c r="E90" t="n">
         <v>189</v>
       </c>
-    </row>
-    <row r="91" ht="14.25" customHeight="1">
-      <c r="A91" s="2" t="inlineStr">
+      <c r="F90" t="inlineStr"/>
+      <c r="G90" t="inlineStr"/>
+      <c r="H90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
         <is>
           <t>Parkland Health</t>
         </is>
       </c>
-      <c r="B91" s="2" t="n"/>
-      <c r="C91" s="2" t="inlineStr">
+      <c r="B91" t="inlineStr"/>
+      <c r="C91" t="inlineStr">
         <is>
           <t>https://jobs.parklandcareers.com/</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="D91" t="b">
+        <v>1</v>
       </c>
       <c r="E91" t="n">
         <v>10</v>
       </c>
-    </row>
-    <row r="92" ht="27" customHeight="1">
-      <c r="A92" s="2" t="inlineStr">
+      <c r="F91" t="inlineStr"/>
+      <c r="G91" t="inlineStr"/>
+      <c r="H91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
         <is>
           <t>Methodist Health System</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
+      <c r="B92" t="inlineStr">
         <is>
           <t>https://methodisthealthsystem.wd1.myworkdayjobs.com/MHS_Careers</t>
         </is>
       </c>
-      <c r="C92" s="2" t="inlineStr">
+      <c r="C92" t="inlineStr">
         <is>
           <t>https://jobs.methodisthealthsystem.org/</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="D92" t="b">
+        <v>1</v>
       </c>
       <c r="E92" t="n">
         <v>712</v>
       </c>
-    </row>
-    <row r="93" ht="27" customHeight="1">
-      <c r="A93" s="2" t="inlineStr">
+      <c r="F92" t="inlineStr"/>
+      <c r="G92" t="inlineStr"/>
+      <c r="H92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
         <is>
           <t>Cook Children’s Health Care System</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
+      <c r="B93" t="inlineStr">
         <is>
           <t>https://cookchildrens.wd1.myworkdayjobs.com/Cook_Childrens_Careers?q=research</t>
         </is>
       </c>
-      <c r="C93" s="2" t="inlineStr">
+      <c r="C93" t="inlineStr">
         <is>
           <t>https://careers.cookchildrens.org/</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="D93" t="b">
+        <v>1</v>
       </c>
       <c r="E93" t="n">
         <v>253</v>
       </c>
-    </row>
-    <row r="94" ht="27" customHeight="1">
-      <c r="A94" s="2" t="inlineStr">
+      <c r="F93" t="inlineStr"/>
+      <c r="G93" t="inlineStr"/>
+      <c r="H93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
         <is>
           <t>Tenet Healthcare</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
+      <c r="B94" t="inlineStr">
         <is>
           <t>https://eodr.fa.us2.oraclecloud.com/fscmUI/redwood/internalmobility/opportunitymarketplace/search?optyType=JOB</t>
         </is>
       </c>
-      <c r="C94" s="2" t="inlineStr">
+      <c r="C94" t="inlineStr">
         <is>
           <t>https://jobs.tenethealth.com/</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="D94" t="b">
+        <v>1</v>
       </c>
       <c r="E94" t="n">
         <v>2849</v>
       </c>
-    </row>
-    <row r="95" ht="14.25" customHeight="1">
-      <c r="A95" s="2" t="inlineStr">
+      <c r="F94" t="inlineStr"/>
+      <c r="G94" t="inlineStr"/>
+      <c r="H94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
         <is>
           <t>Conifer Health Solutions</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
+      <c r="B95" t="inlineStr">
         <is>
           <t>https://jobs.tenethealth.com/conifer-health-solutions</t>
         </is>
       </c>
-      <c r="C95" s="2" t="inlineStr">
+      <c r="C95" t="inlineStr">
         <is>
           <t>https://jobs.tenethealth.com/conifer-health-solutions</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="D95" t="b">
+        <v>1</v>
       </c>
       <c r="E95" t="n">
         <v>3344</v>
       </c>
-    </row>
-    <row r="96" ht="27" customHeight="1">
-      <c r="A96" s="2" t="inlineStr">
+      <c r="F95" t="inlineStr"/>
+      <c r="G95" t="inlineStr"/>
+      <c r="H95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
         <is>
           <t>McKesson</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
+      <c r="B96" t="inlineStr">
         <is>
           <t>https://mckesson.wd3.myworkdayjobs.com/en-US/External_Careers/</t>
         </is>
       </c>
-      <c r="C96" s="2" t="n"/>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="C96" t="inlineStr"/>
+      <c r="D96" t="b">
+        <v>1</v>
       </c>
       <c r="E96" t="n">
         <v>489</v>
       </c>
-    </row>
-    <row r="97" ht="14.25" customHeight="1">
-      <c r="A97" s="2" t="inlineStr">
+      <c r="F96" t="inlineStr"/>
+      <c r="G96" t="inlineStr"/>
+      <c r="H96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
         <is>
           <t>Vizient</t>
         </is>
       </c>
-      <c r="B97" s="2" t="n"/>
-      <c r="C97" s="2" t="inlineStr">
+      <c r="B97" t="inlineStr"/>
+      <c r="C97" t="inlineStr">
         <is>
           <t>https://careers.vizientinc.com/</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
+      <c r="D97" t="b">
+        <v>0</v>
       </c>
       <c r="E97" t="n">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" ht="14.25" customHeight="1">
-      <c r="A98" s="2" t="inlineStr">
+      <c r="F97" t="inlineStr"/>
+      <c r="G97" t="inlineStr"/>
+      <c r="H97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
         <is>
           <t>Cencora</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
+      <c r="B98" t="inlineStr">
         <is>
           <t>https://careers.cencora.com/us/en</t>
         </is>
       </c>
-      <c r="C98" s="2" t="inlineStr">
+      <c r="C98" t="inlineStr">
         <is>
           <t>https://careers.cencora.com/</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="D98" t="b">
+        <v>1</v>
       </c>
       <c r="E98" t="n">
         <v>960</v>
       </c>
-    </row>
-    <row r="99" ht="14.25" customHeight="1">
-      <c r="A99" s="2" t="inlineStr">
+      <c r="F98" t="inlineStr"/>
+      <c r="G98" t="inlineStr"/>
+      <c r="H98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
         <is>
           <t>Cardinal Health</t>
         </is>
       </c>
-      <c r="B99" s="2" t="n"/>
-      <c r="C99" s="2" t="inlineStr">
+      <c r="B99" t="inlineStr"/>
+      <c r="C99" t="inlineStr">
         <is>
           <t>https://jobs.cardinalhealth.com/</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="D99" t="b">
+        <v>1</v>
       </c>
       <c r="E99" t="n">
         <v>6</v>
       </c>
-    </row>
-    <row r="100" ht="14.25" customHeight="1">
-      <c r="A100" s="2" t="inlineStr">
+      <c r="F99" t="inlineStr"/>
+      <c r="G99" t="inlineStr"/>
+      <c r="H99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
         <is>
           <t>CVS Health / Aetna</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
+      <c r="B100" t="inlineStr">
         <is>
           <t>https://cvshealth.wd1.myworkdayjobs.com/en-US/CVS_Health_Careers</t>
         </is>
       </c>
-      <c r="C100" s="2" t="inlineStr">
+      <c r="C100" t="inlineStr">
         <is>
           <t>https://jobs.cvshealth.com/us/en</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="D100" t="b">
+        <v>1</v>
       </c>
       <c r="E100" t="n">
         <v>5864</v>
       </c>
+      <c r="F100" t="inlineStr"/>
+      <c r="G100" t="inlineStr"/>
       <c r="H100" t="inlineStr">
         <is>
           <t>2026-08-26: moved off the Phenom board (jobs.cvshealth.com) to the Workday tenant its own applyUrl links to. Phenom served this tenant in relevance order - measured, offset 0 held a 12 Jun posting and offset 7,990 one from 24 Aug - so its 8,000-row ceiling hid jobs of every age including current ones. Workday CXS is posting-date descending (offset 0 'Posted Today', 6,000 '9 Days Ago', 12,000 '23 Days Ago'), so the walk stops at the freshness window instead: 6,777 jobs in 220s, oldest 12 days, vs 8,000 in 432s.</t>
         </is>
       </c>
     </row>
-    <row r="101" ht="14.25" customHeight="1">
-      <c r="A101" s="2" t="inlineStr">
+    <row r="101">
+      <c r="A101" t="inlineStr">
         <is>
           <t>Signify Health</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
+      <c r="B101" t="inlineStr">
         <is>
           <t>https://jobs.cvshealth.com/us/en/signify-health</t>
         </is>
       </c>
-      <c r="C101" s="2" t="inlineStr">
+      <c r="C101" t="inlineStr">
         <is>
           <t>https://www.signifyhealth.com/careers</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="D101" t="b">
+        <v>1</v>
       </c>
       <c r="E101" t="n">
         <v>8000</v>
       </c>
+      <c r="F101" t="inlineStr"/>
+      <c r="G101" t="inlineStr"/>
       <c r="H101" t="inlineStr">
         <is>
           <t>2026-08-26: DUPLICATE OF CVS. signifyhealth.com/careers redirects to jobs.cvshealth.com/us/en/signify-health, and that sub-path has no board of its own - the search endpoint ignores it and returns CVS's full 19,126, so this row scrapes CVS's board a second time (~430s) and files the result under the wrong employer. There is no Signify site on the CVS Workday tenant either (Signify_Health / SignifyHealth / Signify_Health_Careers all 404). Consider removing this row.</t>
         </is>
       </c>
     </row>
-    <row r="102" ht="27" customHeight="1">
-      <c r="A102" s="2" t="inlineStr">
+    <row r="102">
+      <c r="A102" t="inlineStr">
         <is>
           <t>Blue Cross and Blue Shield of Texas / HCSC</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
+      <c r="B102" t="inlineStr">
         <is>
           <t>https://hcsc.wd1.myworkdayjobs.com/HCSC_External/login</t>
         </is>
       </c>
-      <c r="C102" s="2" t="inlineStr">
+      <c r="C102" t="inlineStr">
         <is>
           <t>https://careers.hcsc.com/</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="D102" t="b">
+        <v>1</v>
       </c>
       <c r="E102" t="n">
         <v>114</v>
       </c>
-    </row>
-    <row r="103" ht="14.25" customHeight="1">
-      <c r="A103" s="2" t="inlineStr">
+      <c r="F102" t="inlineStr"/>
+      <c r="G102" t="inlineStr"/>
+      <c r="H102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
         <is>
           <t>UnitedHealth Group</t>
         </is>
       </c>
-      <c r="B103" s="2" t="n"/>
-      <c r="C103" s="2" t="inlineStr">
+      <c r="B103" t="inlineStr"/>
+      <c r="C103" t="inlineStr">
         <is>
           <t>https://careers.unitedhealthgroup.com/</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="D103" t="b">
+        <v>1</v>
       </c>
       <c r="E103" t="n">
         <v>18</v>
       </c>
-    </row>
-    <row r="104" ht="27" customHeight="1">
-      <c r="A104" s="2" t="inlineStr">
+      <c r="F103" t="inlineStr"/>
+      <c r="G103" t="inlineStr"/>
+      <c r="H103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
         <is>
           <t>Optum</t>
         </is>
       </c>
-      <c r="B104" s="2" t="n"/>
-      <c r="C104" s="2" t="inlineStr">
+      <c r="B104" t="inlineStr"/>
+      <c r="C104" t="inlineStr">
         <is>
           <t>https://careers.unitedhealthgroup.com/job-search-results/?brand=Optum</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="D104" t="b">
+        <v>1</v>
       </c>
       <c r="E104" t="n">
         <v>18</v>
       </c>
-    </row>
-    <row r="105" ht="14.25" customHeight="1">
-      <c r="A105" s="2" t="inlineStr">
+      <c r="F104" t="inlineStr"/>
+      <c r="G104" t="inlineStr"/>
+      <c r="H104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
         <is>
           <t>The Cigna Group / Evernorth</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
+      <c r="B105" t="inlineStr">
         <is>
           <t>https://cigna.wd5.myworkdayjobs.com/cignacareers</t>
         </is>
       </c>
-      <c r="C105" s="2" t="inlineStr">
+      <c r="C105" t="inlineStr">
         <is>
           <t>https://jobs.thecignagroup.com/</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="D105" t="b">
+        <v>1</v>
       </c>
       <c r="E105" t="n">
         <v>558</v>
       </c>
-    </row>
-    <row r="106" ht="27" customHeight="1">
-      <c r="A106" s="2" t="inlineStr">
+      <c r="F105" t="inlineStr"/>
+      <c r="G105" t="inlineStr"/>
+      <c r="H105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
         <is>
           <t>Elevance Health</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
+      <c r="B106" t="inlineStr">
         <is>
           <t>https://elevancehealth.wd1.myworkdayjobs.com/ANT/job/Florida---Port-St-Lucie/AFC-Field-Sales---Service-Rep_JR197060/apply</t>
         </is>
       </c>
-      <c r="C106" s="2" t="inlineStr">
+      <c r="C106" t="inlineStr">
         <is>
           <t>https://careers.elevancehealth.com/</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="D106" t="b">
+        <v>1</v>
       </c>
       <c r="E106" t="n">
         <v>301</v>
       </c>
-    </row>
-    <row r="107" ht="14.25" customHeight="1">
-      <c r="A107" s="2" t="inlineStr">
+      <c r="F106" t="inlineStr"/>
+      <c r="G106" t="inlineStr"/>
+      <c r="H106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
         <is>
           <t>Centene</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
+      <c r="B107" t="inlineStr">
         <is>
           <t>https://centene.wd5.myworkdayjobs.com/centene_external</t>
         </is>
       </c>
-      <c r="C107" s="2" t="inlineStr">
+      <c r="C107" t="inlineStr">
         <is>
           <t>https://jobs.centene.com/</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="D107" t="b">
+        <v>1</v>
       </c>
       <c r="E107" t="n">
         <v>216</v>
       </c>
-    </row>
-    <row r="108" ht="14.25" customHeight="1">
-      <c r="A108" s="2" t="inlineStr">
+      <c r="F107" t="inlineStr"/>
+      <c r="G107" t="inlineStr"/>
+      <c r="H107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
         <is>
           <t>Superior HealthPlan</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
+      <c r="B108" t="inlineStr">
         <is>
           <t>https://centene.wd5.myworkdayjobs.com/centene_external</t>
         </is>
       </c>
-      <c r="C108" s="2" t="inlineStr">
+      <c r="C108" t="inlineStr">
         <is>
           <t>https://jobs.centene.com/</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="D108" t="b">
+        <v>1</v>
       </c>
       <c r="E108" t="n">
         <v>216</v>
       </c>
-    </row>
-    <row r="109" ht="14.25" customHeight="1">
-      <c r="A109" s="2" t="inlineStr">
+      <c r="F108" t="inlineStr"/>
+      <c r="G108" t="inlineStr"/>
+      <c r="H108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
         <is>
           <t>Humana</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
+      <c r="B109" t="inlineStr">
         <is>
           <t>https://careers.humana.com/us/en</t>
         </is>
       </c>
-      <c r="C109" s="2" t="inlineStr">
+      <c r="C109" t="inlineStr">
         <is>
           <t>https://careers.humana.com/</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="D109" t="b">
+        <v>1</v>
       </c>
       <c r="E109" t="n">
         <v>2151</v>
       </c>
-    </row>
-    <row r="110" ht="27" customHeight="1">
-      <c r="A110" s="2" t="inlineStr">
+      <c r="F109" t="inlineStr"/>
+      <c r="G109" t="inlineStr"/>
+      <c r="H109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
         <is>
           <t>Molina Healthcare</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
+      <c r="B110" t="inlineStr">
         <is>
           <t>https://hckd.fa.us2.oraclecloud.com/fscmUI/faces/deeplink?objType=IRC_RECRUITING&amp;action=ICE_JOB_SEARCH_RESP</t>
         </is>
       </c>
-      <c r="C110" s="2" t="inlineStr">
+      <c r="C110" t="inlineStr">
         <is>
           <t>https://careers.molinahealthcare.com/</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="D110" t="b">
+        <v>1</v>
       </c>
       <c r="E110" t="n">
         <v>331</v>
       </c>
-    </row>
-    <row r="111" ht="14.25" customHeight="1">
-      <c r="A111" s="2" t="inlineStr">
+      <c r="F110" t="inlineStr"/>
+      <c r="G110" t="inlineStr"/>
+      <c r="H110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
         <is>
           <t>Concentra</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
+      <c r="B111" t="inlineStr">
         <is>
           <t>https://concentrahealthservices.jibeapply.com</t>
         </is>
       </c>
-      <c r="C111" s="2" t="inlineStr">
+      <c r="C111" t="inlineStr">
         <is>
           <t>https://careers.concentra.com/</t>
         </is>
       </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="D111" t="b">
+        <v>1</v>
       </c>
       <c r="E111" t="n">
         <v>1189</v>
       </c>
-    </row>
-    <row r="112" ht="14.25" customHeight="1">
-      <c r="A112" s="2" t="inlineStr">
+      <c r="F111" t="inlineStr"/>
+      <c r="G111" t="inlineStr"/>
+      <c r="H111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
         <is>
           <t>USMD Health System</t>
         </is>
       </c>
-      <c r="B112" s="2" t="n"/>
-      <c r="C112" s="2" t="inlineStr">
+      <c r="B112" t="inlineStr"/>
+      <c r="C112" t="inlineStr">
         <is>
           <t>https://careers.unitedhealthgroup.com/</t>
         </is>
       </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="D112" t="b">
+        <v>1</v>
       </c>
       <c r="E112" t="n">
         <v>18</v>
       </c>
-    </row>
-    <row r="113" ht="14.25" customHeight="1">
-      <c r="A113" s="2" t="inlineStr">
+      <c r="F112" t="inlineStr"/>
+      <c r="G112" t="inlineStr"/>
+      <c r="H112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
         <is>
           <t>Texas Oncology</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
+      <c r="B113" t="inlineStr">
         <is>
           <t>https://careers.usoncology.com/main/jobs</t>
         </is>
       </c>
-      <c r="C113" s="2" t="inlineStr">
+      <c r="C113" t="inlineStr">
         <is>
           <t>https://www.texasoncology.com/careers</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="D113" t="b">
+        <v>1</v>
       </c>
       <c r="E113" t="n">
         <v>691</v>
       </c>
-    </row>
-    <row r="114" ht="27" customHeight="1">
-      <c r="A114" s="2" t="inlineStr">
+      <c r="F113" t="inlineStr"/>
+      <c r="G113" t="inlineStr"/>
+      <c r="H113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
         <is>
           <t>CorVel</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
+      <c r="B114" t="inlineStr">
         <is>
           <t>https://recruiting2.ultipro.com/COR1025CVEL/JobBoard/661856a2-40b3-49f9-ab1e-9845cfac508d</t>
         </is>
       </c>
-      <c r="C114" s="2" t="inlineStr">
+      <c r="C114" t="inlineStr">
         <is>
           <t>https://www.corvel.com/careers/</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="D114" t="b">
+        <v>1</v>
       </c>
       <c r="E114" t="n">
         <v>195</v>
       </c>
-    </row>
-    <row r="115" ht="14.25" customHeight="1">
-      <c r="A115" s="2" t="inlineStr">
+      <c r="F114" t="inlineStr"/>
+      <c r="G114" t="inlineStr"/>
+      <c r="H114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
         <is>
           <t>Addus HomeCare</t>
         </is>
       </c>
-      <c r="B115" s="2" t="n"/>
-      <c r="C115" s="2" t="inlineStr">
+      <c r="B115" t="inlineStr"/>
+      <c r="C115" t="inlineStr">
         <is>
           <t>https://addus.com/careers/</t>
         </is>
       </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="D115" t="b">
+        <v>1</v>
       </c>
       <c r="E115" t="n">
         <v>100</v>
       </c>
-    </row>
-    <row r="116" ht="14.25" customHeight="1">
-      <c r="A116" s="2" t="inlineStr">
+      <c r="F115" t="inlineStr"/>
+      <c r="G115" t="inlineStr"/>
+      <c r="H115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
         <is>
           <t>Enhabit Home Health &amp; Hospice</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
+      <c r="B116" t="inlineStr">
         <is>
           <t>https://careers.enhabit.com/</t>
         </is>
       </c>
-      <c r="C116" s="2" t="inlineStr">
+      <c r="C116" t="inlineStr">
         <is>
           <t>https://careers.ehab.com/</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="D116" t="b">
+        <v>1</v>
       </c>
       <c r="E116" t="n">
         <v>2140</v>
       </c>
-    </row>
-    <row r="117" ht="14.25" customHeight="1">
-      <c r="A117" s="2" t="inlineStr">
+      <c r="F116" t="inlineStr"/>
+      <c r="G116" t="inlineStr"/>
+      <c r="H116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
         <is>
           <t>Aveanna Healthcare</t>
         </is>
       </c>
-      <c r="B117" s="2" t="n"/>
-      <c r="C117" s="2" t="inlineStr">
+      <c r="B117" t="inlineStr"/>
+      <c r="C117" t="inlineStr">
         <is>
           <t>https://jobs.aveanna.com/</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="D117" t="b">
+        <v>1</v>
       </c>
       <c r="E117" t="n">
         <v>3722</v>
       </c>
-    </row>
-    <row r="118" ht="14.25" customHeight="1">
-      <c r="A118" s="2" t="inlineStr">
+      <c r="F117" t="inlineStr"/>
+      <c r="G117" t="inlineStr"/>
+      <c r="H117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
         <is>
           <t>FinThrive</t>
         </is>
       </c>
-      <c r="B118" s="2" t="n"/>
-      <c r="C118" s="2" t="inlineStr">
+      <c r="B118" t="inlineStr"/>
+      <c r="C118" t="inlineStr">
         <is>
           <t>https://finthrive.com/careers/</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="D118" t="b">
+        <v>1</v>
       </c>
       <c r="E118" t="n">
         <v>16</v>
       </c>
-    </row>
-    <row r="119" ht="14.25" customHeight="1">
-      <c r="A119" s="2" t="inlineStr">
+      <c r="F118" t="inlineStr"/>
+      <c r="G118" t="inlineStr"/>
+      <c r="H118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
         <is>
           <t>Omnicell</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
+      <c r="B119" t="inlineStr">
         <is>
           <t>https://apply.omnicell.com/careers</t>
         </is>
       </c>
-      <c r="C119" s="2" t="inlineStr">
+      <c r="C119" t="inlineStr">
         <is>
           <t>https://www.omnicell.com/about-us/careers</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
+      <c r="D119" t="b">
+        <v>0</v>
       </c>
       <c r="E119" t="n">
         <v>0</v>
       </c>
-    </row>
-    <row r="120" ht="27" customHeight="1">
-      <c r="A120" s="2" t="inlineStr">
+      <c r="F119" t="inlineStr"/>
+      <c r="G119" t="inlineStr"/>
+      <c r="H119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
         <is>
           <t>HealthEquity</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
+      <c r="B120" t="inlineStr">
         <is>
           <t>https://careers-healthequity.icims.com/jobs/search?hashed=-435620570</t>
         </is>
       </c>
-      <c r="C120" s="2" t="inlineStr">
+      <c r="C120" t="inlineStr">
         <is>
           <t>https://healthequity.com/careers</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="D120" t="b">
+        <v>1</v>
       </c>
       <c r="E120" t="n">
         <v>36</v>
       </c>
-    </row>
-    <row r="121" ht="41.25" customHeight="1">
-      <c r="A121" s="2" t="inlineStr">
+      <c r="F120" t="inlineStr"/>
+      <c r="G120" t="inlineStr"/>
+      <c r="H120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
         <is>
           <t>Teladoc Health</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
+      <c r="B121" t="inlineStr">
         <is>
           <t>https://teladoc.wd503.myworkdayjobs.com/en-US/teladochealth_is_hiring?q=THMG&amp;locationCountry=bc33aa3152ec42d4995f4791a106ed09</t>
         </is>
       </c>
-      <c r="C121" s="2" t="inlineStr">
+      <c r="C121" t="inlineStr">
         <is>
           <t>https://www.teladochealth.com/careers/</t>
         </is>
       </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="D121" t="b">
+        <v>1</v>
       </c>
       <c r="E121" t="n">
         <v>41</v>
       </c>
-    </row>
-    <row r="122" ht="14.25" customHeight="1">
-      <c r="A122" s="2" t="inlineStr">
+      <c r="F121" t="inlineStr"/>
+      <c r="G121" t="inlineStr"/>
+      <c r="H121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
         <is>
           <t>TIAA</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
+      <c r="B122" t="inlineStr">
         <is>
           <t>https://tiaa.wd1.myworkdayjobs.com/en-US/Search/</t>
         </is>
       </c>
-      <c r="C122" s="2" t="n"/>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="C122" t="inlineStr"/>
+      <c r="D122" t="b">
+        <v>1</v>
       </c>
       <c r="E122" t="n">
         <v>199</v>
       </c>
-    </row>
-    <row r="123" ht="14.25" customHeight="1">
-      <c r="A123" s="2" t="inlineStr">
+      <c r="F122" t="inlineStr"/>
+      <c r="G122" t="inlineStr"/>
+      <c r="H122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
         <is>
           <t>Allworth Financial</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
+      <c r="B123" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/allworthfinancial</t>
         </is>
       </c>
-      <c r="C123" s="2" t="n"/>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="C123" t="inlineStr"/>
+      <c r="D123" t="b">
+        <v>1</v>
       </c>
       <c r="E123" t="n">
         <v>21</v>
       </c>
-    </row>
-    <row r="124" ht="27" customHeight="1">
-      <c r="A124" s="2" t="inlineStr">
+      <c r="F123" t="inlineStr"/>
+      <c r="G123" t="inlineStr"/>
+      <c r="H123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
         <is>
           <t>Vanguard</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
+      <c r="B124" t="inlineStr">
         <is>
           <t>https://vanguard.wd5.myworkdayjobs.com/en-US/vanguard_external/</t>
         </is>
       </c>
-      <c r="C124" s="2" t="n"/>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="C124" t="inlineStr"/>
+      <c r="D124" t="b">
+        <v>1</v>
       </c>
       <c r="E124" t="n">
         <v>423</v>
       </c>
-    </row>
-    <row r="125" ht="14.25" customHeight="1">
-      <c r="A125" s="2" t="inlineStr">
+      <c r="F124" t="inlineStr"/>
+      <c r="G124" t="inlineStr"/>
+      <c r="H124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
         <is>
           <t>USAA</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
+      <c r="B125" t="inlineStr">
         <is>
           <t>https://usaa.wd1.myworkdayjobs.com/USAAJOBSWD/login</t>
         </is>
       </c>
-      <c r="C125" s="2" t="inlineStr">
+      <c r="C125" t="inlineStr">
         <is>
           <t>https://www.usaajobs.com/search-jobs</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="D125" t="b">
+        <v>1</v>
       </c>
       <c r="E125" t="n">
         <v>171</v>
       </c>
-    </row>
-    <row r="126" ht="14.25" customHeight="1">
-      <c r="A126" s="2" t="inlineStr">
+      <c r="F125" t="inlineStr"/>
+      <c r="G125" t="inlineStr"/>
+      <c r="H125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
         <is>
           <t>SoFi</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
+      <c r="B126" t="inlineStr">
         <is>
           <t>https://boards.greenhouse.io/sofi</t>
         </is>
       </c>
-      <c r="C126" s="2" t="n"/>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="C126" t="inlineStr"/>
+      <c r="D126" t="b">
+        <v>1</v>
       </c>
       <c r="E126" t="n">
         <v>58</v>
       </c>
-    </row>
-    <row r="127" ht="27" customHeight="1">
-      <c r="A127" s="2" t="inlineStr">
+      <c r="F126" t="inlineStr"/>
+      <c r="G126" t="inlineStr"/>
+      <c r="H126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
         <is>
           <t>RealPage</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
+      <c r="B127" t="inlineStr">
         <is>
           <t>https://careers-realpagepms.icims.com/jobs/search?hashed=-625856947</t>
         </is>
       </c>
-      <c r="C127" s="2" t="inlineStr">
+      <c r="C127" t="inlineStr">
         <is>
           <t>https://www.realpage.com/careers/</t>
         </is>
       </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="D127" t="b">
+        <v>1</v>
       </c>
       <c r="E127" t="n">
         <v>64</v>
       </c>
-    </row>
-    <row r="128" ht="14.25" customHeight="1">
-      <c r="A128" s="2" t="inlineStr">
+      <c r="F127" t="inlineStr"/>
+      <c r="G127" t="inlineStr"/>
+      <c r="H127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
         <is>
           <t>CBRE</t>
         </is>
       </c>
-      <c r="B128" s="2" t="n"/>
-      <c r="C128" s="2" t="inlineStr">
+      <c r="B128" t="inlineStr"/>
+      <c r="C128" t="inlineStr">
         <is>
           <t>https://careers.cbre.com/</t>
         </is>
       </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="D128" t="b">
+        <v>1</v>
       </c>
       <c r="E128" t="n">
         <v>752</v>
       </c>
-    </row>
-    <row r="129" ht="27" customHeight="1">
-      <c r="A129" s="2" t="inlineStr">
+      <c r="F128" t="inlineStr"/>
+      <c r="G128" t="inlineStr"/>
+      <c r="H128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
         <is>
           <t>Invitation Homes</t>
         </is>
       </c>
-      <c r="B129" s="2" t="inlineStr">
+      <c r="B129" t="inlineStr">
         <is>
           <t>https://invitationhomes.wd503.myworkdayjobs.com/en-US/INVH/introduceYourself</t>
         </is>
       </c>
-      <c r="C129" s="2" t="inlineStr">
+      <c r="C129" t="inlineStr">
         <is>
           <t>https://careers.invitationhomes.com/</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="D129" t="b">
+        <v>1</v>
       </c>
       <c r="E129" t="n">
         <v>63</v>
       </c>
-    </row>
-    <row r="130" ht="27" customHeight="1">
-      <c r="A130" s="2" t="inlineStr">
+      <c r="F129" t="inlineStr"/>
+      <c r="G129" t="inlineStr"/>
+      <c r="H129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
         <is>
           <t>Welltower</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
+      <c r="B130" t="inlineStr">
         <is>
           <t>https://recruiting.ultipro.com/WEL1008WLLT/JobBoard/30969ce4-3b7e-40a6-b86c-34d3616fe0ed/</t>
         </is>
       </c>
-      <c r="C130" s="2" t="n"/>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="C130" t="inlineStr"/>
+      <c r="D130" t="b">
+        <v>1</v>
       </c>
       <c r="E130" t="n">
         <v>82</v>
       </c>
-    </row>
-    <row r="131" ht="14.25" customHeight="1">
-      <c r="A131" s="2" t="inlineStr">
+      <c r="F130" t="inlineStr"/>
+      <c r="G130" t="inlineStr"/>
+      <c r="H130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
         <is>
           <t>Frost Bank</t>
         </is>
       </c>
-      <c r="B131" s="2" t="inlineStr">
+      <c r="B131" t="inlineStr">
         <is>
           <t>https://careers.frostbank.com/us/en</t>
         </is>
       </c>
-      <c r="C131" s="2" t="n"/>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="C131" t="inlineStr"/>
+      <c r="D131" t="b">
+        <v>1</v>
       </c>
       <c r="E131" t="n">
         <v>183</v>
       </c>
-    </row>
-    <row r="132" ht="14.25" customHeight="1">
-      <c r="A132" s="2" t="inlineStr">
+      <c r="F131" t="inlineStr"/>
+      <c r="G131" t="inlineStr"/>
+      <c r="H131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
         <is>
           <t>State Farm</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
+      <c r="B132" t="inlineStr">
         <is>
           <t>https://events-statefarm.icims.com/jobs/search</t>
         </is>
       </c>
-      <c r="C132" s="2" t="inlineStr">
+      <c r="C132" t="inlineStr">
         <is>
           <t>https://jobs.statefarm.com/</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="D132" t="b">
+        <v>1</v>
       </c>
       <c r="E132" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="133" ht="14.25" customHeight="1">
-      <c r="A133" s="2" t="inlineStr">
+      <c r="F132" t="inlineStr"/>
+      <c r="G132" t="inlineStr"/>
+      <c r="H132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
         <is>
           <t>Globe Life</t>
         </is>
       </c>
-      <c r="B133" s="2" t="n"/>
-      <c r="C133" s="2" t="inlineStr">
+      <c r="B133" t="inlineStr"/>
+      <c r="C133" t="inlineStr">
         <is>
           <t>https://careers.globelifeinsurance.com/</t>
         </is>
       </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="D133" t="b">
+        <v>1</v>
       </c>
       <c r="E133" t="n">
         <v>27</v>
       </c>
-    </row>
-    <row r="134" ht="54.75" customHeight="1">
-      <c r="A134" s="2" t="inlineStr">
+      <c r="F133" t="inlineStr"/>
+      <c r="G133" t="inlineStr"/>
+      <c r="H133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
         <is>
           <t>PlainsCapital Bank</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
+      <c r="B134" t="inlineStr">
         <is>
           <t>https://ejlu.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/HilltopHoldingsAllJobs/requisitions?lastSelectedFacet=ORGANIZATIONS&amp;mode=location&amp;selectedOrganizationsFacet=300000001412198</t>
         </is>
       </c>
-      <c r="C134" s="2" t="inlineStr">
+      <c r="C134" t="inlineStr">
         <is>
           <t>https://plainscapital.com/careers/</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="D134" t="b">
+        <v>1</v>
       </c>
       <c r="E134" t="n">
         <v>254</v>
       </c>
-    </row>
-    <row r="135" ht="27.75" customHeight="1">
-      <c r="A135" s="2" t="inlineStr">
+      <c r="F134" t="inlineStr"/>
+      <c r="G134" t="inlineStr"/>
+      <c r="H134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
         <is>
           <t>Bank of Texas / BOK Financial</t>
         </is>
       </c>
-      <c r="B135" s="2" t="inlineStr">
+      <c r="B135" t="inlineStr">
         <is>
           <t>https://jobs.bokf.com/Bank-of-Texas/go/Bank-of-Texas/4477400/</t>
         </is>
       </c>
-      <c r="C135" s="2" t="inlineStr">
+      <c r="C135" t="inlineStr">
         <is>
           <t>https://jobs.bokf.com/Bank-of-Texas/go/Bank-of-Texas/4477400/</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="D135" t="b">
+        <v>1</v>
       </c>
       <c r="E135" t="n">
         <v>200</v>
       </c>
-    </row>
-    <row r="136" ht="14.25" customHeight="1">
-      <c r="A136" s="2" t="inlineStr">
+      <c r="F135" t="inlineStr"/>
+      <c r="G135" t="inlineStr"/>
+      <c r="H135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
         <is>
           <t>Options Clearing Corporation (OCC)</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
+      <c r="B136" t="inlineStr">
         <is>
           <t>https://theocc.wd5.myworkdayjobs.com/careers</t>
         </is>
       </c>
-      <c r="C136" s="2" t="inlineStr">
+      <c r="C136" t="inlineStr">
         <is>
           <t>https://www.theocc.com/careers</t>
         </is>
       </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="D136" t="b">
+        <v>1</v>
       </c>
       <c r="E136" t="n">
         <v>36</v>
       </c>
-    </row>
-    <row r="137" ht="14.25" customHeight="1">
-      <c r="A137" s="2" t="inlineStr">
+      <c r="F136" t="inlineStr"/>
+      <c r="G136" t="inlineStr"/>
+      <c r="H136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
         <is>
           <t>FirstCash Holdings</t>
         </is>
       </c>
-      <c r="B137" s="2" t="inlineStr">
+      <c r="B137" t="inlineStr">
         <is>
           <t>https://jobs.jobvite.com/firstcash-holdings-inc/</t>
         </is>
       </c>
-      <c r="C137" s="2" t="n"/>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="C137" t="inlineStr"/>
+      <c r="D137" t="b">
+        <v>1</v>
       </c>
       <c r="E137" t="n">
         <v>366</v>
       </c>
-    </row>
-    <row r="138" ht="14.25" customHeight="1">
-      <c r="A138" s="2" t="inlineStr">
+      <c r="F137" t="inlineStr"/>
+      <c r="G137" t="inlineStr"/>
+      <c r="H137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
         <is>
           <t>TPG</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
+      <c r="B138" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/tpgcareers</t>
         </is>
       </c>
-      <c r="C138" s="2" t="inlineStr">
+      <c r="C138" t="inlineStr">
         <is>
           <t>https://www.tpg.com/careers</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="D138" t="b">
+        <v>1</v>
       </c>
       <c r="E138" t="n">
         <v>17</v>
       </c>
-    </row>
-    <row r="139" ht="14.25" customHeight="1">
-      <c r="A139" s="2" t="inlineStr">
+      <c r="F138" t="inlineStr"/>
+      <c r="G138" t="inlineStr"/>
+      <c r="H138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
         <is>
           <t>JLL</t>
         </is>
       </c>
-      <c r="B139" s="2" t="inlineStr">
+      <c r="B139" t="inlineStr">
         <is>
           <t>https://jll.wd1.myworkdayjobs.com/en-US/jllcareers/</t>
         </is>
       </c>
-      <c r="C139" s="2" t="n"/>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="C139" t="inlineStr"/>
+      <c r="D139" t="b">
+        <v>1</v>
       </c>
       <c r="E139" t="n">
         <v>2000</v>
       </c>
-    </row>
-    <row r="140" ht="14.25" customHeight="1">
-      <c r="A140" s="2" t="inlineStr">
+      <c r="F139" t="inlineStr"/>
+      <c r="G139" t="inlineStr"/>
+      <c r="H139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
         <is>
           <t>Intuit</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
+      <c r="B140" t="inlineStr">
         <is>
           <t>https://jobs.intuit.com/search-jobs</t>
         </is>
       </c>
-      <c r="C140" s="2" t="inlineStr">
+      <c r="C140" t="inlineStr">
         <is>
           <t>https://www.intuit.com/careers/</t>
         </is>
       </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="D140" t="b">
+        <v>1</v>
       </c>
       <c r="E140" t="n">
         <v>454</v>
       </c>
-    </row>
-    <row r="141" ht="14.25" customHeight="1">
-      <c r="A141" s="2" t="inlineStr">
+      <c r="F140" t="inlineStr"/>
+      <c r="G140" t="inlineStr"/>
+      <c r="H140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
         <is>
           <t>Match Group</t>
         </is>
       </c>
-      <c r="B141" s="2" t="inlineStr">
+      <c r="B141" t="inlineStr">
         <is>
           <t>https://jobs.lever.co/matchgroup</t>
         </is>
       </c>
-      <c r="C141" s="2" t="inlineStr">
+      <c r="C141" t="inlineStr">
         <is>
           <t>https://mtch.com/careers/</t>
         </is>
       </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="D141" t="b">
+        <v>1</v>
       </c>
       <c r="E141" t="n">
         <v>66</v>
       </c>
-    </row>
-    <row r="142" ht="14.25" customHeight="1">
-      <c r="A142" s="2" t="inlineStr">
+      <c r="F141" t="inlineStr"/>
+      <c r="G141" t="inlineStr"/>
+      <c r="H141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
         <is>
           <t>Slalom</t>
         </is>
       </c>
-      <c r="B142" s="2" t="n"/>
-      <c r="C142" s="2" t="inlineStr">
+      <c r="B142" t="inlineStr"/>
+      <c r="C142" t="inlineStr">
         <is>
           <t>https://www.slalom.com/us/en/careers</t>
         </is>
       </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
+      <c r="D142" t="b">
+        <v>0</v>
       </c>
       <c r="E142" t="n">
         <v>0</v>
       </c>
-    </row>
-    <row r="143" ht="14.25" customHeight="1">
-      <c r="A143" s="2" t="inlineStr">
+      <c r="F142" t="inlineStr"/>
+      <c r="G142" t="inlineStr"/>
+      <c r="H142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
         <is>
           <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
-      <c r="B143" s="2" t="inlineStr">
+      <c r="B143" t="inlineStr">
         <is>
           <t>https://www.tcs.com/careers/united-states</t>
         </is>
       </c>
-      <c r="C143" s="2" t="n"/>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
+      <c r="C143" t="inlineStr"/>
+      <c r="D143" t="b">
+        <v>0</v>
       </c>
       <c r="E143" t="n">
         <v>0</v>
       </c>
-    </row>
-    <row r="144" ht="14.25" customHeight="1">
-      <c r="A144" s="2" t="inlineStr">
+      <c r="F143" t="inlineStr"/>
+      <c r="G143" t="inlineStr"/>
+      <c r="H143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
         <is>
           <t>Jacobs Solutions</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
+      <c r="B144" t="inlineStr">
         <is>
           <t>https://careers.jacobs.com/</t>
         </is>
       </c>
-      <c r="C144" s="2" t="inlineStr">
+      <c r="C144" t="inlineStr">
         <is>
           <t>https://www.jacobs.com/careers-jacobs</t>
         </is>
       </c>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="D144" t="b">
+        <v>1</v>
       </c>
       <c r="E144" t="n">
         <v>738</v>
       </c>
-    </row>
-    <row r="145" ht="14.25" customHeight="1">
-      <c r="A145" s="2" t="inlineStr">
+      <c r="F144" t="inlineStr"/>
+      <c r="G144" t="inlineStr"/>
+      <c r="H144" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
         <is>
           <t>McAfee</t>
         </is>
       </c>
-      <c r="B145" s="2" t="inlineStr">
+      <c r="B145" t="inlineStr">
         <is>
           <t>https://mcafee.wd1.myworkdayjobs.com/External/</t>
         </is>
       </c>
-      <c r="C145" s="2" t="inlineStr">
+      <c r="C145" t="inlineStr">
         <is>
           <t>https://www.mcafee.com/en-us/careers.html</t>
         </is>
       </c>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
+      <c r="D145" t="b">
+        <v>0</v>
       </c>
       <c r="E145" t="n">
         <v>0</v>
       </c>
-    </row>
-    <row r="146" ht="14.25" customHeight="1">
-      <c r="A146" s="2" t="inlineStr">
+      <c r="F145" t="inlineStr"/>
+      <c r="G145" t="inlineStr"/>
+      <c r="H145" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
         <is>
           <t>Boston Consulting Group (BCG)</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr">
+      <c r="B146" t="inlineStr">
         <is>
           <t>https://careers.bcg.com/global/en/</t>
         </is>
       </c>
-      <c r="C146" s="2" t="inlineStr">
+      <c r="C146" t="inlineStr">
         <is>
           <t>https://careers.bcg.com/</t>
         </is>
       </c>
-      <c r="D146" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="D146" t="b">
+        <v>1</v>
       </c>
       <c r="E146" t="n">
         <v>890</v>
       </c>
-    </row>
-    <row r="147" ht="14.25" customHeight="1">
-      <c r="A147" s="2" t="inlineStr">
+      <c r="F146" t="inlineStr"/>
+      <c r="G146" t="inlineStr"/>
+      <c r="H146" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
         <is>
           <t>Ryan</t>
         </is>
       </c>
-      <c r="B147" s="2" t="inlineStr">
+      <c r="B147" t="inlineStr">
         <is>
           <t>https://ryan.wd1.myworkdayjobs.com/RyanCareers</t>
         </is>
       </c>
-      <c r="C147" s="2" t="inlineStr">
+      <c r="C147" t="inlineStr">
         <is>
           <t>https://ryan.com/careers/</t>
         </is>
       </c>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="D147" t="b">
+        <v>1</v>
       </c>
       <c r="E147" t="n">
         <v>108</v>
       </c>
-    </row>
-    <row r="148" ht="14.25" customHeight="1">
-      <c r="A148" s="2" t="inlineStr">
+      <c r="F147" t="inlineStr"/>
+      <c r="G147" t="inlineStr"/>
+      <c r="H147" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
         <is>
           <t>CHRISTUS Health</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
+      <c r="B148" t="inlineStr">
         <is>
           <t>https://careers.christushealth.org/job-search</t>
         </is>
       </c>
-      <c r="C148" s="2" t="inlineStr">
+      <c r="C148" t="inlineStr">
         <is>
           <t>https://careers.christushealth.org/</t>
         </is>
       </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="D148" t="b">
+        <v>1</v>
       </c>
       <c r="E148" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="149" ht="27" customHeight="1">
-      <c r="A149" s="2" t="inlineStr">
+      <c r="F148" t="inlineStr"/>
+      <c r="G148" t="inlineStr"/>
+      <c r="H148" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
         <is>
           <t>JPS Health Network</t>
         </is>
       </c>
-      <c r="B149" s="2" t="inlineStr">
+      <c r="B149" t="inlineStr">
         <is>
           <t>https://jpshealthnet.csod.com/ux/ats/careersite/4/home?c=jpshealthnet&amp;cfdd[0][id]=22&amp;cfdd[0][options][0]=18</t>
         </is>
       </c>
-      <c r="C149" s="2" t="inlineStr">
+      <c r="C149" t="inlineStr">
         <is>
           <t>https://jpshealthnet.org/careers</t>
         </is>
       </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="D149" t="b">
+        <v>1</v>
       </c>
       <c r="E149" t="n">
         <v>168</v>
       </c>
-    </row>
-    <row r="150" ht="27" customHeight="1">
-      <c r="A150" s="2" t="inlineStr">
+      <c r="F149" t="inlineStr"/>
+      <c r="G149" t="inlineStr"/>
+      <c r="H149" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
         <is>
           <t>AMN Healthcare</t>
         </is>
       </c>
-      <c r="B150" s="2" t="inlineStr">
+      <c r="B150" t="inlineStr">
         <is>
           <t>https://amn.wd1.myworkdayjobs.com/AMN_Careers/job/Dallas-TX/AI-Product-Manager_Req23778/apply</t>
         </is>
       </c>
-      <c r="C150" s="2" t="inlineStr">
+      <c r="C150" t="inlineStr">
         <is>
           <t>https://www.amncareers.com/</t>
         </is>
       </c>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="D150" t="b">
+        <v>1</v>
       </c>
       <c r="E150" t="n">
         <v>29</v>
       </c>
-    </row>
-    <row r="151" ht="14.25" customHeight="1">
-      <c r="A151" s="2" t="inlineStr">
+      <c r="F150" t="inlineStr"/>
+      <c r="G150" t="inlineStr"/>
+      <c r="H150" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
         <is>
           <t>Galderma</t>
         </is>
       </c>
-      <c r="B151" s="2" t="inlineStr">
+      <c r="B151" t="inlineStr">
         <is>
           <t>https://galderma.wd3.myworkdayjobs.com/External</t>
         </is>
       </c>
-      <c r="C151" s="2" t="inlineStr">
+      <c r="C151" t="inlineStr">
         <is>
           <t>https://www.galderma.com/careers</t>
         </is>
       </c>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="D151" t="b">
+        <v>1</v>
       </c>
       <c r="E151" t="n">
         <v>361</v>
       </c>
-    </row>
-    <row r="152" ht="41.25" customHeight="1">
-      <c r="A152" s="2" t="inlineStr">
+      <c r="F151" t="inlineStr"/>
+      <c r="G151" t="inlineStr"/>
+      <c r="H151" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
         <is>
           <t>Abbott Laboratories</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
+      <c r="B152" t="inlineStr">
         <is>
           <t>https://abbott.wd5.myworkdayjobs.com/abbottcareers/login?utm_source=jobs.abbott/us/en&amp;utm_medium=website&amp;utm_content=widget&amp;utm_campaign=jobs.abbott-application-status</t>
         </is>
       </c>
-      <c r="C152" s="2" t="inlineStr">
+      <c r="C152" t="inlineStr">
         <is>
           <t>https://www.jobs.abbott/us/en</t>
         </is>
       </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="D152" t="b">
+        <v>1</v>
       </c>
       <c r="E152" t="n">
         <v>1998</v>
       </c>
-    </row>
-    <row r="153" ht="14.25" customHeight="1">
-      <c r="A153" s="2" t="inlineStr">
+      <c r="F152" t="inlineStr"/>
+      <c r="G152" t="inlineStr"/>
+      <c r="H152" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
         <is>
           <t>Verily</t>
         </is>
       </c>
-      <c r="B153" s="2" t="inlineStr">
+      <c r="B153" t="inlineStr">
         <is>
           <t>https://verily.wd1.myworkdayjobs.com/Verily_Careers</t>
         </is>
       </c>
-      <c r="C153" s="2" t="inlineStr">
+      <c r="C153" t="inlineStr">
         <is>
           <t>https://verily.com/careers</t>
         </is>
       </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="D153" t="b">
+        <v>1</v>
       </c>
       <c r="E153" t="n">
         <v>76</v>
       </c>
-    </row>
-    <row r="154" ht="14.25" customHeight="1">
-      <c r="A154" s="2" t="inlineStr">
+      <c r="F153" t="inlineStr"/>
+      <c r="G153" t="inlineStr"/>
+      <c r="H153" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
         <is>
           <t>Smith+Nephew</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
+      <c r="B154" t="inlineStr">
         <is>
           <t>https://smithnephew.wd5.myworkdayjobs.com/External</t>
         </is>
       </c>
-      <c r="C154" s="2" t="inlineStr">
+      <c r="C154" t="inlineStr">
         <is>
           <t>https://www.smith-nephew.com/en-us/careers</t>
         </is>
       </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="D154" t="b">
+        <v>1</v>
       </c>
       <c r="E154" t="n">
         <v>339</v>
       </c>
-    </row>
-    <row r="155" ht="14.25" customHeight="1">
-      <c r="A155" s="2" t="inlineStr">
+      <c r="F154" t="inlineStr"/>
+      <c r="G154" t="inlineStr"/>
+      <c r="H154" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
         <is>
           <t>Energy Transfer</t>
         </is>
       </c>
-      <c r="B155" s="2" t="inlineStr">
+      <c r="B155" t="inlineStr">
         <is>
           <t>https://energytransfer.referrals.selectminds.com/</t>
         </is>
       </c>
-      <c r="C155" s="2" t="inlineStr">
+      <c r="C155" t="inlineStr">
         <is>
           <t>https://energytransfer.com/careers/</t>
         </is>
       </c>
-      <c r="D155" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="D155" t="b">
+        <v>1</v>
       </c>
       <c r="E155" t="n">
         <v>10</v>
       </c>
-    </row>
-    <row r="156" ht="14.25" customHeight="1">
-      <c r="A156" s="2" t="inlineStr">
+      <c r="F155" t="inlineStr"/>
+      <c r="G155" t="inlineStr"/>
+      <c r="H155" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
         <is>
           <t>D.R. Horton</t>
         </is>
       </c>
-      <c r="B156" s="2" t="inlineStr">
+      <c r="B156" t="inlineStr">
         <is>
           <t>https://careers-horton.icims.com/</t>
         </is>
       </c>
-      <c r="C156" s="2" t="inlineStr">
+      <c r="C156" t="inlineStr">
         <is>
           <t>https://www.drhorton.com/careers</t>
         </is>
       </c>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="D156" t="b">
+        <v>1</v>
       </c>
       <c r="E156" t="n">
         <v>13</v>
       </c>
-    </row>
-    <row r="157" ht="14.25" customHeight="1">
-      <c r="A157" s="2" t="inlineStr">
+      <c r="F156" t="inlineStr"/>
+      <c r="G156" t="inlineStr"/>
+      <c r="H156" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
         <is>
           <t>HF Sinclair</t>
         </is>
       </c>
-      <c r="B157" s="2" t="inlineStr">
+      <c r="B157" t="inlineStr">
         <is>
           <t>https://careers.hfsinclair.com/</t>
         </is>
       </c>
-      <c r="C157" s="2" t="inlineStr">
+      <c r="C157" t="inlineStr">
         <is>
           <t>https://careers.hfsinclair.com/</t>
         </is>
       </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="D157" t="b">
+        <v>1</v>
       </c>
       <c r="E157" t="n">
         <v>104</v>
       </c>
-    </row>
-    <row r="158" ht="14.25" customHeight="1">
-      <c r="A158" s="2" t="inlineStr">
+      <c r="F157" t="inlineStr"/>
+      <c r="G157" t="inlineStr"/>
+      <c r="H157" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
         <is>
           <t>Keurig Dr Pepper</t>
         </is>
       </c>
-      <c r="B158" s="2" t="n"/>
-      <c r="C158" s="2" t="inlineStr">
+      <c r="B158" t="inlineStr"/>
+      <c r="C158" t="inlineStr">
         <is>
           <t>https://careers.keurigdrpepper.com/en</t>
         </is>
       </c>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="D158" t="b">
+        <v>1</v>
       </c>
       <c r="E158" t="n">
         <v>15</v>
       </c>
-    </row>
-    <row r="159" ht="14.25" customHeight="1">
-      <c r="A159" s="2" t="inlineStr">
+      <c r="F158" t="inlineStr"/>
+      <c r="G158" t="inlineStr"/>
+      <c r="H158" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
         <is>
           <t>Vistra</t>
         </is>
       </c>
-      <c r="B159" s="2" t="inlineStr">
+      <c r="B159" t="inlineStr">
         <is>
           <t>https://vst.wd5.myworkdayjobs.com/en-US/vistra_careers</t>
         </is>
       </c>
-      <c r="C159" s="2" t="inlineStr">
+      <c r="C159" t="inlineStr">
         <is>
           <t>https://vistracorp.com/careers/</t>
         </is>
       </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="D159" t="b">
+        <v>1</v>
       </c>
       <c r="E159" t="n">
         <v>185</v>
       </c>
-    </row>
-    <row r="160" ht="14.25" customHeight="1">
-      <c r="A160" s="2" t="inlineStr">
+      <c r="F159" t="inlineStr"/>
+      <c r="G159" t="inlineStr"/>
+      <c r="H159" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
         <is>
           <t>Kimberly-Clark</t>
         </is>
       </c>
-      <c r="B160" s="2" t="inlineStr">
+      <c r="B160" t="inlineStr">
         <is>
           <t>https://kimberlyclark.wd1.myworkdayjobs.com/global</t>
         </is>
       </c>
-      <c r="C160" s="2" t="inlineStr">
+      <c r="C160" t="inlineStr">
         <is>
           <t>https://careers.kimberly-clark.com/</t>
         </is>
       </c>
-      <c r="D160" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="D160" t="b">
+        <v>1</v>
       </c>
       <c r="E160" t="n">
         <v>184</v>
       </c>
-    </row>
-    <row r="161" ht="14.25" customHeight="1">
-      <c r="A161" s="2" t="inlineStr">
+      <c r="F160" t="inlineStr"/>
+      <c r="G160" t="inlineStr"/>
+      <c r="H160" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
         <is>
           <t>AECOM</t>
         </is>
       </c>
-      <c r="B161" s="2" t="inlineStr">
+      <c r="B161" t="inlineStr">
         <is>
           <t>https://careers.smartrecruiters.com/AECOM2/</t>
         </is>
       </c>
-      <c r="C161" s="2" t="n"/>
-      <c r="D161" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="C161" t="inlineStr"/>
+      <c r="D161" t="b">
+        <v>1</v>
       </c>
       <c r="E161" t="n">
         <v>5010</v>
       </c>
-    </row>
-    <row r="162" ht="14.25" customHeight="1">
-      <c r="A162" s="2" t="inlineStr">
+      <c r="F161" t="inlineStr"/>
+      <c r="G161" t="inlineStr"/>
+      <c r="H161" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
         <is>
           <t>Celanese</t>
         </is>
       </c>
-      <c r="B162" s="2" t="inlineStr">
+      <c r="B162" t="inlineStr">
         <is>
           <t>https://career-celanese.icims.com/jobs/intro</t>
         </is>
       </c>
-      <c r="C162" s="2" t="inlineStr">
+      <c r="C162" t="inlineStr">
         <is>
           <t>https://careers.celanese.com/</t>
         </is>
       </c>
-      <c r="D162" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="D162" t="b">
+        <v>1</v>
       </c>
       <c r="E162" t="n">
         <v>77</v>
       </c>
-    </row>
-    <row r="163" ht="14.25" customHeight="1">
+      <c r="F162" t="inlineStr"/>
+      <c r="G162" t="inlineStr"/>
+      <c r="H162" t="inlineStr"/>
+    </row>
+    <row r="163">
       <c r="A163" t="inlineStr">
         <is>
           <t>Greystar</t>
@@ -4462,16 +4623,17 @@
           <t>https://jobs.greystar.com/</t>
         </is>
       </c>
-      <c r="D163" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="D163" t="b">
+        <v>1</v>
       </c>
       <c r="E163" t="n">
         <v>1600</v>
       </c>
-    </row>
-    <row r="164" ht="14.25" customHeight="1">
+      <c r="F163" t="inlineStr"/>
+      <c r="G163" t="inlineStr"/>
+      <c r="H163" t="inlineStr"/>
+    </row>
+    <row r="164">
       <c r="A164" t="inlineStr">
         <is>
           <t>AT&amp;T</t>
@@ -4487,16 +4649,17 @@
           <t>https://www.att.jobs/</t>
         </is>
       </c>
-      <c r="D164" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="D164" t="b">
+        <v>1</v>
       </c>
       <c r="E164" t="n">
         <v>1266</v>
       </c>
-    </row>
-    <row r="165" ht="14.25" customHeight="1">
+      <c r="F164" t="inlineStr"/>
+      <c r="G164" t="inlineStr"/>
+      <c r="H164" t="inlineStr"/>
+    </row>
+    <row r="165">
       <c r="A165" t="inlineStr">
         <is>
           <t>Charles Schwab</t>
@@ -4512,41 +4675,43 @@
           <t>https://www.schwabjobs.com/</t>
         </is>
       </c>
-      <c r="D165" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="D165" t="b">
+        <v>1</v>
       </c>
       <c r="E165" t="n">
         <v>313</v>
       </c>
-    </row>
-    <row r="166" ht="14.25" customHeight="1">
+      <c r="F165" t="inlineStr"/>
+      <c r="G165" t="inlineStr"/>
+      <c r="H165" t="inlineStr"/>
+    </row>
+    <row r="166">
       <c r="A166" t="inlineStr">
         <is>
           <t>Verizon</t>
         </is>
       </c>
+      <c r="B166" t="inlineStr"/>
       <c r="C166" t="inlineStr">
         <is>
           <t>https://mycareer.verizon.com/jobs/</t>
         </is>
       </c>
-      <c r="D166" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="D166" t="b">
+        <v>1</v>
       </c>
       <c r="E166" t="n">
         <v>346</v>
       </c>
+      <c r="F166" t="inlineStr"/>
+      <c r="G166" t="inlineStr"/>
       <c r="H166" t="inlineStr">
         <is>
           <t>ATS URL pointed at a login-gated Workday candidate-home (userHome) endpoint that 422s on the CXS API; cleared so it routes via the working Live Jobs Page instead.</t>
         </is>
       </c>
     </row>
-    <row r="167" ht="14.25" customHeight="1">
+    <row r="167">
       <c r="A167" t="inlineStr">
         <is>
           <t>Somnigroup International (Tempur Sealy)</t>
@@ -4562,14 +4727,15 @@
           <t>https://www.tempursealy.com/careers/</t>
         </is>
       </c>
-      <c r="D167" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="D167" t="b">
+        <v>1</v>
       </c>
       <c r="E167" t="n">
         <v>224</v>
       </c>
+      <c r="F167" t="inlineStr"/>
+      <c r="G167" t="inlineStr"/>
+      <c r="H167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -4577,19 +4743,21 @@
           <t>Randstad USA</t>
         </is>
       </c>
+      <c r="B168" t="inlineStr"/>
       <c r="C168" t="inlineStr">
         <is>
           <t>https://www.randstadusa.com/jobs/</t>
         </is>
       </c>
-      <c r="D168" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="D168" t="b">
+        <v>1</v>
       </c>
       <c r="E168" t="n">
         <v>160</v>
       </c>
+      <c r="F168" t="inlineStr"/>
+      <c r="G168" t="inlineStr"/>
+      <c r="H168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -4607,14 +4775,15 @@
           <t>https://careers.teksystems.com/us/en</t>
         </is>
       </c>
-      <c r="D169" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="D169" t="b">
+        <v>1</v>
       </c>
       <c r="E169" t="n">
         <v>118</v>
       </c>
+      <c r="F169" t="inlineStr"/>
+      <c r="G169" t="inlineStr"/>
+      <c r="H169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -4632,14 +4801,15 @@
           <t>https://insightglobal.com/find-a-job/</t>
         </is>
       </c>
-      <c r="D170" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="D170" t="b">
+        <v>1</v>
       </c>
       <c r="E170" t="n">
         <v>1</v>
       </c>
+      <c r="F170" t="inlineStr"/>
+      <c r="G170" t="inlineStr"/>
+      <c r="H170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -4647,19 +4817,20 @@
           <t>Apex Systems</t>
         </is>
       </c>
+      <c r="B171" t="inlineStr"/>
       <c r="C171" t="inlineStr">
         <is>
           <t>https://www.apexsystems.com/search-results-usa</t>
         </is>
       </c>
-      <c r="D171" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="D171" t="b">
+        <v>1</v>
       </c>
       <c r="E171" t="n">
         <v>49</v>
       </c>
+      <c r="F171" t="inlineStr"/>
+      <c r="G171" t="inlineStr"/>
       <c r="H171" t="inlineStr">
         <is>
           <t>ATS URL (itcareers.apexsystems.com) intermittently 522s at the Cloudflare edge and always wins over Live Jobs Page in routing regardless; cleared so it routes straight to the working search-results-usa URL instead.</t>
@@ -4672,19 +4843,21 @@
           <t>Kforce</t>
         </is>
       </c>
+      <c r="B172" t="inlineStr"/>
       <c r="C172" t="inlineStr">
         <is>
           <t>https://www.kforce.com/find-work/search-jobs/</t>
         </is>
       </c>
-      <c r="D172" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="D172" t="b">
+        <v>1</v>
       </c>
       <c r="E172" t="n">
         <v>25</v>
       </c>
+      <c r="F172" t="inlineStr"/>
+      <c r="G172" t="inlineStr"/>
+      <c r="H172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -4692,19 +4865,21 @@
           <t>Experis (ManpowerGroup)</t>
         </is>
       </c>
+      <c r="B173" t="inlineStr"/>
       <c r="C173" t="inlineStr">
         <is>
           <t>https://www.experis.com/en/for-job-seekers</t>
         </is>
       </c>
-      <c r="D173" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="D173" t="b">
+        <v>1</v>
       </c>
       <c r="E173" t="n">
         <v>13</v>
       </c>
+      <c r="F173" t="inlineStr"/>
+      <c r="G173" t="inlineStr"/>
+      <c r="H173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -4722,14 +4897,15 @@
           <t>https://www.judge.com/jobs/</t>
         </is>
       </c>
-      <c r="D174" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="D174" t="b">
+        <v>1</v>
       </c>
       <c r="E174" t="n">
         <v>14</v>
       </c>
+      <c r="F174" t="inlineStr"/>
+      <c r="G174" t="inlineStr"/>
+      <c r="H174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -4737,19 +4913,20 @@
           <t>Eliassen Group</t>
         </is>
       </c>
+      <c r="B175" t="inlineStr"/>
       <c r="C175" t="inlineStr">
         <is>
           <t>https://www.eliassen.com/careers</t>
         </is>
       </c>
-      <c r="D175" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
+      <c r="D175" t="b">
+        <v>0</v>
       </c>
       <c r="E175" t="n">
         <v>0</v>
       </c>
+      <c r="F175" t="inlineStr"/>
+      <c r="G175" t="inlineStr"/>
       <c r="H175" t="inlineStr">
         <is>
           <t>careers.eliassen.com (the real consultant job board with a Data category) returns HTTP 403 from nginx to headless Chromium even with stealth patches; a real interactive Chrome session loads it fine, so this is bot-management fingerprinting, not a dead site.</t>
@@ -4772,14 +4949,15 @@
           <t>https://www.roberthalf.com/us/en/find-jobs</t>
         </is>
       </c>
-      <c r="D176" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="D176" t="b">
+        <v>1</v>
       </c>
       <c r="E176" t="n">
         <v>232</v>
       </c>
+      <c r="F176" t="inlineStr"/>
+      <c r="G176" t="inlineStr"/>
+      <c r="H176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -4787,19 +4965,20 @@
           <t>Mphasis</t>
         </is>
       </c>
+      <c r="B177" t="inlineStr"/>
       <c r="C177" t="inlineStr">
         <is>
           <t>https://mphasis.ripplehire.com/candidate/?token=ty4DfyWddnOrtpclQeia&amp;source=CAREERSITE#list</t>
         </is>
       </c>
-      <c r="D177" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="D177" t="b">
+        <v>1</v>
       </c>
       <c r="E177" t="n">
         <v>10</v>
       </c>
+      <c r="F177" t="inlineStr"/>
+      <c r="G177" t="inlineStr"/>
       <c r="H177" t="inlineStr">
         <is>
           <t>careers.mphasis.com only shows jobs after submitting its 3-field search form (experience/title/location), which opens a NEW TAB to mphasis.ripplehire.com with a token in the URL. That token is a stable per-tenant widget key (reproduced identically across separate clicks), not a session token - this exact URL with no filters lists all 189 open jobs directly.</t>
@@ -4812,19 +4991,21 @@
           <t>Pyramid Consulting</t>
         </is>
       </c>
+      <c r="B178" t="inlineStr"/>
       <c r="C178" t="inlineStr">
         <is>
           <t>https://pyramidci.com/careers/</t>
         </is>
       </c>
-      <c r="D178" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="D178" t="b">
+        <v>1</v>
       </c>
       <c r="E178" t="n">
         <v>363</v>
       </c>
+      <c r="F178" t="inlineStr"/>
+      <c r="G178" t="inlineStr"/>
+      <c r="H178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -4842,14 +5023,15 @@
           <t>https://jobs.aerotek.com/us/en</t>
         </is>
       </c>
-      <c r="D179" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="D179" t="b">
+        <v>1</v>
       </c>
       <c r="E179" t="n">
         <v>224</v>
       </c>
+      <c r="F179" t="inlineStr"/>
+      <c r="G179" t="inlineStr"/>
+      <c r="H179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -4857,19 +5039,20 @@
           <t>Kelly Services</t>
         </is>
       </c>
+      <c r="B180" t="inlineStr"/>
       <c r="C180" t="inlineStr">
         <is>
           <t>https://www.mykelly.com/find-jobs/technology-jobs/</t>
         </is>
       </c>
-      <c r="D180" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="D180" t="b">
+        <v>1</v>
       </c>
       <c r="E180" t="n">
         <v>3</v>
       </c>
+      <c r="F180" t="inlineStr"/>
+      <c r="G180" t="inlineStr"/>
       <c r="H180" t="inlineStr">
         <is>
           <t>www.kellyservices.com/find-a-job/ is a marketing splash page with no reachable job list; corrected to the real myKelly technology-jobs search page.</t>
@@ -4882,19 +5065,21 @@
           <t>Motion Recruitment</t>
         </is>
       </c>
-      <c r="C181" s="3" t="inlineStr">
+      <c r="B181" t="inlineStr"/>
+      <c r="C181" t="inlineStr">
         <is>
           <t>https://motionrecruitment.com/tech-jobs/data-engineering</t>
         </is>
       </c>
-      <c r="D181" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="D181" t="b">
+        <v>1</v>
       </c>
       <c r="E181" t="n">
         <v>47</v>
       </c>
+      <c r="F181" t="inlineStr"/>
+      <c r="G181" t="inlineStr"/>
+      <c r="H181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -4902,19 +5087,21 @@
           <t>Dexian</t>
         </is>
       </c>
+      <c r="B182" t="inlineStr"/>
       <c r="C182" t="inlineStr">
         <is>
           <t>https://dexian.com/jobs/</t>
         </is>
       </c>
-      <c r="D182" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="D182" t="b">
+        <v>1</v>
       </c>
       <c r="E182" t="n">
         <v>39</v>
       </c>
+      <c r="F182" t="inlineStr"/>
+      <c r="G182" t="inlineStr"/>
+      <c r="H182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -4922,19 +5109,21 @@
           <t>Built In</t>
         </is>
       </c>
+      <c r="B183" t="inlineStr"/>
       <c r="C183" t="inlineStr">
         <is>
           <t>https://builtin.com/jobs</t>
         </is>
       </c>
-      <c r="D183" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="D183" t="b">
+        <v>1</v>
       </c>
       <c r="E183" t="n">
         <v>1097</v>
       </c>
+      <c r="F183" t="inlineStr"/>
+      <c r="G183" t="inlineStr"/>
+      <c r="H183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -4947,14 +5136,16 @@
           <t>https://globalcareers-msci.icims.com/jobs/</t>
         </is>
       </c>
-      <c r="D184" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="C184" t="inlineStr"/>
+      <c r="D184" t="b">
+        <v>1</v>
       </c>
       <c r="E184" t="n">
         <v>105</v>
       </c>
+      <c r="F184" t="inlineStr"/>
+      <c r="G184" t="inlineStr"/>
+      <c r="H184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -4962,38 +5153,31 @@
           <t>ISNetworld</t>
         </is>
       </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/isn</t>
+        </is>
+      </c>
       <c r="C185" t="inlineStr">
         <is>
           <t>https://www.isnetworld.com/en/careers#jobs</t>
         </is>
       </c>
-      <c r="D185" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
+      <c r="D185" t="b">
+        <v>0</v>
       </c>
       <c r="E185" t="n">
         <v>0</v>
       </c>
+      <c r="F185" t="inlineStr"/>
+      <c r="G185" t="inlineStr"/>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>Greenhouse board token 'isn'; careers page is Drupal + AJAX so the live page resolves to nothing. Board points at isnetworld.com, so gh_jid is the whole job identity.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:B167">
-    <cfRule type="expression" priority="2" dxfId="1">
-      <formula>B2&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C167">
-    <cfRule type="expression" priority="3" dxfId="0">
-      <formula>AND(B2="",C2&lt;&gt;"")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C181" r:id="rId1"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
-  </tableParts>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/config/companies.xlsx
+++ b/config/companies.xlsx
@@ -474,15 +474,14 @@
           <t>https://careers.jpmorgan.com/</t>
         </is>
       </c>
-      <c r="D2" t="b">
-        <v>1</v>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E2" t="n">
-        <v>6987</v>
-      </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
+        <v>7143</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -495,16 +494,14 @@
           <t>https://capitalone.wd12.myworkdayjobs.com/en-US/Capital_One/</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="b">
-        <v>1</v>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E3" t="n">
-        <v>1848</v>
-      </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
+        <v>1868</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -517,16 +514,14 @@
           <t>https://ghr.wd1.myworkdayjobs.com/en-US/Lateral-US/</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="b">
-        <v>1</v>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E4" t="n">
-        <v>2095</v>
-      </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
+        <v>2089</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -544,15 +539,14 @@
           <t>https://www.goldmansachs.com/careers/</t>
         </is>
       </c>
-      <c r="D5" t="b">
-        <v>1</v>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E5" t="n">
         <v>820</v>
       </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -570,15 +564,14 @@
           <t>https://www.morganstanley.com/careers/career-opportunities-search</t>
         </is>
       </c>
-      <c r="D6" t="b">
-        <v>1</v>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E6" t="n">
-        <v>1315</v>
-      </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
+        <v>1330</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -591,16 +584,14 @@
           <t>https://wf.wd1.myworkdayjobs.com/en-US/WellsFargoJobs/</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="b">
-        <v>1</v>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E7" t="n">
-        <v>1593</v>
-      </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
+        <v>1684</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -613,16 +604,14 @@
           <t>https://fmr.wd1.myworkdayjobs.com/en-US/FidelityCareers/</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="b">
-        <v>1</v>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E8" t="n">
-        <v>547</v>
-      </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
+        <v>560</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -640,15 +629,14 @@
           <t>https://jobs.libertymutualgroup.com/locations/plano-tx/</t>
         </is>
       </c>
-      <c r="D9" t="b">
-        <v>1</v>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E9" t="n">
-        <v>206</v>
-      </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
+        <v>207</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -661,16 +649,14 @@
           <t>https://texascapitalbank.wd12.myworkdayjobs.com/en-US/Careers/</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="b">
-        <v>1</v>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E10" t="n">
-        <v>84</v>
-      </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
+        <v>86</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -683,16 +669,14 @@
           <t>https://travelers.wd5.myworkdayjobs.com/en-US/External/</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="b">
-        <v>1</v>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E11" t="n">
-        <v>350</v>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
+        <v>361</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -705,16 +689,14 @@
           <t>https://geico.wd1.myworkdayjobs.com/en-US/External/</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="b">
-        <v>1</v>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E12" t="n">
-        <v>270</v>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
+        <v>282</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -727,12 +709,13 @@
           <t>https://recruiting.paylocity.com/recruiting/jobs/All/1934ff17-218d-4324-bec6-ecc4c5ddcfc4/Texans-Credit-Union</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="b">
-        <v>1</v>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E13" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -766,15 +749,14 @@
           <t>https://www.nasdaq.com/about/careers</t>
         </is>
       </c>
-      <c r="D14" t="b">
-        <v>1</v>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E14" t="n">
-        <v>182</v>
-      </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
+        <v>180</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -792,11 +774,13 @@
           <t>https://www.ice.com/careers</t>
         </is>
       </c>
-      <c r="D15" t="b">
-        <v>1</v>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E15" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -825,16 +809,14 @@
           <t>https://careers.fiserv.com/us/en/search-results</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="b">
-        <v>1</v>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E16" t="n">
-        <v>355</v>
-      </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
+        <v>370</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -842,20 +824,19 @@
           <t>FM</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
           <t>https://careers.fm.com/</t>
         </is>
       </c>
-      <c r="D17" t="b">
-        <v>1</v>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E17" t="n">
-        <v>44</v>
-      </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
+        <v>43</v>
+      </c>
       <c r="H17" t="inlineStr">
         <is>
           <t>2026-08-26: replaced dead ATS URL (careersatfm.com does not resolve) and dead live page (jobs.fm.com refuses connections) with careers.fm.com, verified returning 44 jobs.</t>
@@ -878,11 +859,13 @@
           <t>https://careers.t-mobile.com/jobs</t>
         </is>
       </c>
-      <c r="D18" t="b">
-        <v>1</v>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E18" t="n">
-        <v>1995</v>
+        <v>2000</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -916,15 +899,14 @@
           <t>https://careers.ti.com/</t>
         </is>
       </c>
-      <c r="D19" t="b">
-        <v>1</v>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E19" t="n">
-        <v>590</v>
-      </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
+        <v>607</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -937,16 +919,14 @@
           <t>https://www.amazon.jobs/en/</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="b">
-        <v>1</v>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E20" t="n">
-        <v>10000</v>
-      </c>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
+        <v>9999</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -964,15 +944,14 @@
           <t>https://www.hcltech.com/careers</t>
         </is>
       </c>
-      <c r="D21" t="b">
-        <v>0</v>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
       </c>
       <c r="E21" t="n">
         <v>0</v>
       </c>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -990,8 +969,10 @@
           <t>https://app.jobzmall.com/boingo-wireless/jobs</t>
         </is>
       </c>
-      <c r="D22" t="b">
-        <v>1</v>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E22" t="n">
         <v>4</v>
@@ -1018,17 +999,18 @@
           <t>CommScope</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr">
         <is>
           <t>https://jobs.commscope.com/</t>
         </is>
       </c>
-      <c r="D23" t="b">
-        <v>1</v>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E23" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1062,15 +1044,14 @@
           <t>https://careers.honeywell.com/</t>
         </is>
       </c>
-      <c r="D24" t="b">
-        <v>1</v>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E24" t="n">
-        <v>1338</v>
-      </c>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
+        <v>1334</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1083,16 +1064,14 @@
           <t>https://boeing.wd1.myworkdayjobs.com/external_subsidiary/</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="b">
-        <v>1</v>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E25" t="n">
-        <v>612</v>
-      </c>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
+        <v>620</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1110,11 +1089,13 @@
           <t>https://careers.rtx.com/global/en/collins-aerospace</t>
         </is>
       </c>
-      <c r="D26" t="b">
-        <v>1</v>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E26" t="n">
-        <v>4431</v>
+        <v>4500</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1148,15 +1129,14 @@
           <t>https://www.genpact.com/careers</t>
         </is>
       </c>
-      <c r="D27" t="b">
-        <v>1</v>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E27" t="n">
-        <v>2000</v>
-      </c>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
+        <v>1990</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1174,15 +1154,14 @@
           <t>https://www.yahooinc.com/careers/</t>
         </is>
       </c>
-      <c r="D28" t="b">
-        <v>1</v>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E28" t="n">
-        <v>88</v>
-      </c>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
+        <v>89</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1200,11 +1179,13 @@
           <t>https://careers.chewy.com/</t>
         </is>
       </c>
-      <c r="D29" t="b">
-        <v>1</v>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E29" t="n">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1228,17 +1209,23 @@
           <t>PepsiCo / Frito-Lay North America</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>https://globalflcareers-pepsico.icims.com/jobs/455798/login</t>
+        </is>
+      </c>
       <c r="C30" t="inlineStr">
         <is>
           <t>https://www.pepsicojobs.com/</t>
         </is>
       </c>
-      <c r="D30" t="b">
-        <v>1</v>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E30" t="n">
-        <v>10</v>
+        <v>305</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1272,8 +1259,10 @@
           <t>https://careers.fedex.com/</t>
         </is>
       </c>
-      <c r="D31" t="b">
-        <v>1</v>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E31" t="n">
         <v>46</v>
@@ -1305,9 +1294,10 @@
           <t>https://walmart.wd5.myworkdayjobs.com/WalmartExternal/</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="b">
-        <v>0</v>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
       </c>
       <c r="E32" t="n">
         <v>0</v>
@@ -1344,15 +1334,14 @@
           <t>https://www.fluor.com/careers/</t>
         </is>
       </c>
-      <c r="D33" t="b">
-        <v>1</v>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E33" t="n">
-        <v>640</v>
-      </c>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
+        <v>617</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1360,14 +1349,15 @@
           <t>Builders FirstSource</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr">
         <is>
           <t>https://careers.bldr.com/jobs</t>
         </is>
       </c>
-      <c r="D34" t="b">
-        <v>1</v>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E34" t="n">
         <v>410</v>
@@ -1404,11 +1394,13 @@
           <t>https://jobs.cmc.com/</t>
         </is>
       </c>
-      <c r="D35" t="b">
-        <v>1</v>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E35" t="n">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -1442,11 +1434,13 @@
           <t>https://careers.prim.com/</t>
         </is>
       </c>
-      <c r="D36" t="b">
-        <v>1</v>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E36" t="n">
-        <v>706</v>
+        <v>702</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -1483,15 +1477,14 @@
           <t>https://www.atmosenergy.com/careers/</t>
         </is>
       </c>
-      <c r="D37" t="b">
-        <v>1</v>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E37" t="n">
         <v>34</v>
       </c>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1509,11 +1502,13 @@
           <t>https://careers.7-eleven.com/</t>
         </is>
       </c>
-      <c r="D38" t="b">
-        <v>1</v>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E38" t="n">
-        <v>5263</v>
+        <v>5297</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -1547,15 +1542,14 @@
           <t>https://careers.gamestop.com/us/en</t>
         </is>
       </c>
-      <c r="D39" t="b">
-        <v>1</v>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E39" t="n">
-        <v>5181</v>
-      </c>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
+        <v>5191</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1573,15 +1567,14 @@
           <t>https://jobs.bnsf.com/</t>
         </is>
       </c>
-      <c r="D40" t="b">
-        <v>1</v>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E40" t="n">
-        <v>60</v>
-      </c>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
+        <v>63</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1599,15 +1592,14 @@
           <t>https://www.copart.com/content/us/en/careers</t>
         </is>
       </c>
-      <c r="D41" t="b">
-        <v>1</v>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E41" t="n">
-        <v>352</v>
-      </c>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
+        <v>357</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1620,16 +1612,14 @@
           <t>https://www.google.com/about/careers/applications/jobs/results/</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr"/>
-      <c r="D42" t="b">
-        <v>1</v>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E42" t="n">
         <v>35</v>
       </c>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1647,15 +1637,14 @@
           <t>https://careers.oracle.com/</t>
         </is>
       </c>
-      <c r="D43" t="b">
-        <v>1</v>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E43" t="n">
-        <v>2155</v>
-      </c>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
+        <v>2228</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1673,15 +1662,14 @@
           <t>https://www.ibm.com/careers</t>
         </is>
       </c>
-      <c r="D44" t="b">
-        <v>1</v>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E44" t="n">
-        <v>1046</v>
-      </c>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
+        <v>522</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1699,15 +1687,14 @@
           <t>https://careers.salesforce.com/</t>
         </is>
       </c>
-      <c r="D45" t="b">
-        <v>1</v>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E45" t="n">
-        <v>1479</v>
-      </c>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
+        <v>1482</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1725,15 +1712,14 @@
           <t>https://jobs.cisco.com/</t>
         </is>
       </c>
-      <c r="D46" t="b">
-        <v>1</v>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E46" t="n">
-        <v>1235</v>
-      </c>
-      <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
+        <v>1262</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1751,15 +1737,14 @@
           <t>https://www.nokia.com/about-us/careers/</t>
         </is>
       </c>
-      <c r="D47" t="b">
-        <v>1</v>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E47" t="n">
-        <v>566</v>
-      </c>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
+        <v>577</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1777,15 +1762,14 @@
           <t>https://www.ericsson.com/en/careers</t>
         </is>
       </c>
-      <c r="D48" t="b">
-        <v>0</v>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E48" t="n">
-        <v>0</v>
-      </c>
-      <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
+        <v>20</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1803,15 +1787,14 @@
           <t>https://www.samsungcareers.com/</t>
         </is>
       </c>
-      <c r="D49" t="b">
-        <v>1</v>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E49" t="n">
-        <v>615</v>
-      </c>
-      <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
+        <v>630</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1829,15 +1812,14 @@
           <t>https://www.fujitsu.com/global/about/careers/</t>
         </is>
       </c>
-      <c r="D50" t="b">
-        <v>0</v>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
       </c>
       <c r="E50" t="n">
         <v>0</v>
       </c>
-      <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1855,15 +1837,14 @@
           <t>https://www.nttdata.com/en-us/careers</t>
         </is>
       </c>
-      <c r="D51" t="b">
-        <v>1</v>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E51" t="n">
-        <v>822</v>
-      </c>
-      <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
+        <v>845</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1876,16 +1857,14 @@
           <t>https://www.infosys.com/careers/</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr"/>
-      <c r="D52" t="b">
-        <v>0</v>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
       </c>
       <c r="E52" t="n">
         <v>0</v>
       </c>
-      <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1893,21 +1872,19 @@
           <t>Cognizant</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr"/>
       <c r="C53" t="inlineStr">
         <is>
           <t>https://careers.cognizant.com/</t>
         </is>
       </c>
-      <c r="D53" t="b">
-        <v>1</v>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E53" t="n">
-        <v>360</v>
-      </c>
-      <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
+        <v>35</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1925,15 +1902,14 @@
           <t>https://www.capgemini.com/careers/</t>
         </is>
       </c>
-      <c r="D54" t="b">
-        <v>1</v>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E54" t="n">
         <v>11</v>
       </c>
-      <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1946,16 +1922,14 @@
           <t>https://accenture.wd103.myworkdayjobs.com/en-US/AccentureCareers/</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr"/>
-      <c r="D55" t="b">
-        <v>1</v>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E55" t="n">
-        <v>1967</v>
-      </c>
-      <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
+        <v>1740</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1973,15 +1947,14 @@
           <t>https://apply.deloitte.com/</t>
         </is>
       </c>
-      <c r="D56" t="b">
-        <v>1</v>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E56" t="n">
-        <v>1149</v>
-      </c>
-      <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
+        <v>1152</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1989,20 +1962,19 @@
           <t>PwC</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr"/>
       <c r="C57" t="inlineStr">
         <is>
           <t>https://www.pwc.com/us/en/careers.html</t>
         </is>
       </c>
-      <c r="D57" t="b">
-        <v>1</v>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E57" t="n">
         <v>657</v>
       </c>
-      <c r="F57" t="inlineStr"/>
-      <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr">
         <is>
           <t>2026-08-26: jobs.us.pwc.com fails TLS verification and 404s when that is ignored - the host is gone. Verified 43 jobs on the main careers page.</t>
@@ -2025,15 +1997,14 @@
           <t>https://careers.ey.com/</t>
         </is>
       </c>
-      <c r="D58" t="b">
-        <v>1</v>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E58" t="n">
-        <v>7605</v>
-      </c>
-      <c r="F58" t="inlineStr"/>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
+        <v>7725</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2041,21 +2012,19 @@
           <t>KPMG</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr"/>
       <c r="C59" t="inlineStr">
         <is>
           <t>https://www.kpmguscareers.com/</t>
         </is>
       </c>
-      <c r="D59" t="b">
-        <v>1</v>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E59" t="n">
-        <v>6</v>
-      </c>
-      <c r="F59" t="inlineStr"/>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
+        <v>7</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2073,15 +2042,14 @@
           <t>https://www.cgi.com/en/careers</t>
         </is>
       </c>
-      <c r="D60" t="b">
-        <v>0</v>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E60" t="n">
-        <v>0</v>
-      </c>
-      <c r="F60" t="inlineStr"/>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
+        <v>100</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2089,21 +2057,19 @@
           <t>DXC Technology</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr"/>
       <c r="C61" t="inlineStr">
         <is>
           <t>https://careers.dxc.com/</t>
         </is>
       </c>
-      <c r="D61" t="b">
-        <v>1</v>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E61" t="n">
-        <v>385</v>
-      </c>
-      <c r="F61" t="inlineStr"/>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
+        <v>391</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2121,15 +2087,14 @@
           <t>https://careers.hpe.com/</t>
         </is>
       </c>
-      <c r="D62" t="b">
-        <v>1</v>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E62" t="n">
-        <v>1112</v>
-      </c>
-      <c r="F62" t="inlineStr"/>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
+        <v>1139</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2147,15 +2112,14 @@
           <t>https://jobs.dell.com/</t>
         </is>
       </c>
-      <c r="D63" t="b">
-        <v>1</v>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E63" t="n">
-        <v>387</v>
-      </c>
-      <c r="F63" t="inlineStr"/>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr"/>
+        <v>413</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2173,15 +2137,14 @@
           <t>https://jobs.paloaltonetworks.com/</t>
         </is>
       </c>
-      <c r="D64" t="b">
-        <v>1</v>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E64" t="n">
-        <v>1310</v>
-      </c>
-      <c r="F64" t="inlineStr"/>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
+        <v>1322</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2199,15 +2162,14 @@
           <t>https://www.crowdstrike.com/en-us/careers/</t>
         </is>
       </c>
-      <c r="D65" t="b">
-        <v>1</v>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E65" t="n">
-        <v>429</v>
-      </c>
-      <c r="F65" t="inlineStr"/>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr"/>
+        <v>423</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2220,16 +2182,14 @@
           <t>https://careers.smartrecruiters.com/ServiceNow</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr"/>
-      <c r="D66" t="b">
-        <v>1</v>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E66" t="n">
-        <v>557</v>
-      </c>
-      <c r="F66" t="inlineStr"/>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr"/>
+        <v>574</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2242,16 +2202,14 @@
           <t>https://workday.wd5.myworkdayjobs.com/Workday</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr"/>
-      <c r="D67" t="b">
-        <v>1</v>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E67" t="n">
-        <v>358</v>
-      </c>
-      <c r="F67" t="inlineStr"/>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
+        <v>372</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2269,15 +2227,14 @@
           <t>https://careers.thomsonreuters.com/</t>
         </is>
       </c>
-      <c r="D68" t="b">
-        <v>1</v>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E68" t="n">
-        <v>391</v>
-      </c>
-      <c r="F68" t="inlineStr"/>
-      <c r="G68" t="inlineStr"/>
-      <c r="H68" t="inlineStr"/>
+        <v>423</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2285,21 +2242,19 @@
           <t>Tyler Technologies</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr"/>
       <c r="C69" t="inlineStr">
         <is>
           <t>https://www.tylertech.com/careers/job-listings</t>
         </is>
       </c>
-      <c r="D69" t="b">
-        <v>1</v>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E69" t="n">
         <v>10</v>
       </c>
-      <c r="F69" t="inlineStr"/>
-      <c r="G69" t="inlineStr"/>
-      <c r="H69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2317,15 +2272,14 @@
           <t>https://www.alkami.com/careers/</t>
         </is>
       </c>
-      <c r="D70" t="b">
-        <v>1</v>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E70" t="n">
-        <v>70</v>
-      </c>
-      <c r="F70" t="inlineStr"/>
-      <c r="G70" t="inlineStr"/>
-      <c r="H70" t="inlineStr"/>
+        <v>76</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2343,15 +2297,14 @@
           <t>https://careers.sabre.com/</t>
         </is>
       </c>
-      <c r="D71" t="b">
-        <v>1</v>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E71" t="n">
-        <v>121</v>
-      </c>
-      <c r="F71" t="inlineStr"/>
-      <c r="G71" t="inlineStr"/>
-      <c r="H71" t="inlineStr"/>
+        <v>123</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2369,15 +2322,14 @@
           <t>https://careers.southwestair.com/</t>
         </is>
       </c>
-      <c r="D72" t="b">
-        <v>1</v>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E72" t="n">
-        <v>21</v>
-      </c>
-      <c r="F72" t="inlineStr"/>
-      <c r="G72" t="inlineStr"/>
-      <c r="H72" t="inlineStr"/>
+        <v>30</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2385,21 +2337,19 @@
           <t>American Airlines</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr"/>
       <c r="C73" t="inlineStr">
         <is>
           <t>https://jobs.aa.com/</t>
         </is>
       </c>
-      <c r="D73" t="b">
-        <v>1</v>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E73" t="n">
-        <v>68</v>
-      </c>
-      <c r="F73" t="inlineStr"/>
-      <c r="G73" t="inlineStr"/>
-      <c r="H73" t="inlineStr"/>
+        <v>70</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2417,15 +2367,14 @@
           <t>https://careers.caterpillar.com/</t>
         </is>
       </c>
-      <c r="D74" t="b">
-        <v>1</v>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E74" t="n">
-        <v>863</v>
-      </c>
-      <c r="F74" t="inlineStr"/>
-      <c r="G74" t="inlineStr"/>
-      <c r="H74" t="inlineStr"/>
+        <v>880</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2438,16 +2387,14 @@
           <t>https://toyota.wd503.myworkdayjobs.com/en-US/TMNA/</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr"/>
-      <c r="D75" t="b">
-        <v>1</v>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E75" t="n">
-        <v>107</v>
-      </c>
-      <c r="F75" t="inlineStr"/>
-      <c r="G75" t="inlineStr"/>
-      <c r="H75" t="inlineStr"/>
+        <v>113</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2460,16 +2407,14 @@
           <t>https://mckesson.wd3.myworkdayjobs.com/en-US/External_Careers/</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr"/>
-      <c r="D76" t="b">
-        <v>1</v>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E76" t="n">
-        <v>489</v>
-      </c>
-      <c r="F76" t="inlineStr"/>
-      <c r="G76" t="inlineStr"/>
-      <c r="H76" t="inlineStr"/>
+        <v>491</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2487,15 +2432,14 @@
           <t>https://careers.cotality.com/</t>
         </is>
       </c>
-      <c r="D77" t="b">
-        <v>1</v>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E77" t="n">
-        <v>44</v>
-      </c>
-      <c r="F77" t="inlineStr"/>
-      <c r="G77" t="inlineStr"/>
-      <c r="H77" t="inlineStr"/>
+        <v>34</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2503,21 +2447,19 @@
           <t>Equinix</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr"/>
       <c r="C78" t="inlineStr">
         <is>
           <t>https://careers.equinix.com/</t>
         </is>
       </c>
-      <c r="D78" t="b">
-        <v>1</v>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E78" t="n">
         <v>39</v>
       </c>
-      <c r="F78" t="inlineStr"/>
-      <c r="G78" t="inlineStr"/>
-      <c r="H78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2535,15 +2477,14 @@
           <t>https://careers.digitalrealty.com/</t>
         </is>
       </c>
-      <c r="D79" t="b">
-        <v>1</v>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E79" t="n">
-        <v>192</v>
-      </c>
-      <c r="F79" t="inlineStr"/>
-      <c r="G79" t="inlineStr"/>
-      <c r="H79" t="inlineStr"/>
+        <v>190</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2561,15 +2502,14 @@
           <t>https://www.cyrusone.com/careers</t>
         </is>
       </c>
-      <c r="D80" t="b">
-        <v>1</v>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E80" t="n">
         <v>99</v>
       </c>
-      <c r="F80" t="inlineStr"/>
-      <c r="G80" t="inlineStr"/>
-      <c r="H80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -2587,15 +2527,14 @@
           <t>https://careers.qorvo.com/</t>
         </is>
       </c>
-      <c r="D81" t="b">
-        <v>1</v>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E81" t="n">
-        <v>237</v>
-      </c>
-      <c r="F81" t="inlineStr"/>
-      <c r="G81" t="inlineStr"/>
-      <c r="H81" t="inlineStr"/>
+        <v>235</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -2613,15 +2552,14 @@
           <t>https://careers.rtx.com/</t>
         </is>
       </c>
-      <c r="D82" t="b">
-        <v>1</v>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E82" t="n">
-        <v>4431</v>
-      </c>
-      <c r="F82" t="inlineStr"/>
-      <c r="G82" t="inlineStr"/>
-      <c r="H82" t="inlineStr"/>
+        <v>4500</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -2629,20 +2567,19 @@
           <t>Lockheed Martin</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr"/>
       <c r="C83" t="inlineStr">
         <is>
           <t>https://lockheedmartin.eightfold.ai/careers</t>
         </is>
       </c>
-      <c r="D83" t="b">
-        <v>1</v>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E83" t="n">
-        <v>20</v>
-      </c>
-      <c r="F83" t="inlineStr"/>
-      <c r="G83" t="inlineStr"/>
+        <v>19</v>
+      </c>
       <c r="H83" t="inlineStr">
         <is>
           <t>2026-08-26: lockheedmartinjobs.com is a dead redirect stub (404 via lockheedmartin.com). Real board is the Eightfold tenant; its API answers 403 so the browser route is used. Verified 20 jobs.</t>
@@ -2665,15 +2602,14 @@
           <t>https://jobs.baesystems.com/</t>
         </is>
       </c>
-      <c r="D84" t="b">
-        <v>1</v>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E84" t="n">
-        <v>1868</v>
-      </c>
-      <c r="F84" t="inlineStr"/>
-      <c r="G84" t="inlineStr"/>
-      <c r="H84" t="inlineStr"/>
+        <v>1850</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -2691,15 +2627,14 @@
           <t>https://careers.l3harris.com/</t>
         </is>
       </c>
-      <c r="D85" t="b">
-        <v>1</v>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E85" t="n">
-        <v>1914</v>
-      </c>
-      <c r="F85" t="inlineStr"/>
-      <c r="G85" t="inlineStr"/>
-      <c r="H85" t="inlineStr"/>
+        <v>1934</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -2712,16 +2647,14 @@
           <t>https://bswhealth.taleo.net/careersection/ex/jobsearch.ftl</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr"/>
-      <c r="D86" t="b">
-        <v>1</v>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E86" t="n">
-        <v>320</v>
-      </c>
-      <c r="F86" t="inlineStr"/>
-      <c r="G86" t="inlineStr"/>
-      <c r="H86" t="inlineStr"/>
+        <v>310</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -2739,14 +2672,14 @@
           <t>https://jobs.texashealth.org/</t>
         </is>
       </c>
-      <c r="D87" t="b">
-        <v>1</v>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E87" t="n">
-        <v>400</v>
-      </c>
-      <c r="F87" t="inlineStr"/>
-      <c r="G87" t="inlineStr"/>
+        <v>407</v>
+      </c>
       <c r="H87" t="inlineStr">
         <is>
           <t>2026-08-26: the Taleo moresearch.ftl entry point returns 0 rows. The branded portal renders the same Taleo data and verified 391 jobs.</t>
@@ -2764,16 +2697,14 @@
           <t>https://utsw.referrals.selectminds.com/?lang=en</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr"/>
-      <c r="D88" t="b">
-        <v>1</v>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E88" t="n">
         <v>10</v>
       </c>
-      <c r="F88" t="inlineStr"/>
-      <c r="G88" t="inlineStr"/>
-      <c r="H88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -2781,21 +2712,19 @@
           <t>Medical City Healthcare / HCA</t>
         </is>
       </c>
-      <c r="B89" t="inlineStr"/>
       <c r="C89" t="inlineStr">
         <is>
           <t>https://careers.hcahealthcare.com/</t>
         </is>
       </c>
-      <c r="D89" t="b">
-        <v>0</v>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
       </c>
       <c r="E89" t="n">
         <v>0</v>
       </c>
-      <c r="F89" t="inlineStr"/>
-      <c r="G89" t="inlineStr"/>
-      <c r="H89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -2813,15 +2742,14 @@
           <t>https://jobsearch.childrens.com/</t>
         </is>
       </c>
-      <c r="D90" t="b">
-        <v>1</v>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E90" t="n">
-        <v>189</v>
-      </c>
-      <c r="F90" t="inlineStr"/>
-      <c r="G90" t="inlineStr"/>
-      <c r="H90" t="inlineStr"/>
+        <v>185</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -2829,21 +2757,19 @@
           <t>Parkland Health</t>
         </is>
       </c>
-      <c r="B91" t="inlineStr"/>
       <c r="C91" t="inlineStr">
         <is>
           <t>https://jobs.parklandcareers.com/</t>
         </is>
       </c>
-      <c r="D91" t="b">
-        <v>1</v>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E91" t="n">
         <v>10</v>
       </c>
-      <c r="F91" t="inlineStr"/>
-      <c r="G91" t="inlineStr"/>
-      <c r="H91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -2861,15 +2787,14 @@
           <t>https://jobs.methodisthealthsystem.org/</t>
         </is>
       </c>
-      <c r="D92" t="b">
-        <v>1</v>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E92" t="n">
-        <v>712</v>
-      </c>
-      <c r="F92" t="inlineStr"/>
-      <c r="G92" t="inlineStr"/>
-      <c r="H92" t="inlineStr"/>
+        <v>725</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -2887,15 +2812,14 @@
           <t>https://careers.cookchildrens.org/</t>
         </is>
       </c>
-      <c r="D93" t="b">
-        <v>1</v>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E93" t="n">
-        <v>253</v>
-      </c>
-      <c r="F93" t="inlineStr"/>
-      <c r="G93" t="inlineStr"/>
-      <c r="H93" t="inlineStr"/>
+        <v>247</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -2913,15 +2837,14 @@
           <t>https://jobs.tenethealth.com/</t>
         </is>
       </c>
-      <c r="D94" t="b">
-        <v>1</v>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E94" t="n">
-        <v>2849</v>
-      </c>
-      <c r="F94" t="inlineStr"/>
-      <c r="G94" t="inlineStr"/>
-      <c r="H94" t="inlineStr"/>
+        <v>2895</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -2939,15 +2862,14 @@
           <t>https://jobs.tenethealth.com/conifer-health-solutions</t>
         </is>
       </c>
-      <c r="D95" t="b">
-        <v>1</v>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E95" t="n">
-        <v>3344</v>
-      </c>
-      <c r="F95" t="inlineStr"/>
-      <c r="G95" t="inlineStr"/>
-      <c r="H95" t="inlineStr"/>
+        <v>3398</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -2960,16 +2882,14 @@
           <t>https://mckesson.wd3.myworkdayjobs.com/en-US/External_Careers/</t>
         </is>
       </c>
-      <c r="C96" t="inlineStr"/>
-      <c r="D96" t="b">
-        <v>1</v>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E96" t="n">
-        <v>489</v>
-      </c>
-      <c r="F96" t="inlineStr"/>
-      <c r="G96" t="inlineStr"/>
-      <c r="H96" t="inlineStr"/>
+        <v>491</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -2977,21 +2897,19 @@
           <t>Vizient</t>
         </is>
       </c>
-      <c r="B97" t="inlineStr"/>
       <c r="C97" t="inlineStr">
         <is>
           <t>https://careers.vizientinc.com/</t>
         </is>
       </c>
-      <c r="D97" t="b">
-        <v>0</v>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E97" t="n">
-        <v>0</v>
-      </c>
-      <c r="F97" t="inlineStr"/>
-      <c r="G97" t="inlineStr"/>
-      <c r="H97" t="inlineStr"/>
+        <v>217</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3009,15 +2927,14 @@
           <t>https://careers.cencora.com/</t>
         </is>
       </c>
-      <c r="D98" t="b">
-        <v>1</v>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E98" t="n">
-        <v>960</v>
-      </c>
-      <c r="F98" t="inlineStr"/>
-      <c r="G98" t="inlineStr"/>
-      <c r="H98" t="inlineStr"/>
+        <v>938</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3025,21 +2942,19 @@
           <t>Cardinal Health</t>
         </is>
       </c>
-      <c r="B99" t="inlineStr"/>
       <c r="C99" t="inlineStr">
         <is>
           <t>https://jobs.cardinalhealth.com/</t>
         </is>
       </c>
-      <c r="D99" t="b">
-        <v>1</v>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E99" t="n">
-        <v>6</v>
-      </c>
-      <c r="F99" t="inlineStr"/>
-      <c r="G99" t="inlineStr"/>
-      <c r="H99" t="inlineStr"/>
+        <v>7</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -3057,14 +2972,14 @@
           <t>https://jobs.cvshealth.com/us/en</t>
         </is>
       </c>
-      <c r="D100" t="b">
-        <v>1</v>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E100" t="n">
-        <v>5864</v>
-      </c>
-      <c r="F100" t="inlineStr"/>
-      <c r="G100" t="inlineStr"/>
+        <v>6680</v>
+      </c>
       <c r="H100" t="inlineStr">
         <is>
           <t>2026-08-26: moved off the Phenom board (jobs.cvshealth.com) to the Workday tenant its own applyUrl links to. Phenom served this tenant in relevance order - measured, offset 0 held a 12 Jun posting and offset 7,990 one from 24 Aug - so its 8,000-row ceiling hid jobs of every age including current ones. Workday CXS is posting-date descending (offset 0 'Posted Today', 6,000 '9 Days Ago', 12,000 '23 Days Ago'), so the walk stops at the freshness window instead: 6,777 jobs in 220s, oldest 12 days, vs 8,000 in 432s.</t>
@@ -3087,14 +3002,14 @@
           <t>https://www.signifyhealth.com/careers</t>
         </is>
       </c>
-      <c r="D101" t="b">
-        <v>1</v>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E101" t="n">
         <v>8000</v>
       </c>
-      <c r="F101" t="inlineStr"/>
-      <c r="G101" t="inlineStr"/>
       <c r="H101" t="inlineStr">
         <is>
           <t>2026-08-26: DUPLICATE OF CVS. signifyhealth.com/careers redirects to jobs.cvshealth.com/us/en/signify-health, and that sub-path has no board of its own - the search endpoint ignores it and returns CVS's full 19,126, so this row scrapes CVS's board a second time (~430s) and files the result under the wrong employer. There is no Signify site on the CVS Workday tenant either (Signify_Health / SignifyHealth / Signify_Health_Careers all 404). Consider removing this row.</t>
@@ -3117,15 +3032,14 @@
           <t>https://careers.hcsc.com/</t>
         </is>
       </c>
-      <c r="D102" t="b">
-        <v>1</v>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E102" t="n">
-        <v>114</v>
-      </c>
-      <c r="F102" t="inlineStr"/>
-      <c r="G102" t="inlineStr"/>
-      <c r="H102" t="inlineStr"/>
+        <v>119</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -3133,21 +3047,19 @@
           <t>UnitedHealth Group</t>
         </is>
       </c>
-      <c r="B103" t="inlineStr"/>
       <c r="C103" t="inlineStr">
         <is>
           <t>https://careers.unitedhealthgroup.com/</t>
         </is>
       </c>
-      <c r="D103" t="b">
-        <v>1</v>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E103" t="n">
         <v>18</v>
       </c>
-      <c r="F103" t="inlineStr"/>
-      <c r="G103" t="inlineStr"/>
-      <c r="H103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -3155,21 +3067,19 @@
           <t>Optum</t>
         </is>
       </c>
-      <c r="B104" t="inlineStr"/>
       <c r="C104" t="inlineStr">
         <is>
           <t>https://careers.unitedhealthgroup.com/job-search-results/?brand=Optum</t>
         </is>
       </c>
-      <c r="D104" t="b">
-        <v>1</v>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E104" t="n">
         <v>18</v>
       </c>
-      <c r="F104" t="inlineStr"/>
-      <c r="G104" t="inlineStr"/>
-      <c r="H104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -3187,15 +3097,14 @@
           <t>https://jobs.thecignagroup.com/</t>
         </is>
       </c>
-      <c r="D105" t="b">
-        <v>1</v>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E105" t="n">
-        <v>558</v>
-      </c>
-      <c r="F105" t="inlineStr"/>
-      <c r="G105" t="inlineStr"/>
-      <c r="H105" t="inlineStr"/>
+        <v>549</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -3213,15 +3122,14 @@
           <t>https://careers.elevancehealth.com/</t>
         </is>
       </c>
-      <c r="D106" t="b">
-        <v>1</v>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E106" t="n">
-        <v>301</v>
-      </c>
-      <c r="F106" t="inlineStr"/>
-      <c r="G106" t="inlineStr"/>
-      <c r="H106" t="inlineStr"/>
+        <v>323</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -3239,15 +3147,14 @@
           <t>https://jobs.centene.com/</t>
         </is>
       </c>
-      <c r="D107" t="b">
-        <v>1</v>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E107" t="n">
         <v>216</v>
       </c>
-      <c r="F107" t="inlineStr"/>
-      <c r="G107" t="inlineStr"/>
-      <c r="H107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -3265,15 +3172,14 @@
           <t>https://jobs.centene.com/</t>
         </is>
       </c>
-      <c r="D108" t="b">
-        <v>1</v>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E108" t="n">
         <v>216</v>
       </c>
-      <c r="F108" t="inlineStr"/>
-      <c r="G108" t="inlineStr"/>
-      <c r="H108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -3291,15 +3197,14 @@
           <t>https://careers.humana.com/</t>
         </is>
       </c>
-      <c r="D109" t="b">
-        <v>1</v>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E109" t="n">
-        <v>2151</v>
-      </c>
-      <c r="F109" t="inlineStr"/>
-      <c r="G109" t="inlineStr"/>
-      <c r="H109" t="inlineStr"/>
+        <v>2133</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -3317,15 +3222,14 @@
           <t>https://careers.molinahealthcare.com/</t>
         </is>
       </c>
-      <c r="D110" t="b">
-        <v>1</v>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E110" t="n">
-        <v>331</v>
-      </c>
-      <c r="F110" t="inlineStr"/>
-      <c r="G110" t="inlineStr"/>
-      <c r="H110" t="inlineStr"/>
+        <v>324</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -3343,15 +3247,14 @@
           <t>https://careers.concentra.com/</t>
         </is>
       </c>
-      <c r="D111" t="b">
-        <v>1</v>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E111" t="n">
-        <v>1189</v>
-      </c>
-      <c r="F111" t="inlineStr"/>
-      <c r="G111" t="inlineStr"/>
-      <c r="H111" t="inlineStr"/>
+        <v>1198</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -3359,21 +3262,19 @@
           <t>USMD Health System</t>
         </is>
       </c>
-      <c r="B112" t="inlineStr"/>
       <c r="C112" t="inlineStr">
         <is>
           <t>https://careers.unitedhealthgroup.com/</t>
         </is>
       </c>
-      <c r="D112" t="b">
-        <v>1</v>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E112" t="n">
         <v>18</v>
       </c>
-      <c r="F112" t="inlineStr"/>
-      <c r="G112" t="inlineStr"/>
-      <c r="H112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -3391,15 +3292,14 @@
           <t>https://www.texasoncology.com/careers</t>
         </is>
       </c>
-      <c r="D113" t="b">
-        <v>1</v>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E113" t="n">
         <v>691</v>
       </c>
-      <c r="F113" t="inlineStr"/>
-      <c r="G113" t="inlineStr"/>
-      <c r="H113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -3417,15 +3317,14 @@
           <t>https://www.corvel.com/careers/</t>
         </is>
       </c>
-      <c r="D114" t="b">
-        <v>1</v>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E114" t="n">
-        <v>195</v>
-      </c>
-      <c r="F114" t="inlineStr"/>
-      <c r="G114" t="inlineStr"/>
-      <c r="H114" t="inlineStr"/>
+        <v>192</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -3433,21 +3332,19 @@
           <t>Addus HomeCare</t>
         </is>
       </c>
-      <c r="B115" t="inlineStr"/>
       <c r="C115" t="inlineStr">
         <is>
           <t>https://addus.com/careers/</t>
         </is>
       </c>
-      <c r="D115" t="b">
-        <v>1</v>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E115" t="n">
         <v>100</v>
       </c>
-      <c r="F115" t="inlineStr"/>
-      <c r="G115" t="inlineStr"/>
-      <c r="H115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -3465,15 +3362,14 @@
           <t>https://careers.ehab.com/</t>
         </is>
       </c>
-      <c r="D116" t="b">
-        <v>1</v>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E116" t="n">
-        <v>2140</v>
-      </c>
-      <c r="F116" t="inlineStr"/>
-      <c r="G116" t="inlineStr"/>
-      <c r="H116" t="inlineStr"/>
+        <v>2180</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -3481,21 +3377,19 @@
           <t>Aveanna Healthcare</t>
         </is>
       </c>
-      <c r="B117" t="inlineStr"/>
       <c r="C117" t="inlineStr">
         <is>
           <t>https://jobs.aveanna.com/</t>
         </is>
       </c>
-      <c r="D117" t="b">
-        <v>1</v>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E117" t="n">
-        <v>3722</v>
-      </c>
-      <c r="F117" t="inlineStr"/>
-      <c r="G117" t="inlineStr"/>
-      <c r="H117" t="inlineStr"/>
+        <v>3724</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -3503,21 +3397,19 @@
           <t>FinThrive</t>
         </is>
       </c>
-      <c r="B118" t="inlineStr"/>
       <c r="C118" t="inlineStr">
         <is>
           <t>https://finthrive.com/careers/</t>
         </is>
       </c>
-      <c r="D118" t="b">
-        <v>1</v>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E118" t="n">
-        <v>16</v>
-      </c>
-      <c r="F118" t="inlineStr"/>
-      <c r="G118" t="inlineStr"/>
-      <c r="H118" t="inlineStr"/>
+        <v>17</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -3535,15 +3427,14 @@
           <t>https://www.omnicell.com/about-us/careers</t>
         </is>
       </c>
-      <c r="D119" t="b">
-        <v>0</v>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
       </c>
       <c r="E119" t="n">
         <v>0</v>
       </c>
-      <c r="F119" t="inlineStr"/>
-      <c r="G119" t="inlineStr"/>
-      <c r="H119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -3561,15 +3452,14 @@
           <t>https://healthequity.com/careers</t>
         </is>
       </c>
-      <c r="D120" t="b">
-        <v>1</v>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E120" t="n">
-        <v>36</v>
-      </c>
-      <c r="F120" t="inlineStr"/>
-      <c r="G120" t="inlineStr"/>
-      <c r="H120" t="inlineStr"/>
+        <v>31</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -3587,15 +3477,14 @@
           <t>https://www.teladochealth.com/careers/</t>
         </is>
       </c>
-      <c r="D121" t="b">
-        <v>1</v>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E121" t="n">
-        <v>41</v>
-      </c>
-      <c r="F121" t="inlineStr"/>
-      <c r="G121" t="inlineStr"/>
-      <c r="H121" t="inlineStr"/>
+        <v>45</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -3608,16 +3497,14 @@
           <t>https://tiaa.wd1.myworkdayjobs.com/en-US/Search/</t>
         </is>
       </c>
-      <c r="C122" t="inlineStr"/>
-      <c r="D122" t="b">
-        <v>1</v>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E122" t="n">
-        <v>199</v>
-      </c>
-      <c r="F122" t="inlineStr"/>
-      <c r="G122" t="inlineStr"/>
-      <c r="H122" t="inlineStr"/>
+        <v>221</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -3630,16 +3517,14 @@
           <t>https://job-boards.greenhouse.io/allworthfinancial</t>
         </is>
       </c>
-      <c r="C123" t="inlineStr"/>
-      <c r="D123" t="b">
-        <v>1</v>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E123" t="n">
-        <v>21</v>
-      </c>
-      <c r="F123" t="inlineStr"/>
-      <c r="G123" t="inlineStr"/>
-      <c r="H123" t="inlineStr"/>
+        <v>22</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -3652,16 +3537,14 @@
           <t>https://vanguard.wd5.myworkdayjobs.com/en-US/vanguard_external/</t>
         </is>
       </c>
-      <c r="C124" t="inlineStr"/>
-      <c r="D124" t="b">
-        <v>1</v>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E124" t="n">
-        <v>423</v>
-      </c>
-      <c r="F124" t="inlineStr"/>
-      <c r="G124" t="inlineStr"/>
-      <c r="H124" t="inlineStr"/>
+        <v>428</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -3679,15 +3562,14 @@
           <t>https://www.usaajobs.com/search-jobs</t>
         </is>
       </c>
-      <c r="D125" t="b">
-        <v>1</v>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E125" t="n">
-        <v>171</v>
-      </c>
-      <c r="F125" t="inlineStr"/>
-      <c r="G125" t="inlineStr"/>
-      <c r="H125" t="inlineStr"/>
+        <v>177</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -3700,16 +3582,14 @@
           <t>https://boards.greenhouse.io/sofi</t>
         </is>
       </c>
-      <c r="C126" t="inlineStr"/>
-      <c r="D126" t="b">
-        <v>1</v>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E126" t="n">
-        <v>58</v>
-      </c>
-      <c r="F126" t="inlineStr"/>
-      <c r="G126" t="inlineStr"/>
-      <c r="H126" t="inlineStr"/>
+        <v>62</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -3727,15 +3607,14 @@
           <t>https://www.realpage.com/careers/</t>
         </is>
       </c>
-      <c r="D127" t="b">
-        <v>1</v>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E127" t="n">
-        <v>64</v>
-      </c>
-      <c r="F127" t="inlineStr"/>
-      <c r="G127" t="inlineStr"/>
-      <c r="H127" t="inlineStr"/>
+        <v>60</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -3743,21 +3622,19 @@
           <t>CBRE</t>
         </is>
       </c>
-      <c r="B128" t="inlineStr"/>
       <c r="C128" t="inlineStr">
         <is>
           <t>https://careers.cbre.com/</t>
         </is>
       </c>
-      <c r="D128" t="b">
-        <v>1</v>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E128" t="n">
-        <v>752</v>
-      </c>
-      <c r="F128" t="inlineStr"/>
-      <c r="G128" t="inlineStr"/>
-      <c r="H128" t="inlineStr"/>
+        <v>702</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -3775,15 +3652,14 @@
           <t>https://careers.invitationhomes.com/</t>
         </is>
       </c>
-      <c r="D129" t="b">
-        <v>1</v>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E129" t="n">
-        <v>63</v>
-      </c>
-      <c r="F129" t="inlineStr"/>
-      <c r="G129" t="inlineStr"/>
-      <c r="H129" t="inlineStr"/>
+        <v>62</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -3796,16 +3672,14 @@
           <t>https://recruiting.ultipro.com/WEL1008WLLT/JobBoard/30969ce4-3b7e-40a6-b86c-34d3616fe0ed/</t>
         </is>
       </c>
-      <c r="C130" t="inlineStr"/>
-      <c r="D130" t="b">
-        <v>1</v>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E130" t="n">
-        <v>82</v>
-      </c>
-      <c r="F130" t="inlineStr"/>
-      <c r="G130" t="inlineStr"/>
-      <c r="H130" t="inlineStr"/>
+        <v>81</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -3818,16 +3692,14 @@
           <t>https://careers.frostbank.com/us/en</t>
         </is>
       </c>
-      <c r="C131" t="inlineStr"/>
-      <c r="D131" t="b">
-        <v>1</v>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E131" t="n">
-        <v>183</v>
-      </c>
-      <c r="F131" t="inlineStr"/>
-      <c r="G131" t="inlineStr"/>
-      <c r="H131" t="inlineStr"/>
+        <v>193</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -3845,15 +3717,14 @@
           <t>https://jobs.statefarm.com/</t>
         </is>
       </c>
-      <c r="D132" t="b">
-        <v>1</v>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E132" t="n">
         <v>1</v>
       </c>
-      <c r="F132" t="inlineStr"/>
-      <c r="G132" t="inlineStr"/>
-      <c r="H132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -3861,21 +3732,19 @@
           <t>Globe Life</t>
         </is>
       </c>
-      <c r="B133" t="inlineStr"/>
       <c r="C133" t="inlineStr">
         <is>
           <t>https://careers.globelifeinsurance.com/</t>
         </is>
       </c>
-      <c r="D133" t="b">
-        <v>1</v>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E133" t="n">
-        <v>27</v>
-      </c>
-      <c r="F133" t="inlineStr"/>
-      <c r="G133" t="inlineStr"/>
-      <c r="H133" t="inlineStr"/>
+        <v>25</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -3893,15 +3762,14 @@
           <t>https://plainscapital.com/careers/</t>
         </is>
       </c>
-      <c r="D134" t="b">
-        <v>1</v>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E134" t="n">
-        <v>254</v>
-      </c>
-      <c r="F134" t="inlineStr"/>
-      <c r="G134" t="inlineStr"/>
-      <c r="H134" t="inlineStr"/>
+        <v>255</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -3919,15 +3787,14 @@
           <t>https://jobs.bokf.com/Bank-of-Texas/go/Bank-of-Texas/4477400/</t>
         </is>
       </c>
-      <c r="D135" t="b">
-        <v>1</v>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E135" t="n">
-        <v>200</v>
-      </c>
-      <c r="F135" t="inlineStr"/>
-      <c r="G135" t="inlineStr"/>
-      <c r="H135" t="inlineStr"/>
+        <v>198</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -3945,15 +3812,14 @@
           <t>https://www.theocc.com/careers</t>
         </is>
       </c>
-      <c r="D136" t="b">
-        <v>1</v>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E136" t="n">
-        <v>36</v>
-      </c>
-      <c r="F136" t="inlineStr"/>
-      <c r="G136" t="inlineStr"/>
-      <c r="H136" t="inlineStr"/>
+        <v>38</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -3966,16 +3832,14 @@
           <t>https://jobs.jobvite.com/firstcash-holdings-inc/</t>
         </is>
       </c>
-      <c r="C137" t="inlineStr"/>
-      <c r="D137" t="b">
-        <v>1</v>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E137" t="n">
-        <v>366</v>
-      </c>
-      <c r="F137" t="inlineStr"/>
-      <c r="G137" t="inlineStr"/>
-      <c r="H137" t="inlineStr"/>
+        <v>369</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -3993,15 +3857,14 @@
           <t>https://www.tpg.com/careers</t>
         </is>
       </c>
-      <c r="D138" t="b">
-        <v>1</v>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E138" t="n">
         <v>17</v>
       </c>
-      <c r="F138" t="inlineStr"/>
-      <c r="G138" t="inlineStr"/>
-      <c r="H138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -4014,16 +3877,14 @@
           <t>https://jll.wd1.myworkdayjobs.com/en-US/jllcareers/</t>
         </is>
       </c>
-      <c r="C139" t="inlineStr"/>
-      <c r="D139" t="b">
-        <v>1</v>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E139" t="n">
-        <v>2000</v>
-      </c>
-      <c r="F139" t="inlineStr"/>
-      <c r="G139" t="inlineStr"/>
-      <c r="H139" t="inlineStr"/>
+        <v>1997</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -4041,15 +3902,14 @@
           <t>https://www.intuit.com/careers/</t>
         </is>
       </c>
-      <c r="D140" t="b">
-        <v>1</v>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E140" t="n">
-        <v>454</v>
-      </c>
-      <c r="F140" t="inlineStr"/>
-      <c r="G140" t="inlineStr"/>
-      <c r="H140" t="inlineStr"/>
+        <v>451</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -4067,15 +3927,14 @@
           <t>https://mtch.com/careers/</t>
         </is>
       </c>
-      <c r="D141" t="b">
-        <v>1</v>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E141" t="n">
-        <v>66</v>
-      </c>
-      <c r="F141" t="inlineStr"/>
-      <c r="G141" t="inlineStr"/>
-      <c r="H141" t="inlineStr"/>
+        <v>70</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -4083,21 +3942,19 @@
           <t>Slalom</t>
         </is>
       </c>
-      <c r="B142" t="inlineStr"/>
       <c r="C142" t="inlineStr">
         <is>
           <t>https://www.slalom.com/us/en/careers</t>
         </is>
       </c>
-      <c r="D142" t="b">
-        <v>0</v>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E142" t="n">
-        <v>0</v>
-      </c>
-      <c r="F142" t="inlineStr"/>
-      <c r="G142" t="inlineStr"/>
-      <c r="H142" t="inlineStr"/>
+        <v>40</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -4110,16 +3967,14 @@
           <t>https://www.tcs.com/careers/united-states</t>
         </is>
       </c>
-      <c r="C143" t="inlineStr"/>
-      <c r="D143" t="b">
-        <v>0</v>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
       </c>
       <c r="E143" t="n">
         <v>0</v>
       </c>
-      <c r="F143" t="inlineStr"/>
-      <c r="G143" t="inlineStr"/>
-      <c r="H143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -4137,15 +3992,14 @@
           <t>https://www.jacobs.com/careers-jacobs</t>
         </is>
       </c>
-      <c r="D144" t="b">
-        <v>1</v>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E144" t="n">
-        <v>738</v>
-      </c>
-      <c r="F144" t="inlineStr"/>
-      <c r="G144" t="inlineStr"/>
-      <c r="H144" t="inlineStr"/>
+        <v>760</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -4163,15 +4017,14 @@
           <t>https://www.mcafee.com/en-us/careers.html</t>
         </is>
       </c>
-      <c r="D145" t="b">
-        <v>0</v>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
       </c>
       <c r="E145" t="n">
         <v>0</v>
       </c>
-      <c r="F145" t="inlineStr"/>
-      <c r="G145" t="inlineStr"/>
-      <c r="H145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -4189,15 +4042,14 @@
           <t>https://careers.bcg.com/</t>
         </is>
       </c>
-      <c r="D146" t="b">
-        <v>1</v>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E146" t="n">
-        <v>890</v>
-      </c>
-      <c r="F146" t="inlineStr"/>
-      <c r="G146" t="inlineStr"/>
-      <c r="H146" t="inlineStr"/>
+        <v>897</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -4215,15 +4067,14 @@
           <t>https://ryan.com/careers/</t>
         </is>
       </c>
-      <c r="D147" t="b">
-        <v>1</v>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E147" t="n">
-        <v>108</v>
-      </c>
-      <c r="F147" t="inlineStr"/>
-      <c r="G147" t="inlineStr"/>
-      <c r="H147" t="inlineStr"/>
+        <v>104</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -4241,15 +4092,14 @@
           <t>https://careers.christushealth.org/</t>
         </is>
       </c>
-      <c r="D148" t="b">
-        <v>1</v>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E148" t="n">
         <v>1</v>
       </c>
-      <c r="F148" t="inlineStr"/>
-      <c r="G148" t="inlineStr"/>
-      <c r="H148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -4267,15 +4117,14 @@
           <t>https://jpshealthnet.org/careers</t>
         </is>
       </c>
-      <c r="D149" t="b">
-        <v>1</v>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E149" t="n">
-        <v>168</v>
-      </c>
-      <c r="F149" t="inlineStr"/>
-      <c r="G149" t="inlineStr"/>
-      <c r="H149" t="inlineStr"/>
+        <v>170</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -4293,15 +4142,14 @@
           <t>https://www.amncareers.com/</t>
         </is>
       </c>
-      <c r="D150" t="b">
-        <v>1</v>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E150" t="n">
-        <v>29</v>
-      </c>
-      <c r="F150" t="inlineStr"/>
-      <c r="G150" t="inlineStr"/>
-      <c r="H150" t="inlineStr"/>
+        <v>31</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -4319,15 +4167,14 @@
           <t>https://www.galderma.com/careers</t>
         </is>
       </c>
-      <c r="D151" t="b">
-        <v>1</v>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E151" t="n">
-        <v>361</v>
-      </c>
-      <c r="F151" t="inlineStr"/>
-      <c r="G151" t="inlineStr"/>
-      <c r="H151" t="inlineStr"/>
+        <v>362</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -4345,15 +4192,14 @@
           <t>https://www.jobs.abbott/us/en</t>
         </is>
       </c>
-      <c r="D152" t="b">
-        <v>1</v>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E152" t="n">
-        <v>1998</v>
-      </c>
-      <c r="F152" t="inlineStr"/>
-      <c r="G152" t="inlineStr"/>
-      <c r="H152" t="inlineStr"/>
+        <v>2000</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -4371,15 +4217,14 @@
           <t>https://verily.com/careers</t>
         </is>
       </c>
-      <c r="D153" t="b">
-        <v>1</v>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E153" t="n">
-        <v>76</v>
-      </c>
-      <c r="F153" t="inlineStr"/>
-      <c r="G153" t="inlineStr"/>
-      <c r="H153" t="inlineStr"/>
+        <v>78</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -4397,15 +4242,14 @@
           <t>https://www.smith-nephew.com/en-us/careers</t>
         </is>
       </c>
-      <c r="D154" t="b">
-        <v>1</v>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E154" t="n">
-        <v>339</v>
-      </c>
-      <c r="F154" t="inlineStr"/>
-      <c r="G154" t="inlineStr"/>
-      <c r="H154" t="inlineStr"/>
+        <v>337</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -4423,15 +4267,14 @@
           <t>https://energytransfer.com/careers/</t>
         </is>
       </c>
-      <c r="D155" t="b">
-        <v>1</v>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E155" t="n">
         <v>10</v>
       </c>
-      <c r="F155" t="inlineStr"/>
-      <c r="G155" t="inlineStr"/>
-      <c r="H155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -4449,15 +4292,14 @@
           <t>https://www.drhorton.com/careers</t>
         </is>
       </c>
-      <c r="D156" t="b">
-        <v>1</v>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E156" t="n">
         <v>13</v>
       </c>
-      <c r="F156" t="inlineStr"/>
-      <c r="G156" t="inlineStr"/>
-      <c r="H156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -4475,15 +4317,14 @@
           <t>https://careers.hfsinclair.com/</t>
         </is>
       </c>
-      <c r="D157" t="b">
-        <v>1</v>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E157" t="n">
-        <v>104</v>
-      </c>
-      <c r="F157" t="inlineStr"/>
-      <c r="G157" t="inlineStr"/>
-      <c r="H157" t="inlineStr"/>
+        <v>105</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -4491,21 +4332,19 @@
           <t>Keurig Dr Pepper</t>
         </is>
       </c>
-      <c r="B158" t="inlineStr"/>
       <c r="C158" t="inlineStr">
         <is>
           <t>https://careers.keurigdrpepper.com/en</t>
         </is>
       </c>
-      <c r="D158" t="b">
-        <v>1</v>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E158" t="n">
         <v>15</v>
       </c>
-      <c r="F158" t="inlineStr"/>
-      <c r="G158" t="inlineStr"/>
-      <c r="H158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -4523,15 +4362,14 @@
           <t>https://vistracorp.com/careers/</t>
         </is>
       </c>
-      <c r="D159" t="b">
-        <v>1</v>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E159" t="n">
-        <v>185</v>
-      </c>
-      <c r="F159" t="inlineStr"/>
-      <c r="G159" t="inlineStr"/>
-      <c r="H159" t="inlineStr"/>
+        <v>183</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -4549,15 +4387,14 @@
           <t>https://careers.kimberly-clark.com/</t>
         </is>
       </c>
-      <c r="D160" t="b">
-        <v>1</v>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E160" t="n">
-        <v>184</v>
-      </c>
-      <c r="F160" t="inlineStr"/>
-      <c r="G160" t="inlineStr"/>
-      <c r="H160" t="inlineStr"/>
+        <v>178</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -4570,16 +4407,14 @@
           <t>https://careers.smartrecruiters.com/AECOM2/</t>
         </is>
       </c>
-      <c r="C161" t="inlineStr"/>
-      <c r="D161" t="b">
-        <v>1</v>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E161" t="n">
-        <v>5010</v>
-      </c>
-      <c r="F161" t="inlineStr"/>
-      <c r="G161" t="inlineStr"/>
-      <c r="H161" t="inlineStr"/>
+        <v>5027</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -4597,15 +4432,14 @@
           <t>https://careers.celanese.com/</t>
         </is>
       </c>
-      <c r="D162" t="b">
-        <v>1</v>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E162" t="n">
-        <v>77</v>
-      </c>
-      <c r="F162" t="inlineStr"/>
-      <c r="G162" t="inlineStr"/>
-      <c r="H162" t="inlineStr"/>
+        <v>76</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -4623,15 +4457,14 @@
           <t>https://jobs.greystar.com/</t>
         </is>
       </c>
-      <c r="D163" t="b">
-        <v>1</v>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E163" t="n">
-        <v>1600</v>
-      </c>
-      <c r="F163" t="inlineStr"/>
-      <c r="G163" t="inlineStr"/>
-      <c r="H163" t="inlineStr"/>
+        <v>1634</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -4649,15 +4482,14 @@
           <t>https://www.att.jobs/</t>
         </is>
       </c>
-      <c r="D164" t="b">
-        <v>1</v>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E164" t="n">
-        <v>1266</v>
-      </c>
-      <c r="F164" t="inlineStr"/>
-      <c r="G164" t="inlineStr"/>
-      <c r="H164" t="inlineStr"/>
+        <v>1260</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -4675,15 +4507,14 @@
           <t>https://www.schwabjobs.com/</t>
         </is>
       </c>
-      <c r="D165" t="b">
-        <v>1</v>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E165" t="n">
         <v>313</v>
       </c>
-      <c r="F165" t="inlineStr"/>
-      <c r="G165" t="inlineStr"/>
-      <c r="H165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -4691,20 +4522,19 @@
           <t>Verizon</t>
         </is>
       </c>
-      <c r="B166" t="inlineStr"/>
       <c r="C166" t="inlineStr">
         <is>
           <t>https://mycareer.verizon.com/jobs/</t>
         </is>
       </c>
-      <c r="D166" t="b">
-        <v>1</v>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E166" t="n">
-        <v>346</v>
-      </c>
-      <c r="F166" t="inlineStr"/>
-      <c r="G166" t="inlineStr"/>
+        <v>406</v>
+      </c>
       <c r="H166" t="inlineStr">
         <is>
           <t>ATS URL pointed at a login-gated Workday candidate-home (userHome) endpoint that 422s on the CXS API; cleared so it routes via the working Live Jobs Page instead.</t>
@@ -4727,15 +4557,14 @@
           <t>https://www.tempursealy.com/careers/</t>
         </is>
       </c>
-      <c r="D167" t="b">
-        <v>1</v>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E167" t="n">
         <v>224</v>
       </c>
-      <c r="F167" t="inlineStr"/>
-      <c r="G167" t="inlineStr"/>
-      <c r="H167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -4743,21 +4572,19 @@
           <t>Randstad USA</t>
         </is>
       </c>
-      <c r="B168" t="inlineStr"/>
       <c r="C168" t="inlineStr">
         <is>
           <t>https://www.randstadusa.com/jobs/</t>
         </is>
       </c>
-      <c r="D168" t="b">
-        <v>1</v>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E168" t="n">
         <v>160</v>
       </c>
-      <c r="F168" t="inlineStr"/>
-      <c r="G168" t="inlineStr"/>
-      <c r="H168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -4775,15 +4602,14 @@
           <t>https://careers.teksystems.com/us/en</t>
         </is>
       </c>
-      <c r="D169" t="b">
-        <v>1</v>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E169" t="n">
-        <v>118</v>
-      </c>
-      <c r="F169" t="inlineStr"/>
-      <c r="G169" t="inlineStr"/>
-      <c r="H169" t="inlineStr"/>
+        <v>131</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -4801,15 +4627,14 @@
           <t>https://insightglobal.com/find-a-job/</t>
         </is>
       </c>
-      <c r="D170" t="b">
-        <v>1</v>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E170" t="n">
         <v>1</v>
       </c>
-      <c r="F170" t="inlineStr"/>
-      <c r="G170" t="inlineStr"/>
-      <c r="H170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -4817,20 +4642,19 @@
           <t>Apex Systems</t>
         </is>
       </c>
-      <c r="B171" t="inlineStr"/>
       <c r="C171" t="inlineStr">
         <is>
           <t>https://www.apexsystems.com/search-results-usa</t>
         </is>
       </c>
-      <c r="D171" t="b">
-        <v>1</v>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E171" t="n">
-        <v>49</v>
-      </c>
-      <c r="F171" t="inlineStr"/>
-      <c r="G171" t="inlineStr"/>
+        <v>25</v>
+      </c>
       <c r="H171" t="inlineStr">
         <is>
           <t>ATS URL (itcareers.apexsystems.com) intermittently 522s at the Cloudflare edge and always wins over Live Jobs Page in routing regardless; cleared so it routes straight to the working search-results-usa URL instead.</t>
@@ -4843,21 +4667,19 @@
           <t>Kforce</t>
         </is>
       </c>
-      <c r="B172" t="inlineStr"/>
       <c r="C172" t="inlineStr">
         <is>
           <t>https://www.kforce.com/find-work/search-jobs/</t>
         </is>
       </c>
-      <c r="D172" t="b">
-        <v>1</v>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E172" t="n">
         <v>25</v>
       </c>
-      <c r="F172" t="inlineStr"/>
-      <c r="G172" t="inlineStr"/>
-      <c r="H172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -4865,21 +4687,19 @@
           <t>Experis (ManpowerGroup)</t>
         </is>
       </c>
-      <c r="B173" t="inlineStr"/>
       <c r="C173" t="inlineStr">
         <is>
           <t>https://www.experis.com/en/for-job-seekers</t>
         </is>
       </c>
-      <c r="D173" t="b">
-        <v>1</v>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E173" t="n">
         <v>13</v>
       </c>
-      <c r="F173" t="inlineStr"/>
-      <c r="G173" t="inlineStr"/>
-      <c r="H173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -4897,15 +4717,14 @@
           <t>https://www.judge.com/jobs/</t>
         </is>
       </c>
-      <c r="D174" t="b">
-        <v>1</v>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E174" t="n">
         <v>14</v>
       </c>
-      <c r="F174" t="inlineStr"/>
-      <c r="G174" t="inlineStr"/>
-      <c r="H174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -4913,20 +4732,19 @@
           <t>Eliassen Group</t>
         </is>
       </c>
-      <c r="B175" t="inlineStr"/>
       <c r="C175" t="inlineStr">
         <is>
           <t>https://www.eliassen.com/careers</t>
         </is>
       </c>
-      <c r="D175" t="b">
-        <v>0</v>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
       </c>
       <c r="E175" t="n">
         <v>0</v>
       </c>
-      <c r="F175" t="inlineStr"/>
-      <c r="G175" t="inlineStr"/>
       <c r="H175" t="inlineStr">
         <is>
           <t>careers.eliassen.com (the real consultant job board with a Data category) returns HTTP 403 from nginx to headless Chromium even with stealth patches; a real interactive Chrome session loads it fine, so this is bot-management fingerprinting, not a dead site.</t>
@@ -4949,15 +4767,14 @@
           <t>https://www.roberthalf.com/us/en/find-jobs</t>
         </is>
       </c>
-      <c r="D176" t="b">
-        <v>1</v>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E176" t="n">
-        <v>232</v>
-      </c>
-      <c r="F176" t="inlineStr"/>
-      <c r="G176" t="inlineStr"/>
-      <c r="H176" t="inlineStr"/>
+        <v>245</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -4965,20 +4782,19 @@
           <t>Mphasis</t>
         </is>
       </c>
-      <c r="B177" t="inlineStr"/>
       <c r="C177" t="inlineStr">
         <is>
           <t>https://mphasis.ripplehire.com/candidate/?token=ty4DfyWddnOrtpclQeia&amp;source=CAREERSITE#list</t>
         </is>
       </c>
-      <c r="D177" t="b">
-        <v>1</v>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E177" t="n">
         <v>10</v>
       </c>
-      <c r="F177" t="inlineStr"/>
-      <c r="G177" t="inlineStr"/>
       <c r="H177" t="inlineStr">
         <is>
           <t>careers.mphasis.com only shows jobs after submitting its 3-field search form (experience/title/location), which opens a NEW TAB to mphasis.ripplehire.com with a token in the URL. That token is a stable per-tenant widget key (reproduced identically across separate clicks), not a session token - this exact URL with no filters lists all 189 open jobs directly.</t>
@@ -4991,21 +4807,19 @@
           <t>Pyramid Consulting</t>
         </is>
       </c>
-      <c r="B178" t="inlineStr"/>
       <c r="C178" t="inlineStr">
         <is>
           <t>https://pyramidci.com/careers/</t>
         </is>
       </c>
-      <c r="D178" t="b">
-        <v>1</v>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E178" t="n">
         <v>363</v>
       </c>
-      <c r="F178" t="inlineStr"/>
-      <c r="G178" t="inlineStr"/>
-      <c r="H178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -5023,15 +4837,14 @@
           <t>https://jobs.aerotek.com/us/en</t>
         </is>
       </c>
-      <c r="D179" t="b">
-        <v>1</v>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E179" t="n">
-        <v>224</v>
-      </c>
-      <c r="F179" t="inlineStr"/>
-      <c r="G179" t="inlineStr"/>
-      <c r="H179" t="inlineStr"/>
+        <v>226</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -5039,20 +4852,19 @@
           <t>Kelly Services</t>
         </is>
       </c>
-      <c r="B180" t="inlineStr"/>
       <c r="C180" t="inlineStr">
         <is>
           <t>https://www.mykelly.com/find-jobs/technology-jobs/</t>
         </is>
       </c>
-      <c r="D180" t="b">
-        <v>1</v>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E180" t="n">
-        <v>3</v>
-      </c>
-      <c r="F180" t="inlineStr"/>
-      <c r="G180" t="inlineStr"/>
+        <v>130</v>
+      </c>
       <c r="H180" t="inlineStr">
         <is>
           <t>www.kellyservices.com/find-a-job/ is a marketing splash page with no reachable job list; corrected to the real myKelly technology-jobs search page.</t>
@@ -5065,21 +4877,19 @@
           <t>Motion Recruitment</t>
         </is>
       </c>
-      <c r="B181" t="inlineStr"/>
       <c r="C181" t="inlineStr">
         <is>
           <t>https://motionrecruitment.com/tech-jobs/data-engineering</t>
         </is>
       </c>
-      <c r="D181" t="b">
-        <v>1</v>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E181" t="n">
-        <v>47</v>
-      </c>
-      <c r="F181" t="inlineStr"/>
-      <c r="G181" t="inlineStr"/>
-      <c r="H181" t="inlineStr"/>
+        <v>44</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -5087,21 +4897,19 @@
           <t>Dexian</t>
         </is>
       </c>
-      <c r="B182" t="inlineStr"/>
       <c r="C182" t="inlineStr">
         <is>
           <t>https://dexian.com/jobs/</t>
         </is>
       </c>
-      <c r="D182" t="b">
-        <v>1</v>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E182" t="n">
         <v>39</v>
       </c>
-      <c r="F182" t="inlineStr"/>
-      <c r="G182" t="inlineStr"/>
-      <c r="H182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -5109,21 +4917,19 @@
           <t>Built In</t>
         </is>
       </c>
-      <c r="B183" t="inlineStr"/>
       <c r="C183" t="inlineStr">
         <is>
           <t>https://builtin.com/jobs</t>
         </is>
       </c>
-      <c r="D183" t="b">
-        <v>1</v>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E183" t="n">
-        <v>1097</v>
-      </c>
-      <c r="F183" t="inlineStr"/>
-      <c r="G183" t="inlineStr"/>
-      <c r="H183" t="inlineStr"/>
+        <v>1179</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -5136,16 +4942,14 @@
           <t>https://globalcareers-msci.icims.com/jobs/</t>
         </is>
       </c>
-      <c r="C184" t="inlineStr"/>
-      <c r="D184" t="b">
-        <v>1</v>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E184" t="n">
-        <v>105</v>
-      </c>
-      <c r="F184" t="inlineStr"/>
-      <c r="G184" t="inlineStr"/>
-      <c r="H184" t="inlineStr"/>
+        <v>107</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -5163,14 +4967,14 @@
           <t>https://www.isnetworld.com/en/careers#jobs</t>
         </is>
       </c>
-      <c r="D185" t="b">
-        <v>0</v>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E185" t="n">
-        <v>0</v>
-      </c>
-      <c r="F185" t="inlineStr"/>
-      <c r="G185" t="inlineStr"/>
+        <v>16</v>
+      </c>
       <c r="H185" t="inlineStr">
         <is>
           <t>Greenhouse board token 'isn'; careers page is Drupal + AJAX so the live page resolves to nothing. Board points at isnetworld.com, so gh_jid is the whole job identity.</t>

--- a/config/companies.xlsx
+++ b/config/companies.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H185"/>
+  <dimension ref="A1:H186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,7 +480,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>7143</v>
+        <v>7229</v>
       </c>
     </row>
     <row r="3">
@@ -570,7 +570,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1330</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="7">
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1684</v>
+        <v>1776</v>
       </c>
     </row>
     <row r="8">
@@ -610,7 +610,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>560</v>
+        <v>567</v>
       </c>
     </row>
     <row r="9">
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>207</v>
+        <v>204</v>
       </c>
     </row>
     <row r="10">
@@ -655,7 +655,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="11">
@@ -675,7 +675,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>361</v>
+        <v>359</v>
       </c>
     </row>
     <row r="12">
@@ -695,7 +695,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>282</v>
+        <v>287</v>
       </c>
     </row>
     <row r="13">
@@ -755,7 +755,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="15">
@@ -780,7 +780,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>370</v>
+        <v>395</v>
       </c>
     </row>
     <row r="17">
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>607</v>
+        <v>645</v>
       </c>
     </row>
     <row r="20">
@@ -925,7 +925,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>9999</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="21">
@@ -1050,7 +1050,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1334</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="25">
@@ -1070,7 +1070,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>620</v>
+        <v>685</v>
       </c>
     </row>
     <row r="26">
@@ -1095,7 +1095,7 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4500</v>
+        <v>4505</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1135,7 +1135,7 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1990</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="28">
@@ -1160,7 +1160,7 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="29">
@@ -1185,7 +1185,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>248</v>
+        <v>265</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1225,7 +1225,7 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>305</v>
+        <v>291</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>617</v>
+        <v>610</v>
       </c>
     </row>
     <row r="34">
@@ -1400,7 +1400,7 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -1440,7 +1440,7 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>702</v>
+        <v>707</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
     </row>
     <row r="38">
@@ -1508,7 +1508,7 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5297</v>
+        <v>5312</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -1548,7 +1548,7 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5191</v>
+        <v>5190</v>
       </c>
     </row>
     <row r="40">
@@ -1573,7 +1573,7 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="41">
@@ -1598,7 +1598,7 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="42">
@@ -1643,7 +1643,7 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2228</v>
+        <v>2226</v>
       </c>
     </row>
     <row r="44">
@@ -1668,7 +1668,7 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>522</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="45">
@@ -1693,7 +1693,7 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1482</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="46">
@@ -1718,7 +1718,7 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1262</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="47">
@@ -1743,7 +1743,7 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>577</v>
+        <v>601</v>
       </c>
     </row>
     <row r="48">
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>630</v>
+        <v>639</v>
       </c>
     </row>
     <row r="50">
@@ -1843,7 +1843,7 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>845</v>
+        <v>848</v>
       </c>
     </row>
     <row r="52">
@@ -1883,7 +1883,7 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>35</v>
+        <v>82</v>
       </c>
     </row>
     <row r="54">
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1740</v>
+        <v>1978</v>
       </c>
     </row>
     <row r="56">
@@ -1953,7 +1953,7 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1152</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="57">
@@ -2003,7 +2003,7 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>7725</v>
+        <v>7823</v>
       </c>
     </row>
     <row r="59">
@@ -2023,7 +2023,7 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="60">
@@ -2044,11 +2044,11 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -2068,7 +2068,7 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="62">
@@ -2093,7 +2093,7 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1139</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="63">
@@ -2118,7 +2118,7 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>413</v>
+        <v>433</v>
       </c>
     </row>
     <row r="64">
@@ -2143,7 +2143,7 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1322</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="65">
@@ -2168,7 +2168,7 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>423</v>
+        <v>418</v>
       </c>
     </row>
     <row r="66">
@@ -2188,7 +2188,7 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>574</v>
+        <v>586</v>
       </c>
     </row>
     <row r="67">
@@ -2208,7 +2208,7 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>372</v>
+        <v>391</v>
       </c>
     </row>
     <row r="68">
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>423</v>
+        <v>437</v>
       </c>
     </row>
     <row r="69">
@@ -2278,7 +2278,7 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="71">
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="72">
@@ -2328,7 +2328,7 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="73">
@@ -2348,7 +2348,7 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
     </row>
     <row r="74">
@@ -2373,7 +2373,7 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>880</v>
+        <v>925</v>
       </c>
     </row>
     <row r="75">
@@ -2413,7 +2413,7 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>491</v>
+        <v>511</v>
       </c>
     </row>
     <row r="77">
@@ -2438,7 +2438,7 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="78">
@@ -2483,7 +2483,7 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="80">
@@ -2508,7 +2508,7 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="81">
@@ -2533,7 +2533,7 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>235</v>
+        <v>248</v>
       </c>
     </row>
     <row r="82">
@@ -2558,7 +2558,7 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>4500</v>
+        <v>4505</v>
       </c>
     </row>
     <row r="83">
@@ -2578,7 +2578,7 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
@@ -2608,7 +2608,7 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1850</v>
+        <v>1855</v>
       </c>
     </row>
     <row r="85">
@@ -2633,7 +2633,7 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1934</v>
+        <v>1936</v>
       </c>
     </row>
     <row r="86">
@@ -2653,7 +2653,7 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>310</v>
+        <v>306</v>
       </c>
     </row>
     <row r="87">
@@ -2678,7 +2678,7 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>185</v>
+        <v>182</v>
       </c>
     </row>
     <row r="91">
@@ -2768,7 +2768,7 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="92">
@@ -2793,7 +2793,7 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>725</v>
+        <v>729</v>
       </c>
     </row>
     <row r="93">
@@ -2818,7 +2818,7 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>247</v>
+        <v>242</v>
       </c>
     </row>
     <row r="94">
@@ -2843,7 +2843,7 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>2895</v>
+        <v>2932</v>
       </c>
     </row>
     <row r="95">
@@ -2868,7 +2868,7 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>3398</v>
+        <v>3394</v>
       </c>
     </row>
     <row r="96">
@@ -2888,7 +2888,7 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>491</v>
+        <v>511</v>
       </c>
     </row>
     <row r="97">
@@ -2908,7 +2908,7 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>217</v>
+        <v>222</v>
       </c>
     </row>
     <row r="98">
@@ -2933,7 +2933,7 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>938</v>
+        <v>943</v>
       </c>
     </row>
     <row r="99">
@@ -2953,7 +2953,7 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="100">
@@ -2978,7 +2978,7 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6680</v>
+        <v>7300</v>
       </c>
       <c r="H100" t="inlineStr">
         <is>
@@ -3038,7 +3038,7 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>119</v>
+        <v>132</v>
       </c>
     </row>
     <row r="103">
@@ -3103,7 +3103,7 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>549</v>
+        <v>566</v>
       </c>
     </row>
     <row r="106">
@@ -3128,7 +3128,7 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>323</v>
+        <v>336</v>
       </c>
     </row>
     <row r="107">
@@ -3153,7 +3153,7 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="108">
@@ -3178,7 +3178,7 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="109">
@@ -3203,7 +3203,7 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>2133</v>
+        <v>2159</v>
       </c>
     </row>
     <row r="110">
@@ -3228,7 +3228,7 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>324</v>
+        <v>315</v>
       </c>
     </row>
     <row r="111">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>1198</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="112">
@@ -3323,7 +3323,7 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>192</v>
+        <v>189</v>
       </c>
     </row>
     <row r="115">
@@ -3343,7 +3343,7 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="116">
@@ -3368,7 +3368,7 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>2180</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="117">
@@ -3408,7 +3408,7 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="119">
@@ -3458,7 +3458,7 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="121">
@@ -3503,7 +3503,7 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>221</v>
+        <v>232</v>
       </c>
     </row>
     <row r="123">
@@ -3543,7 +3543,7 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>428</v>
+        <v>439</v>
       </c>
     </row>
     <row r="125">
@@ -3568,7 +3568,7 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>177</v>
+        <v>189</v>
       </c>
     </row>
     <row r="126">
@@ -3588,7 +3588,7 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="127">
@@ -3613,7 +3613,7 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="128">
@@ -3633,7 +3633,7 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>702</v>
+        <v>302</v>
       </c>
     </row>
     <row r="129">
@@ -3658,7 +3658,7 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="130">
@@ -3678,7 +3678,7 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="131">
@@ -3698,7 +3698,7 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>193</v>
+        <v>197</v>
       </c>
     </row>
     <row r="132">
@@ -3768,7 +3768,7 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="135">
@@ -3818,7 +3818,7 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="137">
@@ -3838,7 +3838,7 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>369</v>
+        <v>373</v>
       </c>
     </row>
     <row r="138">
@@ -3883,7 +3883,7 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>1997</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="140">
@@ -3908,7 +3908,7 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>451</v>
+        <v>454</v>
       </c>
     </row>
     <row r="141">
@@ -3933,7 +3933,7 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="142">
@@ -3998,7 +3998,7 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>760</v>
+        <v>756</v>
       </c>
     </row>
     <row r="145">
@@ -4048,7 +4048,7 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>897</v>
+        <v>906</v>
       </c>
     </row>
     <row r="147">
@@ -4073,7 +4073,7 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="148">
@@ -4123,7 +4123,7 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>170</v>
+        <v>176</v>
       </c>
     </row>
     <row r="150">
@@ -4173,7 +4173,7 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>362</v>
+        <v>366</v>
       </c>
     </row>
     <row r="152">
@@ -4198,7 +4198,7 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>2000</v>
+        <v>1999</v>
       </c>
     </row>
     <row r="153">
@@ -4223,7 +4223,7 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>78</v>
+        <v>68</v>
       </c>
     </row>
     <row r="154">
@@ -4248,7 +4248,7 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>337</v>
+        <v>343</v>
       </c>
     </row>
     <row r="155">
@@ -4273,7 +4273,7 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>10</v>
+        <v>54</v>
       </c>
     </row>
     <row r="156">
@@ -4298,7 +4298,7 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="157">
@@ -4323,7 +4323,7 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>105</v>
+        <v>109</v>
       </c>
     </row>
     <row r="158">
@@ -4368,7 +4368,7 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="160">
@@ -4393,7 +4393,7 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>178</v>
+        <v>175</v>
       </c>
     </row>
     <row r="161">
@@ -4413,7 +4413,7 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>5027</v>
+        <v>5029</v>
       </c>
     </row>
     <row r="162">
@@ -4438,7 +4438,7 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="163">
@@ -4463,7 +4463,7 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>1634</v>
+        <v>1627</v>
       </c>
     </row>
     <row r="164">
@@ -4488,7 +4488,7 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>1260</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="165">
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>313</v>
+        <v>334</v>
       </c>
     </row>
     <row r="166">
@@ -4533,7 +4533,7 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>406</v>
+        <v>384</v>
       </c>
       <c r="H166" t="inlineStr">
         <is>
@@ -4563,7 +4563,7 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>224</v>
+        <v>219</v>
       </c>
     </row>
     <row r="168">
@@ -4583,7 +4583,7 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="169">
@@ -4653,7 +4653,7 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="H171" t="inlineStr">
         <is>
@@ -4723,7 +4723,7 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="175">
@@ -4773,7 +4773,7 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>245</v>
+        <v>249</v>
       </c>
     </row>
     <row r="177">
@@ -4818,7 +4818,7 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>363</v>
+        <v>373</v>
       </c>
     </row>
     <row r="179">
@@ -4843,7 +4843,7 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>226</v>
+        <v>216</v>
       </c>
     </row>
     <row r="180">
@@ -4863,7 +4863,7 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>130</v>
+        <v>30</v>
       </c>
       <c r="H180" t="inlineStr">
         <is>
@@ -4888,7 +4888,7 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="182">
@@ -4908,7 +4908,7 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>39</v>
+        <v>197</v>
       </c>
     </row>
     <row r="183">
@@ -4928,7 +4928,7 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>1179</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="184">
@@ -4948,7 +4948,7 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="185">
@@ -4978,6 +4978,23 @@
       <c r="H185" t="inlineStr">
         <is>
           <t>Greenhouse board token 'isn'; careers page is Drupal + AJAX so the live page resolves to nothing. Board points at isnetworld.com, so gh_jid is the whole job identity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Citi</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>https://citi.wd5.myworkdayjobs.com/2</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>https://jobs.citi.com/search-jobs</t>
         </is>
       </c>
     </row>
